--- a/sea_productive.xlsx
+++ b/sea_productive.xlsx
@@ -109,8 +109,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:H11" totalsRowShown="0">
-  <autoFilter ref="A1:H11"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:H12" totalsRowShown="0">
+  <autoFilter ref="A1:H12"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Date_Converted" dataDxfId="0"/>
     <tableColumn id="2" name="Staff Hour (In Hours)" dataDxfId="1"/>
@@ -410,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -678,25 +678,51 @@
         <v>46133</v>
       </c>
       <c r="B11" s="2">
-        <v>13.01193775102289</v>
+        <v>286.7875681531905</v>
       </c>
       <c r="C11" s="2">
-        <v>0.4386736128065321</v>
+        <v>44.36489684247308</v>
       </c>
       <c r="D11" s="2">
-        <v>10.91706857803588</v>
+        <v>151.8822429773853</v>
       </c>
       <c r="E11" s="2">
-        <v>1.405921672119035</v>
+        <v>57.75635954093602</v>
       </c>
       <c r="F11" s="2">
+        <v>30.57105546871821</v>
+      </c>
+      <c r="G11" s="2">
+        <v>2.213013323677911</v>
+      </c>
+      <c r="H11" s="3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B12" s="2">
+        <v>15.82497109674745</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0.7298255750868056</v>
+      </c>
+      <c r="D12" s="2">
+        <v>7.837001960277558</v>
+      </c>
+      <c r="E12" s="2">
+        <v>6.042070522076553</v>
+      </c>
+      <c r="F12" s="2">
         <v>0</v>
       </c>
-      <c r="G11" s="2">
-        <v>0.250273888061444</v>
-      </c>
-      <c r="H11" s="3">
-        <v>13</v>
+      <c r="G12" s="2">
+        <v>1.216073039306535</v>
+      </c>
+      <c r="H12" s="3">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -956,13 +982,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA0E2238-E2E0-4631-A5CF-183465458178}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1E89805-057F-4AD8-A4A8-8AFC4A0A0304}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2FD1F60A-5D44-4F59-9463-A87672A0291C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{884AB486-68D1-432E-B69B-F8740844C916}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{905CD423-1253-4D88-9045-782F1FC7E85E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14882C8E-5212-4729-A0CE-8AE2FE4AF6B9}"/>
 </file>
--- a/sea_productive.xlsx
+++ b/sea_productive.xlsx
@@ -109,8 +109,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:H12" totalsRowShown="0">
-  <autoFilter ref="A1:H12"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:H13" totalsRowShown="0">
+  <autoFilter ref="A1:H13"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Date_Converted" dataDxfId="0"/>
     <tableColumn id="2" name="Staff Hour (In Hours)" dataDxfId="1"/>
@@ -410,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -704,25 +704,51 @@
         <v>46134</v>
       </c>
       <c r="B12" s="2">
-        <v>15.82497109674745</v>
+        <v>249.6248776487447</v>
       </c>
       <c r="C12" s="2">
-        <v>0.7298255750868056</v>
+        <v>33.29971796876854</v>
       </c>
       <c r="D12" s="2">
-        <v>7.837001960277558</v>
+        <v>115.4994636634427</v>
       </c>
       <c r="E12" s="2">
-        <v>6.042070522076553</v>
+        <v>48.54623563612501</v>
       </c>
       <c r="F12" s="2">
+        <v>40.18255291408963</v>
+      </c>
+      <c r="G12" s="2">
+        <v>12.09690746631887</v>
+      </c>
+      <c r="H12" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B13" s="2">
+        <v>14.50191506182154</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0.234566396077474</v>
+      </c>
+      <c r="D13" s="2">
+        <v>1.200191957685683</v>
+      </c>
+      <c r="E13" s="2">
+        <v>7.748134893112712</v>
+      </c>
+      <c r="F13" s="2">
         <v>0</v>
       </c>
-      <c r="G12" s="2">
-        <v>1.216073039306535</v>
-      </c>
-      <c r="H12" s="3">
-        <v>14</v>
+      <c r="G13" s="2">
+        <v>5.319021814945671</v>
+      </c>
+      <c r="H13" s="3">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -982,13 +1008,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1E89805-057F-4AD8-A4A8-8AFC4A0A0304}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5DABEDD-1376-4AEE-9B6B-E21CFD9EA67B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{884AB486-68D1-432E-B69B-F8740844C916}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A79001C6-7B95-44AD-946F-2FDCD5A4CAF4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14882C8E-5212-4729-A0CE-8AE2FE4AF6B9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DD04D4E-5A4C-4AE8-AE95-4F8033C4B02C}"/>
 </file>
--- a/sea_productive.xlsx
+++ b/sea_productive.xlsx
@@ -109,8 +109,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:H13" totalsRowShown="0">
-  <autoFilter ref="A1:H13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:H14" totalsRowShown="0">
+  <autoFilter ref="A1:H14"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Date_Converted" dataDxfId="0"/>
     <tableColumn id="2" name="Staff Hour (In Hours)" dataDxfId="1"/>
@@ -410,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -730,25 +730,51 @@
         <v>46135</v>
       </c>
       <c r="B13" s="2">
-        <v>14.50191506182154</v>
+        <v>251.2084220583075</v>
       </c>
       <c r="C13" s="2">
-        <v>0.234566396077474</v>
+        <v>34.3688434874018</v>
       </c>
       <c r="D13" s="2">
-        <v>1.200191957685683</v>
+        <v>106.304737093548</v>
       </c>
       <c r="E13" s="2">
-        <v>7.748134893112712</v>
+        <v>64.60221893481082</v>
       </c>
       <c r="F13" s="2">
-        <v>0</v>
+        <v>39.09782712300618</v>
       </c>
       <c r="G13" s="2">
-        <v>5.319021814945671</v>
+        <v>6.83479541954067</v>
       </c>
       <c r="H13" s="3">
-        <v>12</v>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="1">
+        <v>46136</v>
+      </c>
+      <c r="B14" s="2">
+        <v>29.52834722847574</v>
+      </c>
+      <c r="C14" s="2">
+        <v>2.31149888780382</v>
+      </c>
+      <c r="D14" s="2">
+        <v>24.53639470837182</v>
+      </c>
+      <c r="E14" s="2">
+        <v>1.993315842176477</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0.4375977918836805</v>
+      </c>
+      <c r="G14" s="2">
+        <v>0.2495399982399411</v>
+      </c>
+      <c r="H14" s="3">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1008,13 +1034,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5DABEDD-1376-4AEE-9B6B-E21CFD9EA67B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54F578EA-5B75-415B-8E9C-4316B2A83C34}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A79001C6-7B95-44AD-946F-2FDCD5A4CAF4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7A1EF05-3457-48B2-81CA-5526A4799744}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DD04D4E-5A4C-4AE8-AE95-4F8033C4B02C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C875F271-A127-422C-8B0B-08DCEC6D1735}"/>
 </file>
--- a/sea_productive.xlsx
+++ b/sea_productive.xlsx
@@ -109,8 +109,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:H14" totalsRowShown="0">
-  <autoFilter ref="A1:H14"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:H16" totalsRowShown="0">
+  <autoFilter ref="A1:H16"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Date_Converted" dataDxfId="0"/>
     <tableColumn id="2" name="Staff Hour (In Hours)" dataDxfId="1"/>
@@ -410,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -756,25 +756,77 @@
         <v>46136</v>
       </c>
       <c r="B14" s="2">
-        <v>29.52834722847574</v>
+        <v>261.515016779108</v>
       </c>
       <c r="C14" s="2">
-        <v>2.31149888780382</v>
+        <v>38.25786742495166</v>
       </c>
       <c r="D14" s="2">
-        <v>24.53639470837182</v>
+        <v>148.7460722376282</v>
       </c>
       <c r="E14" s="2">
-        <v>1.993315842176477</v>
+        <v>41.9854927673522</v>
       </c>
       <c r="F14" s="2">
-        <v>0.4375977918836805</v>
+        <v>29.84546653747559</v>
       </c>
       <c r="G14" s="2">
-        <v>0.2495399982399411</v>
+        <v>2.680117811700329</v>
       </c>
       <c r="H14" s="3">
-        <v>15</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="1">
+        <v>46137</v>
+      </c>
+      <c r="B15" s="2">
+        <v>295.5410275634233</v>
+      </c>
+      <c r="C15" s="2">
+        <v>45.03800446298387</v>
+      </c>
+      <c r="D15" s="2">
+        <v>159.6257019741647</v>
+      </c>
+      <c r="E15" s="2">
+        <v>79.94608134516412</v>
+      </c>
+      <c r="F15" s="2">
+        <v>8.576289774576823</v>
+      </c>
+      <c r="G15" s="2">
+        <v>2.354950006533828</v>
+      </c>
+      <c r="H15" s="3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="1">
+        <v>46138</v>
+      </c>
+      <c r="B16" s="2">
+        <v>67.82963681224733</v>
+      </c>
+      <c r="C16" s="2">
+        <v>7.054274519681931</v>
+      </c>
+      <c r="D16" s="2">
+        <v>32.12192141407894</v>
+      </c>
+      <c r="E16" s="2">
+        <v>27.65078086275193</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0.2637830607096354</v>
+      </c>
+      <c r="G16" s="2">
+        <v>0.738876955024898</v>
+      </c>
+      <c r="H16" s="3">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1034,13 +1086,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54F578EA-5B75-415B-8E9C-4316B2A83C34}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E08C8E29-0F0C-43B3-8851-2378ABF340BC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7A1EF05-3457-48B2-81CA-5526A4799744}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81E74CEB-E413-449E-93D7-BAE959D9179B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C875F271-A127-422C-8B0B-08DCEC6D1735}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B721E093-9425-44A8-ABFD-9C7008BFAF17}"/>
 </file>
--- a/sea_productive.xlsx
+++ b/sea_productive.xlsx
@@ -109,8 +109,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:H16" totalsRowShown="0">
-  <autoFilter ref="A1:H16"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:H18" totalsRowShown="0">
+  <autoFilter ref="A1:H18"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Date_Converted" dataDxfId="0"/>
     <tableColumn id="2" name="Staff Hour (In Hours)" dataDxfId="1"/>
@@ -410,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -652,10 +652,10 @@
         <v>46132</v>
       </c>
       <c r="B10" s="2">
-        <v>298.058737374821</v>
+        <v>288.824123178335</v>
       </c>
       <c r="C10" s="2">
-        <v>43.25082855224609</v>
+        <v>42.36635189480252</v>
       </c>
       <c r="D10" s="2">
         <v>129.1712352487305</v>
@@ -664,13 +664,13 @@
         <v>107.0414793449309</v>
       </c>
       <c r="F10" s="2">
-        <v>15.43102753036552</v>
+        <v>7.084813880191909</v>
       </c>
       <c r="G10" s="2">
-        <v>3.164166698547908</v>
+        <v>3.160242809679152</v>
       </c>
       <c r="H10" s="3">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -678,10 +678,10 @@
         <v>46133</v>
       </c>
       <c r="B11" s="2">
-        <v>286.7875681531905</v>
+        <v>260.8965785061465</v>
       </c>
       <c r="C11" s="2">
-        <v>44.36489684247308</v>
+        <v>40.30407802194357</v>
       </c>
       <c r="D11" s="2">
         <v>151.8822429773853</v>
@@ -690,13 +690,13 @@
         <v>57.75635954093602</v>
       </c>
       <c r="F11" s="2">
-        <v>30.57105546871821</v>
+        <v>8.765534364117517</v>
       </c>
       <c r="G11" s="2">
-        <v>2.213013323677911</v>
+        <v>2.188363601764043</v>
       </c>
       <c r="H11" s="3">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -704,10 +704,10 @@
         <v>46134</v>
       </c>
       <c r="B12" s="2">
-        <v>249.6248776487447</v>
+        <v>212.8907304516042</v>
       </c>
       <c r="C12" s="2">
-        <v>33.29971796876854</v>
+        <v>32.27424128419823</v>
       </c>
       <c r="D12" s="2">
         <v>115.4994636634427</v>
@@ -716,13 +716,13 @@
         <v>48.54623563612501</v>
       </c>
       <c r="F12" s="2">
-        <v>40.18255291408963</v>
+        <v>14.17942682902018</v>
       </c>
       <c r="G12" s="2">
-        <v>12.09690746631887</v>
+        <v>2.391363038818041</v>
       </c>
       <c r="H12" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -730,10 +730,10 @@
         <v>46135</v>
       </c>
       <c r="B13" s="2">
-        <v>251.2084220583075</v>
+        <v>218.9280812006692</v>
       </c>
       <c r="C13" s="2">
-        <v>34.3688434874018</v>
+        <v>33.38276323295302</v>
       </c>
       <c r="D13" s="2">
         <v>106.304737093548</v>
@@ -742,13 +742,13 @@
         <v>64.60221893481082</v>
       </c>
       <c r="F13" s="2">
-        <v>39.09782712300618</v>
+        <v>13.08933916727702</v>
       </c>
       <c r="G13" s="2">
-        <v>6.83479541954067</v>
+        <v>1.549022772080368</v>
       </c>
       <c r="H13" s="3">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -756,10 +756,10 @@
         <v>46136</v>
       </c>
       <c r="B14" s="2">
-        <v>261.515016779108</v>
+        <v>243.5352080432605</v>
       </c>
       <c r="C14" s="2">
-        <v>38.25786742495166</v>
+        <v>37.10335299352805</v>
       </c>
       <c r="D14" s="2">
         <v>148.7460722376282</v>
@@ -768,13 +768,13 @@
         <v>41.9854927673522</v>
       </c>
       <c r="F14" s="2">
-        <v>29.84546653747559</v>
+        <v>13.08109723409017</v>
       </c>
       <c r="G14" s="2">
-        <v>2.680117811700329</v>
+        <v>2.619192810661884</v>
       </c>
       <c r="H14" s="3">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -808,25 +808,77 @@
         <v>46138</v>
       </c>
       <c r="B16" s="2">
-        <v>67.82963681224733</v>
+        <v>281.2355133626817</v>
       </c>
       <c r="C16" s="2">
-        <v>7.054274519681931</v>
+        <v>42.84105554348893</v>
       </c>
       <c r="D16" s="2">
-        <v>32.12192141407894</v>
+        <v>97.31553551588621</v>
       </c>
       <c r="E16" s="2">
-        <v>27.65078086275193</v>
+        <v>133.8467120167447</v>
       </c>
       <c r="F16" s="2">
-        <v>0.2637830607096354</v>
+        <v>2.745579155815972</v>
       </c>
       <c r="G16" s="2">
-        <v>0.738876955024898</v>
+        <v>4.486631130745842</v>
       </c>
       <c r="H16" s="3">
-        <v>20</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="1">
+        <v>46139</v>
+      </c>
+      <c r="B17" s="2">
+        <v>214.7356720573704</v>
+      </c>
+      <c r="C17" s="2">
+        <v>31.84751321550873</v>
+      </c>
+      <c r="D17" s="2">
+        <v>80.54385508432985</v>
+      </c>
+      <c r="E17" s="2">
+        <v>97.50572902141346</v>
+      </c>
+      <c r="F17" s="2">
+        <v>3.601089180840386</v>
+      </c>
+      <c r="G17" s="2">
+        <v>1.23748555527793</v>
+      </c>
+      <c r="H17" s="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="1">
+        <v>46140</v>
+      </c>
+      <c r="B18" s="2">
+        <v>16.81707222398784</v>
+      </c>
+      <c r="C18" s="2">
+        <v>0.4354755655924479</v>
+      </c>
+      <c r="D18" s="2">
+        <v>9.759091125859154</v>
+      </c>
+      <c r="E18" s="2">
+        <v>6.434805810451508</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0</v>
+      </c>
+      <c r="G18" s="2">
+        <v>0.1876997220847342</v>
+      </c>
+      <c r="H18" s="3">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1086,13 +1138,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E08C8E29-0F0C-43B3-8851-2378ABF340BC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1870C758-4E7B-4EA2-8F27-F2E2BCBAB539}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81E74CEB-E413-449E-93D7-BAE959D9179B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1BA870F1-9DEE-423D-8C56-6506025FFFC8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B721E093-9425-44A8-ABFD-9C7008BFAF17}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B2CB0B8A-92BA-48EC-9E72-53F6BD2C4CBC}"/>
 </file>
--- a/sea_productive.xlsx
+++ b/sea_productive.xlsx
@@ -109,8 +109,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:H18" totalsRowShown="0">
-  <autoFilter ref="A1:H18"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:H19" totalsRowShown="0">
+  <autoFilter ref="A1:H19"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Date_Converted" dataDxfId="0"/>
     <tableColumn id="2" name="Staff Hour (In Hours)" dataDxfId="1"/>
@@ -410,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -860,25 +860,51 @@
         <v>46140</v>
       </c>
       <c r="B18" s="2">
-        <v>16.81707222398784</v>
+        <v>188.3966501657499</v>
       </c>
       <c r="C18" s="2">
-        <v>0.4354755655924479</v>
+        <v>28.4410385724571</v>
       </c>
       <c r="D18" s="2">
-        <v>9.759091125859154</v>
+        <v>85.89948526518212</v>
       </c>
       <c r="E18" s="2">
-        <v>6.434805810451508</v>
+        <v>68.54402510571811</v>
       </c>
       <c r="F18" s="2">
+        <v>4.423320109049479</v>
+      </c>
+      <c r="G18" s="2">
+        <v>1.088781113343106</v>
+      </c>
+      <c r="H18" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="1">
+        <v>46141</v>
+      </c>
+      <c r="B19" s="2">
+        <v>31.17535522351662</v>
+      </c>
+      <c r="C19" s="2">
+        <v>0.8537411159939237</v>
+      </c>
+      <c r="D19" s="2">
+        <v>13.11674444503254</v>
+      </c>
+      <c r="E19" s="2">
+        <v>16.89507688363393</v>
+      </c>
+      <c r="F19" s="2">
         <v>0</v>
       </c>
-      <c r="G18" s="2">
-        <v>0.1876997220847342</v>
-      </c>
-      <c r="H18" s="3">
-        <v>8</v>
+      <c r="G19" s="2">
+        <v>0.3097927788562245</v>
+      </c>
+      <c r="H19" s="3">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1138,13 +1164,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1870C758-4E7B-4EA2-8F27-F2E2BCBAB539}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77A7EDBD-3A1C-4B2E-AFA5-0064DF9C41E5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1BA870F1-9DEE-423D-8C56-6506025FFFC8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8FC0443-E2DC-4305-9860-2D47C7E34886}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B2CB0B8A-92BA-48EC-9E72-53F6BD2C4CBC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12C57343-9475-4493-A0D5-3E644F129090}"/>
 </file>
--- a/sea_productive.xlsx
+++ b/sea_productive.xlsx
@@ -109,8 +109,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:H19" totalsRowShown="0">
-  <autoFilter ref="A1:H19"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:H20" totalsRowShown="0">
+  <autoFilter ref="A1:H20"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Date_Converted" dataDxfId="0"/>
     <tableColumn id="2" name="Staff Hour (In Hours)" dataDxfId="1"/>
@@ -410,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -886,25 +886,51 @@
         <v>46141</v>
       </c>
       <c r="B19" s="2">
-        <v>31.17535522351662</v>
+        <v>250.7527417366662</v>
       </c>
       <c r="C19" s="2">
-        <v>0.8537411159939237</v>
+        <v>36.03463883413209</v>
       </c>
       <c r="D19" s="2">
-        <v>13.11674444503254</v>
+        <v>115.5841033623078</v>
       </c>
       <c r="E19" s="2">
-        <v>16.89507688363393</v>
+        <v>92.17480784644683</v>
       </c>
       <c r="F19" s="2">
+        <v>3.25470106654697</v>
+      </c>
+      <c r="G19" s="2">
+        <v>3.704490627232525</v>
+      </c>
+      <c r="H19" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="1">
+        <v>46142</v>
+      </c>
+      <c r="B20" s="2">
+        <v>55.43430330821209</v>
+      </c>
+      <c r="C20" s="2">
+        <v>5.343841403987673</v>
+      </c>
+      <c r="D20" s="2">
+        <v>38.20205745779806</v>
+      </c>
+      <c r="E20" s="2">
+        <v>11.32253582432866</v>
+      </c>
+      <c r="F20" s="2">
         <v>0</v>
       </c>
-      <c r="G19" s="2">
-        <v>0.3097927788562245</v>
-      </c>
-      <c r="H19" s="3">
-        <v>15</v>
+      <c r="G20" s="2">
+        <v>0.5658686220977042</v>
+      </c>
+      <c r="H20" s="3">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1164,13 +1190,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77A7EDBD-3A1C-4B2E-AFA5-0064DF9C41E5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{360DDFB6-38EE-4656-9CF9-597D600F5D64}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8FC0443-E2DC-4305-9860-2D47C7E34886}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10AEF44F-CB42-4D3B-99A9-54CB8C31E4A5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12C57343-9475-4493-A0D5-3E644F129090}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CFD3D15-4442-47E0-82A5-DE904D44B47E}"/>
 </file>
--- a/sea_productive.xlsx
+++ b/sea_productive.xlsx
@@ -109,8 +109,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:H20" totalsRowShown="0">
-  <autoFilter ref="A1:H20"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:H22" totalsRowShown="0">
+  <autoFilter ref="A1:H22"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Date_Converted" dataDxfId="0"/>
     <tableColumn id="2" name="Staff Hour (In Hours)" dataDxfId="1"/>
@@ -410,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -912,25 +912,77 @@
         <v>46142</v>
       </c>
       <c r="B20" s="2">
-        <v>55.43430330821209</v>
+        <v>189.8929473854664</v>
       </c>
       <c r="C20" s="2">
-        <v>5.343841403987673</v>
+        <v>29.90951245903969</v>
       </c>
       <c r="D20" s="2">
-        <v>38.20205745779806</v>
+        <v>109.241959625139</v>
       </c>
       <c r="E20" s="2">
-        <v>11.32253582432866</v>
+        <v>49.2553244445059</v>
       </c>
       <c r="F20" s="2">
+        <v>0.0004016666611035665</v>
+      </c>
+      <c r="G20" s="2">
+        <v>1.485749190120647</v>
+      </c>
+      <c r="H20" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="1">
+        <v>46143</v>
+      </c>
+      <c r="B21" s="2">
+        <v>236.9741027833154</v>
+      </c>
+      <c r="C21" s="2">
+        <v>35.30577249864737</v>
+      </c>
+      <c r="D21" s="2">
+        <v>118.939983162243</v>
+      </c>
+      <c r="E21" s="2">
+        <v>79.02687909699148</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0.289986384080516</v>
+      </c>
+      <c r="G21" s="2">
+        <v>3.411481641353005</v>
+      </c>
+      <c r="H21" s="3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="1">
+        <v>46144</v>
+      </c>
+      <c r="B22" s="2">
+        <v>69.94097559931895</v>
+      </c>
+      <c r="C22" s="2">
+        <v>4.268404702080621</v>
+      </c>
+      <c r="D22" s="2">
+        <v>42.99527116890273</v>
+      </c>
+      <c r="E22" s="2">
+        <v>22.4405597274916</v>
+      </c>
+      <c r="F22" s="2">
         <v>0</v>
       </c>
-      <c r="G20" s="2">
-        <v>0.5658686220977042</v>
-      </c>
-      <c r="H20" s="3">
-        <v>12</v>
+      <c r="G22" s="2">
+        <v>0.2367400008440018</v>
+      </c>
+      <c r="H22" s="3">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -1190,13 +1242,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{360DDFB6-38EE-4656-9CF9-597D600F5D64}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C86F6C3-411E-4297-B03E-CD2534BE9497}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10AEF44F-CB42-4D3B-99A9-54CB8C31E4A5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11467407-C8C5-4549-937E-12F695A02BF5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CFD3D15-4442-47E0-82A5-DE904D44B47E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FBBC0E1F-AD4F-4B63-9518-C79D5CE3AE7C}"/>
 </file>
--- a/sea_productive.xlsx
+++ b/sea_productive.xlsx
@@ -109,8 +109,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:H22" totalsRowShown="0">
-  <autoFilter ref="A1:H22"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:H25" totalsRowShown="0">
+  <autoFilter ref="A1:H25"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Date_Converted" dataDxfId="0"/>
     <tableColumn id="2" name="Staff Hour (In Hours)" dataDxfId="1"/>
@@ -410,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -964,25 +964,103 @@
         <v>46144</v>
       </c>
       <c r="B22" s="2">
-        <v>69.94097559931895</v>
+        <v>287.6914919003316</v>
       </c>
       <c r="C22" s="2">
-        <v>4.268404702080621</v>
+        <v>45.85951106760237</v>
       </c>
       <c r="D22" s="2">
-        <v>42.99527116890273</v>
+        <v>168.6124217177565</v>
       </c>
       <c r="E22" s="2">
-        <v>22.4405597274916</v>
+        <v>68.90445611220267</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>1.737823571099175</v>
       </c>
       <c r="G22" s="2">
-        <v>0.2367400008440018</v>
+        <v>2.577279431670904</v>
       </c>
       <c r="H22" s="3">
-        <v>17</v>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="1">
+        <v>46145</v>
+      </c>
+      <c r="B23" s="2">
+        <v>259.709311512347</v>
+      </c>
+      <c r="C23" s="2">
+        <v>39.46693604773945</v>
+      </c>
+      <c r="D23" s="2">
+        <v>116.7329225043021</v>
+      </c>
+      <c r="E23" s="2">
+        <v>100.732365763055</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0.9525635796123081</v>
+      </c>
+      <c r="G23" s="2">
+        <v>1.824523617638172</v>
+      </c>
+      <c r="H23" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="1">
+        <v>46146</v>
+      </c>
+      <c r="B24" s="2">
+        <v>419.1311424101785</v>
+      </c>
+      <c r="C24" s="2">
+        <v>52.99363439333108</v>
+      </c>
+      <c r="D24" s="2">
+        <v>240.5802804369272</v>
+      </c>
+      <c r="E24" s="2">
+        <v>94.28195947988786</v>
+      </c>
+      <c r="F24" s="2">
+        <v>14.12164852566189</v>
+      </c>
+      <c r="G24" s="2">
+        <v>17.15361957437048</v>
+      </c>
+      <c r="H24" s="3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="1">
+        <v>46147</v>
+      </c>
+      <c r="B25" s="2">
+        <v>58.39487821909702</v>
+      </c>
+      <c r="C25" s="2">
+        <v>2.492463599344095</v>
+      </c>
+      <c r="D25" s="2">
+        <v>37.18409544021305</v>
+      </c>
+      <c r="E25" s="2">
+        <v>16.80530001307527</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0.3628191645691792</v>
+      </c>
+      <c r="G25" s="2">
+        <v>1.550200001895428</v>
+      </c>
+      <c r="H25" s="3">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -1242,13 +1320,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C86F6C3-411E-4297-B03E-CD2534BE9497}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1580B45B-1F83-4DE5-AAC6-5283A006A330}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11467407-C8C5-4549-937E-12F695A02BF5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD003F39-4BE8-4727-97CB-F11FF3A51FF8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FBBC0E1F-AD4F-4B63-9518-C79D5CE3AE7C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A2B45EE-E754-4F09-8BE8-42DDAE0A0DB7}"/>
 </file>
--- a/sea_productive.xlsx
+++ b/sea_productive.xlsx
@@ -109,8 +109,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:H25" totalsRowShown="0">
-  <autoFilter ref="A1:H25"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:H27" totalsRowShown="0">
+  <autoFilter ref="A1:H27"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Date_Converted" dataDxfId="0"/>
     <tableColumn id="2" name="Staff Hour (In Hours)" dataDxfId="1"/>
@@ -410,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1042,25 +1042,77 @@
         <v>46147</v>
       </c>
       <c r="B25" s="2">
-        <v>58.39487821909702</v>
+        <v>461.1700450927418</v>
       </c>
       <c r="C25" s="2">
-        <v>2.492463599344095</v>
+        <v>65.63128696233292</v>
       </c>
       <c r="D25" s="2">
-        <v>37.18409544021305</v>
+        <v>198.2021644964359</v>
       </c>
       <c r="E25" s="2">
-        <v>16.80530001307527</v>
+        <v>163.891013423966</v>
       </c>
       <c r="F25" s="2">
-        <v>0.3628191645691792</v>
+        <v>9.302166808984346</v>
       </c>
       <c r="G25" s="2">
-        <v>1.550200001895428</v>
+        <v>24.14341340102255</v>
       </c>
       <c r="H25" s="3">
-        <v>22</v>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B26" s="2">
+        <v>448.2830351440391</v>
+      </c>
+      <c r="C26" s="2">
+        <v>61.99363578266568</v>
+      </c>
+      <c r="D26" s="2">
+        <v>187.0999176729916</v>
+      </c>
+      <c r="E26" s="2">
+        <v>147.7754280505743</v>
+      </c>
+      <c r="F26" s="2">
+        <v>20.66326173659828</v>
+      </c>
+      <c r="G26" s="2">
+        <v>30.75079190120929</v>
+      </c>
+      <c r="H26" s="3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B27" s="2">
+        <v>40.89102994323605</v>
+      </c>
+      <c r="C27" s="2">
+        <v>1.544781104193793</v>
+      </c>
+      <c r="D27" s="2">
+        <v>23.5155561520656</v>
+      </c>
+      <c r="E27" s="2">
+        <v>15.16887518746158</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0</v>
+      </c>
+      <c r="G27" s="2">
+        <v>0.6618174995150831</v>
+      </c>
+      <c r="H27" s="3">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1320,13 +1372,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1580B45B-1F83-4DE5-AAC6-5283A006A330}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEACD1EC-DFF5-4FE8-84BF-30D9AD7D265A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD003F39-4BE8-4727-97CB-F11FF3A51FF8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1A679B9-829F-4B25-82D3-A34106DEAB0A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A2B45EE-E754-4F09-8BE8-42DDAE0A0DB7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55AB8A7F-2C0F-4314-90F9-A94054CB3FF7}"/>
 </file>
--- a/sea_productive.xlsx
+++ b/sea_productive.xlsx
@@ -109,8 +109,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:H27" totalsRowShown="0">
-  <autoFilter ref="A1:H27"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:H28" totalsRowShown="0">
+  <autoFilter ref="A1:H28"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Date_Converted" dataDxfId="0"/>
     <tableColumn id="2" name="Staff Hour (In Hours)" dataDxfId="1"/>
@@ -410,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -441,678 +441,704 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="1">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B2" s="2">
-        <v>55.76765300801645</v>
+        <v>323.1610120714394</v>
       </c>
       <c r="C2" s="2">
-        <v>4.953005040486653</v>
+        <v>44.92686601665285</v>
       </c>
       <c r="D2" s="2">
-        <v>43.30376297463973</v>
+        <v>139.963458599324</v>
       </c>
       <c r="E2" s="2">
-        <v>7.027266379143629</v>
+        <v>130.2241021273575</v>
       </c>
       <c r="F2" s="2">
-        <v>0</v>
+        <v>2.248729739718967</v>
       </c>
       <c r="G2" s="2">
-        <v>0.4836186137464311</v>
+        <v>5.797855588386042</v>
       </c>
       <c r="H2" s="3">
-        <v>11</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B3" s="2">
-        <v>267.3933590634229</v>
+        <v>273.6781417201752</v>
       </c>
       <c r="C3" s="2">
-        <v>39.97386097616619</v>
+        <v>40.0413355584277</v>
       </c>
       <c r="D3" s="2">
-        <v>96.65969562468429</v>
+        <v>103.511928198818</v>
       </c>
       <c r="E3" s="2">
-        <v>123.1968357482139</v>
+        <v>117.2581249379449</v>
       </c>
       <c r="F3" s="2">
-        <v>2.248729739718967</v>
+        <v>7.059696611232228</v>
       </c>
       <c r="G3" s="2">
-        <v>5.314236974639611</v>
+        <v>5.807056413752337</v>
       </c>
       <c r="H3" s="3">
-        <v>41</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B4" s="2">
-        <v>273.6781417201752</v>
+        <v>298.2914358288205</v>
       </c>
       <c r="C4" s="2">
-        <v>40.0413355584277</v>
+        <v>47.16884657353162</v>
       </c>
       <c r="D4" s="2">
-        <v>103.511928198818</v>
+        <v>119.399162515108</v>
       </c>
       <c r="E4" s="2">
-        <v>117.2581249379449</v>
+        <v>117.7262078565638</v>
       </c>
       <c r="F4" s="2">
-        <v>7.059696611232228</v>
+        <v>12.05913498222828</v>
       </c>
       <c r="G4" s="2">
-        <v>5.807056413752337</v>
+        <v>1.938083901388778</v>
       </c>
       <c r="H4" s="3">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B5" s="2">
-        <v>298.2914358288205</v>
+        <v>272.8079848140644</v>
       </c>
       <c r="C5" s="2">
-        <v>47.16884657353162</v>
+        <v>39.51949952118927</v>
       </c>
       <c r="D5" s="2">
-        <v>119.399162515108</v>
+        <v>120.8711398820165</v>
       </c>
       <c r="E5" s="2">
-        <v>117.7262078565638</v>
+        <v>100.8949301929772</v>
       </c>
       <c r="F5" s="2">
-        <v>12.05913498222828</v>
+        <v>8.75364024238454</v>
       </c>
       <c r="G5" s="2">
-        <v>1.938083901388778</v>
+        <v>2.768774975496862</v>
       </c>
       <c r="H5" s="3">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B6" s="2">
-        <v>272.8079848140644</v>
+        <v>309.9964914664471</v>
       </c>
       <c r="C6" s="2">
-        <v>39.51949952118927</v>
+        <v>43.6269740500715</v>
       </c>
       <c r="D6" s="2">
-        <v>120.8711398820165</v>
+        <v>133.4939823072486</v>
       </c>
       <c r="E6" s="2">
-        <v>100.8949301929772</v>
+        <v>108.2581891838058</v>
       </c>
       <c r="F6" s="2">
-        <v>8.75364024238454</v>
+        <v>17.38662732382615</v>
       </c>
       <c r="G6" s="2">
-        <v>2.768774975496862</v>
+        <v>7.230718601495028</v>
       </c>
       <c r="H6" s="3">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1">
-        <v>46129</v>
+        <v>46130</v>
       </c>
       <c r="B7" s="2">
-        <v>309.9964914664471</v>
+        <v>308.5183830143159</v>
       </c>
       <c r="C7" s="2">
-        <v>43.6269740500715</v>
+        <v>46.30651540866329</v>
       </c>
       <c r="D7" s="2">
-        <v>133.4939823072486</v>
+        <v>166.1900152229249</v>
       </c>
       <c r="E7" s="2">
-        <v>108.2581891838058</v>
+        <v>84.06776373089188</v>
       </c>
       <c r="F7" s="2">
-        <v>17.38662732382615</v>
+        <v>8.05202755873402</v>
       </c>
       <c r="G7" s="2">
-        <v>7.230718601495028</v>
+        <v>3.902061093101899</v>
       </c>
       <c r="H7" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B8" s="2">
-        <v>308.5183830143159</v>
+        <v>249.7613502550125</v>
       </c>
       <c r="C8" s="2">
-        <v>46.30651540866329</v>
+        <v>31.50441224275364</v>
       </c>
       <c r="D8" s="2">
-        <v>166.1900152229249</v>
+        <v>89.46780061095126</v>
       </c>
       <c r="E8" s="2">
-        <v>84.06776373089188</v>
+        <v>92.31769759105312</v>
       </c>
       <c r="F8" s="2">
-        <v>8.05202755873402</v>
+        <v>25.69309524112278</v>
       </c>
       <c r="G8" s="2">
-        <v>3.902061093101899</v>
+        <v>10.77834456913173</v>
       </c>
       <c r="H8" s="3">
-        <v>36</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B9" s="2">
-        <v>249.7613502550125</v>
+        <v>288.824123178335</v>
       </c>
       <c r="C9" s="2">
-        <v>31.50441224275364</v>
+        <v>42.36635189480252</v>
       </c>
       <c r="D9" s="2">
-        <v>89.46780061095126</v>
+        <v>129.1712352487305</v>
       </c>
       <c r="E9" s="2">
-        <v>92.31769759105312</v>
+        <v>107.0414793449309</v>
       </c>
       <c r="F9" s="2">
-        <v>25.69309524112278</v>
+        <v>7.084813880191909</v>
       </c>
       <c r="G9" s="2">
-        <v>10.77834456913173</v>
+        <v>3.160242809679152</v>
       </c>
       <c r="H9" s="3">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B10" s="2">
-        <v>288.824123178335</v>
+        <v>260.8965785061465</v>
       </c>
       <c r="C10" s="2">
-        <v>42.36635189480252</v>
+        <v>40.30407802194357</v>
       </c>
       <c r="D10" s="2">
-        <v>129.1712352487305</v>
+        <v>151.8822429773853</v>
       </c>
       <c r="E10" s="2">
-        <v>107.0414793449309</v>
+        <v>57.75635954093602</v>
       </c>
       <c r="F10" s="2">
-        <v>7.084813880191909</v>
+        <v>8.765534364117517</v>
       </c>
       <c r="G10" s="2">
-        <v>3.160242809679152</v>
+        <v>2.188363601764043</v>
       </c>
       <c r="H10" s="3">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B11" s="2">
-        <v>260.8965785061465</v>
+        <v>212.8907304516042</v>
       </c>
       <c r="C11" s="2">
-        <v>40.30407802194357</v>
+        <v>32.27424128419823</v>
       </c>
       <c r="D11" s="2">
-        <v>151.8822429773853</v>
+        <v>115.4994636634427</v>
       </c>
       <c r="E11" s="2">
-        <v>57.75635954093602</v>
+        <v>48.54623563612501</v>
       </c>
       <c r="F11" s="2">
-        <v>8.765534364117517</v>
+        <v>14.17942682902018</v>
       </c>
       <c r="G11" s="2">
-        <v>2.188363601764043</v>
+        <v>2.391363038818041</v>
       </c>
       <c r="H11" s="3">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B12" s="2">
-        <v>212.8907304516042</v>
+        <v>218.9280812006692</v>
       </c>
       <c r="C12" s="2">
-        <v>32.27424128419823</v>
+        <v>33.38276323295302</v>
       </c>
       <c r="D12" s="2">
-        <v>115.4994636634427</v>
+        <v>106.304737093548</v>
       </c>
       <c r="E12" s="2">
-        <v>48.54623563612501</v>
+        <v>64.60221893481082</v>
       </c>
       <c r="F12" s="2">
-        <v>14.17942682902018</v>
+        <v>13.08933916727702</v>
       </c>
       <c r="G12" s="2">
-        <v>2.391363038818041</v>
+        <v>1.549022772080368</v>
       </c>
       <c r="H12" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B13" s="2">
-        <v>218.9280812006692</v>
+        <v>243.5352080432605</v>
       </c>
       <c r="C13" s="2">
-        <v>33.38276323295302</v>
+        <v>37.10335299352805</v>
       </c>
       <c r="D13" s="2">
-        <v>106.304737093548</v>
+        <v>148.7460722376282</v>
       </c>
       <c r="E13" s="2">
-        <v>64.60221893481082</v>
+        <v>41.9854927673522</v>
       </c>
       <c r="F13" s="2">
-        <v>13.08933916727702</v>
+        <v>13.08109723409017</v>
       </c>
       <c r="G13" s="2">
-        <v>1.549022772080368</v>
+        <v>2.619192810661884</v>
       </c>
       <c r="H13" s="3">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B14" s="2">
-        <v>243.5352080432605</v>
+        <v>295.5410275634233</v>
       </c>
       <c r="C14" s="2">
-        <v>37.10335299352805</v>
+        <v>45.03800446298387</v>
       </c>
       <c r="D14" s="2">
-        <v>148.7460722376282</v>
+        <v>159.6257019741647</v>
       </c>
       <c r="E14" s="2">
-        <v>41.9854927673522</v>
+        <v>79.94608134516412</v>
       </c>
       <c r="F14" s="2">
-        <v>13.08109723409017</v>
+        <v>8.576289774576823</v>
       </c>
       <c r="G14" s="2">
-        <v>2.619192810661884</v>
+        <v>2.354950006533828</v>
       </c>
       <c r="H14" s="3">
-        <v>28</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B15" s="2">
-        <v>295.5410275634233</v>
+        <v>281.2355133626817</v>
       </c>
       <c r="C15" s="2">
-        <v>45.03800446298387</v>
+        <v>42.84105554348893</v>
       </c>
       <c r="D15" s="2">
-        <v>159.6257019741647</v>
+        <v>97.31553551588621</v>
       </c>
       <c r="E15" s="2">
-        <v>79.94608134516412</v>
+        <v>133.8467120167447</v>
       </c>
       <c r="F15" s="2">
-        <v>8.576289774576823</v>
+        <v>2.745579155815972</v>
       </c>
       <c r="G15" s="2">
-        <v>2.354950006533828</v>
+        <v>4.486631130745842</v>
       </c>
       <c r="H15" s="3">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1">
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="B16" s="2">
-        <v>281.2355133626817</v>
+        <v>214.7356720573704</v>
       </c>
       <c r="C16" s="2">
-        <v>42.84105554348893</v>
+        <v>31.84751321550873</v>
       </c>
       <c r="D16" s="2">
-        <v>97.31553551588621</v>
+        <v>80.54385508432985</v>
       </c>
       <c r="E16" s="2">
-        <v>133.8467120167447</v>
+        <v>97.50572902141346</v>
       </c>
       <c r="F16" s="2">
-        <v>2.745579155815972</v>
+        <v>3.601089180840386</v>
       </c>
       <c r="G16" s="2">
-        <v>4.486631130745842</v>
+        <v>1.23748555527793</v>
       </c>
       <c r="H16" s="3">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B17" s="2">
-        <v>214.7356720573704</v>
+        <v>188.3966501657499</v>
       </c>
       <c r="C17" s="2">
-        <v>31.84751321550873</v>
+        <v>28.4410385724571</v>
       </c>
       <c r="D17" s="2">
-        <v>80.54385508432985</v>
+        <v>85.89948526518212</v>
       </c>
       <c r="E17" s="2">
-        <v>97.50572902141346</v>
+        <v>68.54402510571811</v>
       </c>
       <c r="F17" s="2">
-        <v>3.601089180840386</v>
+        <v>4.423320109049479</v>
       </c>
       <c r="G17" s="2">
-        <v>1.23748555527793</v>
+        <v>1.088781113343106</v>
       </c>
       <c r="H17" s="3">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B18" s="2">
-        <v>188.3966501657499</v>
+        <v>250.7527417366662</v>
       </c>
       <c r="C18" s="2">
-        <v>28.4410385724571</v>
+        <v>36.03463883413209</v>
       </c>
       <c r="D18" s="2">
-        <v>85.89948526518212</v>
+        <v>115.5841033623078</v>
       </c>
       <c r="E18" s="2">
-        <v>68.54402510571811</v>
+        <v>92.17480784644683</v>
       </c>
       <c r="F18" s="2">
-        <v>4.423320109049479</v>
+        <v>3.25470106654697</v>
       </c>
       <c r="G18" s="2">
-        <v>1.088781113343106</v>
+        <v>3.704490627232525</v>
       </c>
       <c r="H18" s="3">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B19" s="2">
-        <v>250.7527417366662</v>
+        <v>189.8929473854664</v>
       </c>
       <c r="C19" s="2">
-        <v>36.03463883413209</v>
+        <v>29.90951245903969</v>
       </c>
       <c r="D19" s="2">
-        <v>115.5841033623078</v>
+        <v>109.241959625139</v>
       </c>
       <c r="E19" s="2">
-        <v>92.17480784644683</v>
+        <v>49.2553244445059</v>
       </c>
       <c r="F19" s="2">
-        <v>3.25470106654697</v>
+        <v>0.0004016666611035665</v>
       </c>
       <c r="G19" s="2">
-        <v>3.704490627232525</v>
+        <v>1.485749190120647</v>
       </c>
       <c r="H19" s="3">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B20" s="2">
-        <v>189.8929473854664</v>
+        <v>236.9741027833154</v>
       </c>
       <c r="C20" s="2">
-        <v>29.90951245903969</v>
+        <v>35.30577249864737</v>
       </c>
       <c r="D20" s="2">
-        <v>109.241959625139</v>
+        <v>118.939983162243</v>
       </c>
       <c r="E20" s="2">
-        <v>49.2553244445059</v>
+        <v>79.02687909699148</v>
       </c>
       <c r="F20" s="2">
-        <v>0.0004016666611035665</v>
+        <v>0.289986384080516</v>
       </c>
       <c r="G20" s="2">
-        <v>1.485749190120647</v>
+        <v>3.411481641353005</v>
       </c>
       <c r="H20" s="3">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B21" s="2">
-        <v>236.9741027833154</v>
+        <v>287.6914919003316</v>
       </c>
       <c r="C21" s="2">
-        <v>35.30577249864737</v>
+        <v>45.85951106760237</v>
       </c>
       <c r="D21" s="2">
-        <v>118.939983162243</v>
+        <v>168.6124217177565</v>
       </c>
       <c r="E21" s="2">
-        <v>79.02687909699148</v>
+        <v>68.90445611220267</v>
       </c>
       <c r="F21" s="2">
-        <v>0.289986384080516</v>
+        <v>1.737823571099175</v>
       </c>
       <c r="G21" s="2">
-        <v>3.411481641353005</v>
+        <v>2.577279431670904</v>
       </c>
       <c r="H21" s="3">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B22" s="2">
-        <v>287.6914919003316</v>
+        <v>259.709311512347</v>
       </c>
       <c r="C22" s="2">
-        <v>45.85951106760237</v>
+        <v>39.46693604773945</v>
       </c>
       <c r="D22" s="2">
-        <v>168.6124217177565</v>
+        <v>116.7329225043021</v>
       </c>
       <c r="E22" s="2">
-        <v>68.90445611220267</v>
+        <v>100.732365763055</v>
       </c>
       <c r="F22" s="2">
-        <v>1.737823571099175</v>
+        <v>0.9525635796123081</v>
       </c>
       <c r="G22" s="2">
-        <v>2.577279431670904</v>
+        <v>1.824523617638172</v>
       </c>
       <c r="H22" s="3">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B23" s="2">
-        <v>259.709311512347</v>
+        <v>419.1311424101785</v>
       </c>
       <c r="C23" s="2">
-        <v>39.46693604773945</v>
+        <v>52.99363439333108</v>
       </c>
       <c r="D23" s="2">
-        <v>116.7329225043021</v>
+        <v>240.5802804369272</v>
       </c>
       <c r="E23" s="2">
-        <v>100.732365763055</v>
+        <v>94.28195947988786</v>
       </c>
       <c r="F23" s="2">
-        <v>0.9525635796123081</v>
+        <v>14.12164852566189</v>
       </c>
       <c r="G23" s="2">
-        <v>1.824523617638172</v>
+        <v>17.15361957437048</v>
       </c>
       <c r="H23" s="3">
-        <v>30</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B24" s="2">
-        <v>419.1311424101785</v>
+        <v>461.1700450927418</v>
       </c>
       <c r="C24" s="2">
-        <v>52.99363439333108</v>
+        <v>65.63128696233292</v>
       </c>
       <c r="D24" s="2">
-        <v>240.5802804369272</v>
+        <v>198.2021644964359</v>
       </c>
       <c r="E24" s="2">
-        <v>94.28195947988786</v>
+        <v>163.891013423966</v>
       </c>
       <c r="F24" s="2">
-        <v>14.12164852566189</v>
+        <v>9.302166808984346</v>
       </c>
       <c r="G24" s="2">
-        <v>17.15361957437048</v>
+        <v>24.14341340102255</v>
       </c>
       <c r="H24" s="3">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B25" s="2">
-        <v>461.1700450927418</v>
+        <v>448.6106826456667</v>
       </c>
       <c r="C25" s="2">
-        <v>65.63128696233292</v>
+        <v>61.99363578266568</v>
       </c>
       <c r="D25" s="2">
-        <v>198.2021644964359</v>
+        <v>187.4275651746192</v>
       </c>
       <c r="E25" s="2">
-        <v>163.891013423966</v>
+        <v>147.7754280505743</v>
       </c>
       <c r="F25" s="2">
-        <v>9.302166808984346</v>
+        <v>20.66326173659828</v>
       </c>
       <c r="G25" s="2">
-        <v>24.14341340102255</v>
+        <v>30.75079190120929</v>
       </c>
       <c r="H25" s="3">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B26" s="2">
-        <v>448.2830351440391</v>
+        <v>461.3554681082712</v>
       </c>
       <c r="C26" s="2">
-        <v>61.99363578266568</v>
+        <v>58.04814968847566</v>
       </c>
       <c r="D26" s="2">
-        <v>187.0999176729916</v>
+        <v>261.8794807807998</v>
       </c>
       <c r="E26" s="2">
-        <v>147.7754280505743</v>
+        <v>84.15174691715174</v>
       </c>
       <c r="F26" s="2">
-        <v>20.66326173659828</v>
+        <v>18.4203873065114</v>
       </c>
       <c r="G26" s="2">
-        <v>30.75079190120929</v>
+        <v>38.85570341533257</v>
       </c>
       <c r="H26" s="3">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B27" s="2">
-        <v>40.89102994323605</v>
+        <v>457.7958089138443</v>
       </c>
       <c r="C27" s="2">
-        <v>1.544781104193793</v>
+        <v>58.10913231266869</v>
       </c>
       <c r="D27" s="2">
-        <v>23.5155561520656</v>
+        <v>250.7107381860125</v>
       </c>
       <c r="E27" s="2">
-        <v>15.16887518746158</v>
+        <v>96.61882178998655</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>7.685050275590685</v>
       </c>
       <c r="G27" s="2">
-        <v>0.6618174995150831</v>
+        <v>44.67206634958585</v>
       </c>
       <c r="H27" s="3">
-        <v>25</v>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="1">
+        <v>46151</v>
+      </c>
+      <c r="B28" s="2">
+        <v>75.06731561634069</v>
+      </c>
+      <c r="C28" s="2">
+        <v>3.368639426165157</v>
+      </c>
+      <c r="D28" s="2">
+        <v>53.57014715886157</v>
+      </c>
+      <c r="E28" s="2">
+        <v>12.20326773086356</v>
+      </c>
+      <c r="F28" s="2">
+        <v>1.48381475660536</v>
+      </c>
+      <c r="G28" s="2">
+        <v>4.441446543845037</v>
+      </c>
+      <c r="H28" s="3">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1372,13 +1398,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEACD1EC-DFF5-4FE8-84BF-30D9AD7D265A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{899574BC-2C93-4D17-9BB9-96D199FD753F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1A679B9-829F-4B25-82D3-A34106DEAB0A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D89CBE3-2C13-4F7D-86CC-DE708B6A9D91}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55AB8A7F-2C0F-4314-90F9-A94054CB3FF7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9DFB400B-8B07-420A-A9D0-9F621F8885C8}"/>
 </file>
--- a/sea_productive.xlsx
+++ b/sea_productive.xlsx
@@ -109,8 +109,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:H28" totalsRowShown="0">
-  <autoFilter ref="A1:H28"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:H67" totalsRowShown="0">
+  <autoFilter ref="A1:H67"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Date_Converted" dataDxfId="0"/>
     <tableColumn id="2" name="Staff Hour (In Hours)" dataDxfId="1"/>
@@ -410,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -441,704 +441,1718 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="1">
-        <v>46125</v>
+        <v>46082</v>
       </c>
       <c r="B2" s="2">
-        <v>323.1610120714394</v>
+        <v>144.9462511898163</v>
       </c>
       <c r="C2" s="2">
-        <v>44.92686601665285</v>
+        <v>30.43381824033128</v>
       </c>
       <c r="D2" s="2">
-        <v>139.963458599324</v>
+        <v>65.83465752542847</v>
       </c>
       <c r="E2" s="2">
-        <v>130.2241021273575</v>
+        <v>43.46663293831878</v>
       </c>
       <c r="F2" s="2">
-        <v>2.248729739718967</v>
+        <v>3.882614976730612</v>
       </c>
       <c r="G2" s="2">
-        <v>5.797855588386042</v>
+        <v>1.328527509007189</v>
       </c>
       <c r="H2" s="3">
-        <v>41</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1">
-        <v>46126</v>
+        <v>46083</v>
       </c>
       <c r="B3" s="2">
-        <v>273.6781417201752</v>
+        <v>566.4589457685557</v>
       </c>
       <c r="C3" s="2">
-        <v>40.0413355584277</v>
+        <v>81.79042648090257</v>
       </c>
       <c r="D3" s="2">
-        <v>103.511928198818</v>
+        <v>236.4762368437068</v>
       </c>
       <c r="E3" s="2">
-        <v>117.2581249379449</v>
+        <v>212.7162072622528</v>
       </c>
       <c r="F3" s="2">
-        <v>7.059696611232228</v>
+        <v>4.730071461995442</v>
       </c>
       <c r="G3" s="2">
-        <v>5.807056413752337</v>
+        <v>30.74600371969812</v>
       </c>
       <c r="H3" s="3">
-        <v>31</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1">
-        <v>46127</v>
+        <v>46084</v>
       </c>
       <c r="B4" s="2">
-        <v>298.2914358288205</v>
+        <v>543.004154127551</v>
       </c>
       <c r="C4" s="2">
-        <v>47.16884657353162</v>
+        <v>75.21996667741074</v>
       </c>
       <c r="D4" s="2">
-        <v>119.399162515108</v>
+        <v>240.6100245056533</v>
       </c>
       <c r="E4" s="2">
-        <v>117.7262078565638</v>
+        <v>183.525896537929</v>
       </c>
       <c r="F4" s="2">
-        <v>12.05913498222828</v>
+        <v>13.87591089910931</v>
       </c>
       <c r="G4" s="2">
-        <v>1.938083901388778</v>
+        <v>29.77235550744873</v>
       </c>
       <c r="H4" s="3">
-        <v>33</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1">
-        <v>46128</v>
+        <v>46085</v>
       </c>
       <c r="B5" s="2">
-        <v>272.8079848140644</v>
+        <v>652.1374747542685</v>
       </c>
       <c r="C5" s="2">
-        <v>39.51949952118927</v>
+        <v>87.2538680783059</v>
       </c>
       <c r="D5" s="2">
-        <v>120.8711398820165</v>
+        <v>190.7186813584632</v>
       </c>
       <c r="E5" s="2">
-        <v>100.8949301929772</v>
+        <v>328.3260291573405</v>
       </c>
       <c r="F5" s="2">
-        <v>8.75364024238454</v>
+        <v>2.60505912039015</v>
       </c>
       <c r="G5" s="2">
-        <v>2.768774975496862</v>
+        <v>43.23383703976869</v>
       </c>
       <c r="H5" s="3">
-        <v>31</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1">
-        <v>46129</v>
+        <v>46086</v>
       </c>
       <c r="B6" s="2">
-        <v>309.9964914664471</v>
+        <v>552.5170689391487</v>
       </c>
       <c r="C6" s="2">
-        <v>43.6269740500715</v>
+        <v>72.99988324473301</v>
       </c>
       <c r="D6" s="2">
-        <v>133.4939823072486</v>
+        <v>139.0270460216515</v>
       </c>
       <c r="E6" s="2">
-        <v>108.2581891838058</v>
+        <v>287.3805466105044</v>
       </c>
       <c r="F6" s="2">
-        <v>17.38662732382615</v>
+        <v>2.225114700827334</v>
       </c>
       <c r="G6" s="2">
-        <v>7.230718601495028</v>
+        <v>50.88447836143249</v>
       </c>
       <c r="H6" s="3">
-        <v>35</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1">
-        <v>46130</v>
+        <v>46087</v>
       </c>
       <c r="B7" s="2">
-        <v>308.5183830143159</v>
+        <v>581.8307532002539</v>
       </c>
       <c r="C7" s="2">
-        <v>46.30651540866329</v>
+        <v>78.02865678081911</v>
       </c>
       <c r="D7" s="2">
-        <v>166.1900152229249</v>
+        <v>265.5542291173505</v>
       </c>
       <c r="E7" s="2">
-        <v>84.06776373089188</v>
+        <v>190.5495442012283</v>
       </c>
       <c r="F7" s="2">
-        <v>8.05202755873402</v>
+        <v>7.218209352791309</v>
       </c>
       <c r="G7" s="2">
-        <v>3.902061093101899</v>
+        <v>40.48011374806468</v>
       </c>
       <c r="H7" s="3">
-        <v>36</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1">
-        <v>46131</v>
+        <v>46088</v>
       </c>
       <c r="B8" s="2">
-        <v>249.7613502550125</v>
+        <v>554.1020983077575</v>
       </c>
       <c r="C8" s="2">
-        <v>31.50441224275364</v>
+        <v>73.29810811517967</v>
       </c>
       <c r="D8" s="2">
-        <v>89.46780061095126</v>
+        <v>312.294159649178</v>
       </c>
       <c r="E8" s="2">
-        <v>92.31769759105312</v>
+        <v>118.7588735390372</v>
       </c>
       <c r="F8" s="2">
-        <v>25.69309524112278</v>
+        <v>11.33450496256351</v>
       </c>
       <c r="G8" s="2">
-        <v>10.77834456913173</v>
+        <v>38.4164520417992</v>
       </c>
       <c r="H8" s="3">
-        <v>29</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1">
-        <v>46132</v>
+        <v>46089</v>
       </c>
       <c r="B9" s="2">
-        <v>288.824123178335</v>
+        <v>416.2632707354343</v>
       </c>
       <c r="C9" s="2">
-        <v>42.36635189480252</v>
+        <v>55.79421803508368</v>
       </c>
       <c r="D9" s="2">
-        <v>129.1712352487305</v>
+        <v>236.2747499374166</v>
       </c>
       <c r="E9" s="2">
-        <v>107.0414793449309</v>
+        <v>112.2282732929372</v>
       </c>
       <c r="F9" s="2">
-        <v>7.084813880191909</v>
+        <v>3.857798608144124</v>
       </c>
       <c r="G9" s="2">
-        <v>3.160242809679152</v>
+        <v>8.108230861852773</v>
       </c>
       <c r="H9" s="3">
-        <v>32</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1">
-        <v>46133</v>
+        <v>46090</v>
       </c>
       <c r="B10" s="2">
-        <v>260.8965785061465</v>
+        <v>337.6228754706349</v>
       </c>
       <c r="C10" s="2">
-        <v>40.30407802194357</v>
+        <v>49.07389021492666</v>
       </c>
       <c r="D10" s="2">
-        <v>151.8822429773853</v>
+        <v>202.5890308013144</v>
       </c>
       <c r="E10" s="2">
-        <v>57.75635954093602</v>
+        <v>62.05616933513846</v>
       </c>
       <c r="F10" s="2">
-        <v>8.765534364117517</v>
+        <v>3.03712106956376</v>
       </c>
       <c r="G10" s="2">
-        <v>2.188363601764043</v>
+        <v>20.86666404969163</v>
       </c>
       <c r="H10" s="3">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1">
-        <v>46134</v>
+        <v>46091</v>
       </c>
       <c r="B11" s="2">
-        <v>212.8907304516042</v>
+        <v>413.8341504297483</v>
       </c>
       <c r="C11" s="2">
-        <v>32.27424128419823</v>
+        <v>57.92299057775074</v>
       </c>
       <c r="D11" s="2">
-        <v>115.4994636634427</v>
+        <v>226.324775053836</v>
       </c>
       <c r="E11" s="2">
-        <v>48.54623563612501</v>
+        <v>96.5049233409183</v>
       </c>
       <c r="F11" s="2">
-        <v>14.17942682902018</v>
+        <v>6.998535788688395</v>
       </c>
       <c r="G11" s="2">
-        <v>2.391363038818041</v>
+        <v>26.0829256685549</v>
       </c>
       <c r="H11" s="3">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1">
-        <v>46135</v>
+        <v>46092</v>
       </c>
       <c r="B12" s="2">
-        <v>218.9280812006692</v>
+        <v>354.3850937351966</v>
       </c>
       <c r="C12" s="2">
-        <v>33.38276323295302</v>
+        <v>48.71531399448713</v>
       </c>
       <c r="D12" s="2">
-        <v>106.304737093548</v>
+        <v>194.2217908815408</v>
       </c>
       <c r="E12" s="2">
-        <v>64.60221893481082</v>
+        <v>89.42217878584181</v>
       </c>
       <c r="F12" s="2">
-        <v>13.08933916727702</v>
+        <v>9.195928547117445</v>
       </c>
       <c r="G12" s="2">
-        <v>1.549022772080368</v>
+        <v>12.82988152620939</v>
       </c>
       <c r="H12" s="3">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1">
-        <v>46136</v>
+        <v>46093</v>
       </c>
       <c r="B13" s="2">
-        <v>243.5352080432605</v>
+        <v>380.1324037595098</v>
       </c>
       <c r="C13" s="2">
-        <v>37.10335299352805</v>
+        <v>49.28357895612717</v>
       </c>
       <c r="D13" s="2">
-        <v>148.7460722376282</v>
+        <v>195.2196874099908</v>
       </c>
       <c r="E13" s="2">
-        <v>41.9854927673522</v>
+        <v>104.0880426873681</v>
       </c>
       <c r="F13" s="2">
-        <v>13.08109723409017</v>
+        <v>6.650347009433641</v>
       </c>
       <c r="G13" s="2">
-        <v>2.619192810661884</v>
+        <v>24.8907476965902</v>
       </c>
       <c r="H13" s="3">
-        <v>28</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1">
-        <v>46137</v>
+        <v>46094</v>
       </c>
       <c r="B14" s="2">
-        <v>295.5410275634233</v>
+        <v>450.403546915983</v>
       </c>
       <c r="C14" s="2">
-        <v>45.03800446298387</v>
+        <v>65.53895001998688</v>
       </c>
       <c r="D14" s="2">
-        <v>159.6257019741647</v>
+        <v>264.8115411872319</v>
       </c>
       <c r="E14" s="2">
-        <v>79.94608134516412</v>
+        <v>89.26595133310391</v>
       </c>
       <c r="F14" s="2">
-        <v>8.576289774576823</v>
+        <v>13.42511066390408</v>
       </c>
       <c r="G14" s="2">
-        <v>2.354950006533828</v>
+        <v>17.36199371175633</v>
       </c>
       <c r="H14" s="3">
-        <v>35</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1">
-        <v>46138</v>
+        <v>46095</v>
       </c>
       <c r="B15" s="2">
-        <v>281.2355133626817</v>
+        <v>450.3057350144028</v>
       </c>
       <c r="C15" s="2">
-        <v>42.84105554348893</v>
+        <v>67.1063798524936</v>
       </c>
       <c r="D15" s="2">
-        <v>97.31553551588621</v>
+        <v>329.8650853912341</v>
       </c>
       <c r="E15" s="2">
-        <v>133.8467120167447</v>
+        <v>33.15675891608983</v>
       </c>
       <c r="F15" s="2">
-        <v>2.745579155815972</v>
+        <v>7.979291646083196</v>
       </c>
       <c r="G15" s="2">
-        <v>4.486631130745842</v>
+        <v>12.19821920850211</v>
       </c>
       <c r="H15" s="3">
-        <v>33</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1">
-        <v>46139</v>
+        <v>46096</v>
       </c>
       <c r="B16" s="2">
-        <v>214.7356720573704</v>
+        <v>347.4651230987844</v>
       </c>
       <c r="C16" s="2">
-        <v>31.84751321550873</v>
+        <v>50.11702934110433</v>
       </c>
       <c r="D16" s="2">
-        <v>80.54385508432985</v>
+        <v>274.3363245417126</v>
       </c>
       <c r="E16" s="2">
-        <v>97.50572902141346</v>
+        <v>16.3684872214848</v>
       </c>
       <c r="F16" s="2">
-        <v>3.601089180840386</v>
+        <v>2.380206146240234</v>
       </c>
       <c r="G16" s="2">
-        <v>1.23748555527793</v>
+        <v>4.263075848242475</v>
       </c>
       <c r="H16" s="3">
-        <v>24</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1">
-        <v>46140</v>
+        <v>46097</v>
       </c>
       <c r="B17" s="2">
-        <v>188.3966501657499</v>
+        <v>375.244211665029</v>
       </c>
       <c r="C17" s="2">
-        <v>28.4410385724571</v>
+        <v>53.76107375714514</v>
       </c>
       <c r="D17" s="2">
-        <v>85.89948526518212</v>
+        <v>287.373537530503</v>
       </c>
       <c r="E17" s="2">
-        <v>68.54402510571811</v>
+        <v>19.10829601754745</v>
       </c>
       <c r="F17" s="2">
-        <v>4.423320109049479</v>
+        <v>8.712412985894415</v>
       </c>
       <c r="G17" s="2">
-        <v>1.088781113343106</v>
+        <v>6.288891373938984</v>
       </c>
       <c r="H17" s="3">
-        <v>21</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1">
-        <v>46141</v>
+        <v>46098</v>
       </c>
       <c r="B18" s="2">
-        <v>250.7527417366662</v>
+        <v>327.3673983494994</v>
       </c>
       <c r="C18" s="2">
-        <v>36.03463883413209</v>
+        <v>42.22733177123747</v>
       </c>
       <c r="D18" s="2">
-        <v>115.5841033623078</v>
+        <v>229.7642146909216</v>
       </c>
       <c r="E18" s="2">
-        <v>92.17480784644683</v>
+        <v>29.18151517025299</v>
       </c>
       <c r="F18" s="2">
-        <v>3.25470106654697</v>
+        <v>11.40589873439736</v>
       </c>
       <c r="G18" s="2">
-        <v>3.704490627232525</v>
+        <v>14.78843798269</v>
       </c>
       <c r="H18" s="3">
-        <v>28</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1">
-        <v>46142</v>
+        <v>46099</v>
       </c>
       <c r="B19" s="2">
-        <v>189.8929473854664</v>
+        <v>302.889306007544</v>
       </c>
       <c r="C19" s="2">
-        <v>29.90951245903969</v>
+        <v>40.26306771715482</v>
       </c>
       <c r="D19" s="2">
-        <v>109.241959625139</v>
+        <v>138.7392255803508</v>
       </c>
       <c r="E19" s="2">
-        <v>49.2553244445059</v>
+        <v>106.0459789887236</v>
       </c>
       <c r="F19" s="2">
-        <v>0.0004016666611035665</v>
+        <v>6.778992815117041</v>
       </c>
       <c r="G19" s="2">
-        <v>1.485749190120647</v>
+        <v>11.0620409061977</v>
       </c>
       <c r="H19" s="3">
-        <v>21</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1">
-        <v>46143</v>
+        <v>46100</v>
       </c>
       <c r="B20" s="2">
-        <v>236.9741027833154</v>
+        <v>290.5285264125032</v>
       </c>
       <c r="C20" s="2">
-        <v>35.30577249864737</v>
+        <v>40.59091454254256</v>
       </c>
       <c r="D20" s="2">
-        <v>118.939983162243</v>
+        <v>118.41086726056</v>
       </c>
       <c r="E20" s="2">
-        <v>79.02687909699148</v>
+        <v>112.6022851758699</v>
       </c>
       <c r="F20" s="2">
-        <v>0.289986384080516</v>
+        <v>8.285319689114889</v>
       </c>
       <c r="G20" s="2">
-        <v>3.411481641353005</v>
+        <v>10.63913974441588</v>
       </c>
       <c r="H20" s="3">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1">
-        <v>46144</v>
+        <v>46101</v>
       </c>
       <c r="B21" s="2">
-        <v>287.6914919003316</v>
+        <v>358.2330693519385</v>
       </c>
       <c r="C21" s="2">
-        <v>45.85951106760237</v>
+        <v>53.27758774060756</v>
       </c>
       <c r="D21" s="2">
-        <v>168.6124217177565</v>
+        <v>170.8602496395819</v>
       </c>
       <c r="E21" s="2">
-        <v>68.90445611220267</v>
+        <v>115.0255443816384</v>
       </c>
       <c r="F21" s="2">
-        <v>1.737823571099175</v>
+        <v>13.30206065036356</v>
       </c>
       <c r="G21" s="2">
-        <v>2.577279431670904</v>
+        <v>5.767626939747069</v>
       </c>
       <c r="H21" s="3">
-        <v>32</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1">
-        <v>46145</v>
+        <v>46102</v>
       </c>
       <c r="B22" s="2">
-        <v>259.709311512347</v>
+        <v>428.9770823672869</v>
       </c>
       <c r="C22" s="2">
-        <v>39.46693604773945</v>
+        <v>64.94292565504711</v>
       </c>
       <c r="D22" s="2">
-        <v>116.7329225043021</v>
+        <v>219.4155451001475</v>
       </c>
       <c r="E22" s="2">
-        <v>100.732365763055</v>
+        <v>133.4568338182486</v>
       </c>
       <c r="F22" s="2">
-        <v>0.9525635796123081</v>
+        <v>7.102920854356554</v>
       </c>
       <c r="G22" s="2">
-        <v>1.824523617638172</v>
+        <v>4.05885693948716</v>
       </c>
       <c r="H22" s="3">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1">
-        <v>46146</v>
+        <v>46103</v>
       </c>
       <c r="B23" s="2">
-        <v>419.1311424101785</v>
+        <v>373.2646733152812</v>
       </c>
       <c r="C23" s="2">
-        <v>52.99363439333108</v>
+        <v>55.25804654869768</v>
       </c>
       <c r="D23" s="2">
-        <v>240.5802804369272</v>
+        <v>249.5936668323423</v>
       </c>
       <c r="E23" s="2">
-        <v>94.28195947988786</v>
+        <v>61.10367273522334</v>
       </c>
       <c r="F23" s="2">
-        <v>14.12164852566189</v>
+        <v>3.551864988009135</v>
       </c>
       <c r="G23" s="2">
-        <v>17.15361957437048</v>
+        <v>3.757422211008767</v>
       </c>
       <c r="H23" s="3">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1">
-        <v>46147</v>
+        <v>46104</v>
       </c>
       <c r="B24" s="2">
-        <v>461.1700450927418</v>
+        <v>291.7639407892349</v>
       </c>
       <c r="C24" s="2">
-        <v>65.63128696233292</v>
+        <v>20.32542846687966</v>
       </c>
       <c r="D24" s="2">
-        <v>198.2021644964359</v>
+        <v>248.5747846650488</v>
       </c>
       <c r="E24" s="2">
-        <v>163.891013423966</v>
+        <v>12.3895491556906</v>
       </c>
       <c r="F24" s="2">
-        <v>9.302166808984346</v>
+        <v>7.138337923685709</v>
       </c>
       <c r="G24" s="2">
-        <v>24.14341340102255</v>
+        <v>3.335840577930212</v>
       </c>
       <c r="H24" s="3">
-        <v>48</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1">
-        <v>46148</v>
+        <v>46105</v>
       </c>
       <c r="B25" s="2">
-        <v>448.6106826456667</v>
+        <v>305.9541171467698</v>
       </c>
       <c r="C25" s="2">
-        <v>61.99363578266568</v>
+        <v>34.16942481944958</v>
       </c>
       <c r="D25" s="2">
-        <v>187.4275651746192</v>
+        <v>224.7904226703362</v>
       </c>
       <c r="E25" s="2">
-        <v>147.7754280505743</v>
+        <v>36.57108552712533</v>
       </c>
       <c r="F25" s="2">
-        <v>20.66326173659828</v>
+        <v>8.667285250557793</v>
       </c>
       <c r="G25" s="2">
-        <v>30.75079190120929</v>
+        <v>1.755898879300803</v>
       </c>
       <c r="H25" s="3">
-        <v>47</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1">
-        <v>46149</v>
+        <v>46106</v>
       </c>
       <c r="B26" s="2">
-        <v>461.3554681082712</v>
+        <v>343.2158147900986</v>
       </c>
       <c r="C26" s="2">
-        <v>58.04814968847566</v>
+        <v>37.79626579413812</v>
       </c>
       <c r="D26" s="2">
-        <v>261.8794807807998</v>
+        <v>165.18065914866</v>
       </c>
       <c r="E26" s="2">
-        <v>84.15174691715174</v>
+        <v>125.011963697109</v>
       </c>
       <c r="F26" s="2">
-        <v>18.4203873065114</v>
+        <v>4.895261433919271</v>
       </c>
       <c r="G26" s="2">
-        <v>38.85570341533257</v>
+        <v>10.3316647162723</v>
       </c>
       <c r="H26" s="3">
-        <v>48</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1">
-        <v>46150</v>
+        <v>46107</v>
       </c>
       <c r="B27" s="2">
-        <v>457.7958089138443</v>
+        <v>295.712606121772</v>
       </c>
       <c r="C27" s="2">
-        <v>58.10913231266869</v>
+        <v>29.96294723812077</v>
       </c>
       <c r="D27" s="2">
-        <v>250.7107381860125</v>
+        <v>151.3055243767467</v>
       </c>
       <c r="E27" s="2">
-        <v>96.61882178998655</v>
+        <v>99.84880426946199</v>
       </c>
       <c r="F27" s="2">
-        <v>7.685050275590685</v>
+        <v>13.13339579264323</v>
       </c>
       <c r="G27" s="2">
-        <v>44.67206634958585</v>
+        <v>1.461934444799295</v>
       </c>
       <c r="H27" s="3">
-        <v>47</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1">
+        <v>46108</v>
+      </c>
+      <c r="B28" s="2">
+        <v>332.5118910751678</v>
+      </c>
+      <c r="C28" s="2">
+        <v>49.92647149648931</v>
+      </c>
+      <c r="D28" s="2">
+        <v>143.0534553335442</v>
+      </c>
+      <c r="E28" s="2">
+        <v>127.5189474205259</v>
+      </c>
+      <c r="F28" s="2">
+        <v>9.410011845595307</v>
+      </c>
+      <c r="G28" s="2">
+        <v>2.603004979013155</v>
+      </c>
+      <c r="H28" s="3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="1">
+        <v>46109</v>
+      </c>
+      <c r="B29" s="2">
+        <v>402.7783231851968</v>
+      </c>
+      <c r="C29" s="2">
+        <v>58.55442659868135</v>
+      </c>
+      <c r="D29" s="2">
+        <v>150.5436717197488</v>
+      </c>
+      <c r="E29" s="2">
+        <v>187.5175101825885</v>
+      </c>
+      <c r="F29" s="2">
+        <v>2.802114723192321</v>
+      </c>
+      <c r="G29" s="2">
+        <v>3.360599960985904</v>
+      </c>
+      <c r="H29" s="3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="1">
+        <v>46110</v>
+      </c>
+      <c r="B30" s="2">
+        <v>313.8764589604311</v>
+      </c>
+      <c r="C30" s="2">
+        <v>45.09727938546074</v>
+      </c>
+      <c r="D30" s="2">
+        <v>138.2112484407435</v>
+      </c>
+      <c r="E30" s="2">
+        <v>125.7445075329952</v>
+      </c>
+      <c r="F30" s="2">
+        <v>2.103562786314222</v>
+      </c>
+      <c r="G30" s="2">
+        <v>2.719860814917419</v>
+      </c>
+      <c r="H30" s="3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="1">
+        <v>46111</v>
+      </c>
+      <c r="B31" s="2">
+        <v>322.4642883801957</v>
+      </c>
+      <c r="C31" s="2">
+        <v>49.43798138876756</v>
+      </c>
+      <c r="D31" s="2">
+        <v>139.0268761372566</v>
+      </c>
+      <c r="E31" s="2">
+        <v>127.2150895330227</v>
+      </c>
+      <c r="F31" s="2">
+        <v>4.576561868720584</v>
+      </c>
+      <c r="G31" s="2">
+        <v>2.207779452428221</v>
+      </c>
+      <c r="H31" s="3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="1">
+        <v>46112</v>
+      </c>
+      <c r="B32" s="2">
+        <v>303.7321328057344</v>
+      </c>
+      <c r="C32" s="2">
+        <v>40.37584235525794</v>
+      </c>
+      <c r="D32" s="2">
+        <v>117.6803280255028</v>
+      </c>
+      <c r="E32" s="2">
+        <v>116.1597747703724</v>
+      </c>
+      <c r="F32" s="2">
+        <v>2.950167168511285</v>
+      </c>
+      <c r="G32" s="2">
+        <v>26.56602048608992</v>
+      </c>
+      <c r="H32" s="3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B33" s="2">
+        <v>319.3030338970054</v>
+      </c>
+      <c r="C33" s="2">
+        <v>46.25189561208089</v>
+      </c>
+      <c r="D33" s="2">
+        <v>144.7031512825646</v>
+      </c>
+      <c r="E33" s="2">
+        <v>122.4700969688015</v>
+      </c>
+      <c r="F33" s="2">
+        <v>1.583625554177496</v>
+      </c>
+      <c r="G33" s="2">
+        <v>4.294264479380929</v>
+      </c>
+      <c r="H33" s="3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B34" s="2">
+        <v>249.3237649363755</v>
+      </c>
+      <c r="C34" s="2">
+        <v>34.14573048230675</v>
+      </c>
+      <c r="D34" s="2">
+        <v>131.3198983922829</v>
+      </c>
+      <c r="E34" s="2">
+        <v>74.81185791517298</v>
+      </c>
+      <c r="F34" s="2">
+        <v>5.118818070226245</v>
+      </c>
+      <c r="G34" s="2">
+        <v>3.92746007638673</v>
+      </c>
+      <c r="H34" s="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="1">
+        <v>46115</v>
+      </c>
+      <c r="B35" s="2">
+        <v>268.9178836139819</v>
+      </c>
+      <c r="C35" s="2">
+        <v>37.51144920309385</v>
+      </c>
+      <c r="D35" s="2">
+        <v>135.4633324013651</v>
+      </c>
+      <c r="E35" s="2">
+        <v>90.26212058136447</v>
+      </c>
+      <c r="F35" s="2">
+        <v>3.177322836981879</v>
+      </c>
+      <c r="G35" s="2">
+        <v>2.503658591176694</v>
+      </c>
+      <c r="H35" s="3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="1">
+        <v>46116</v>
+      </c>
+      <c r="B36" s="2">
+        <v>303.6367755822258</v>
+      </c>
+      <c r="C36" s="2">
+        <v>44.93887431705991</v>
+      </c>
+      <c r="D36" s="2">
+        <v>146.1341548401697</v>
+      </c>
+      <c r="E36" s="2">
+        <v>107.8033502957473</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0.3177908325195313</v>
+      </c>
+      <c r="G36" s="2">
+        <v>4.442605296729339</v>
+      </c>
+      <c r="H36" s="3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="1">
+        <v>46117</v>
+      </c>
+      <c r="B37" s="2">
+        <v>179.7793454074818</v>
+      </c>
+      <c r="C37" s="2">
+        <v>24.8302235065235</v>
+      </c>
+      <c r="D37" s="2">
+        <v>67.26173536416557</v>
+      </c>
+      <c r="E37" s="2">
+        <v>84.27680431906548</v>
+      </c>
+      <c r="F37" s="2">
+        <v>0.7290197245279948</v>
+      </c>
+      <c r="G37" s="2">
+        <v>2.681562493199276</v>
+      </c>
+      <c r="H37" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B38" s="2">
+        <v>323.1610120714394</v>
+      </c>
+      <c r="C38" s="2">
+        <v>44.92686601665285</v>
+      </c>
+      <c r="D38" s="2">
+        <v>139.963458599324</v>
+      </c>
+      <c r="E38" s="2">
+        <v>130.2241021273575</v>
+      </c>
+      <c r="F38" s="2">
+        <v>2.248729739718967</v>
+      </c>
+      <c r="G38" s="2">
+        <v>5.797855588386042</v>
+      </c>
+      <c r="H38" s="3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B39" s="2">
+        <v>273.6781417201752</v>
+      </c>
+      <c r="C39" s="2">
+        <v>40.0413355584277</v>
+      </c>
+      <c r="D39" s="2">
+        <v>103.511928198818</v>
+      </c>
+      <c r="E39" s="2">
+        <v>117.2581249379449</v>
+      </c>
+      <c r="F39" s="2">
+        <v>7.059696611232228</v>
+      </c>
+      <c r="G39" s="2">
+        <v>5.807056413752337</v>
+      </c>
+      <c r="H39" s="3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B40" s="2">
+        <v>298.2914358288205</v>
+      </c>
+      <c r="C40" s="2">
+        <v>47.16884657353162</v>
+      </c>
+      <c r="D40" s="2">
+        <v>119.399162515108</v>
+      </c>
+      <c r="E40" s="2">
+        <v>117.7262078565638</v>
+      </c>
+      <c r="F40" s="2">
+        <v>12.05913498222828</v>
+      </c>
+      <c r="G40" s="2">
+        <v>1.938083901388778</v>
+      </c>
+      <c r="H40" s="3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B41" s="2">
+        <v>272.8079848140644</v>
+      </c>
+      <c r="C41" s="2">
+        <v>39.51949952118927</v>
+      </c>
+      <c r="D41" s="2">
+        <v>120.8711398820165</v>
+      </c>
+      <c r="E41" s="2">
+        <v>100.8949301929772</v>
+      </c>
+      <c r="F41" s="2">
+        <v>8.75364024238454</v>
+      </c>
+      <c r="G41" s="2">
+        <v>2.768774975496862</v>
+      </c>
+      <c r="H41" s="3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" s="1">
+        <v>46129</v>
+      </c>
+      <c r="B42" s="2">
+        <v>309.9964914664471</v>
+      </c>
+      <c r="C42" s="2">
+        <v>43.6269740500715</v>
+      </c>
+      <c r="D42" s="2">
+        <v>133.4939823072486</v>
+      </c>
+      <c r="E42" s="2">
+        <v>108.2581891838058</v>
+      </c>
+      <c r="F42" s="2">
+        <v>17.38662732382615</v>
+      </c>
+      <c r="G42" s="2">
+        <v>7.230718601495028</v>
+      </c>
+      <c r="H42" s="3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" s="1">
+        <v>46130</v>
+      </c>
+      <c r="B43" s="2">
+        <v>308.5183830143159</v>
+      </c>
+      <c r="C43" s="2">
+        <v>46.30651540866329</v>
+      </c>
+      <c r="D43" s="2">
+        <v>166.1900152229249</v>
+      </c>
+      <c r="E43" s="2">
+        <v>84.06776373089188</v>
+      </c>
+      <c r="F43" s="2">
+        <v>8.05202755873402</v>
+      </c>
+      <c r="G43" s="2">
+        <v>3.902061093101899</v>
+      </c>
+      <c r="H43" s="3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="1">
+        <v>46131</v>
+      </c>
+      <c r="B44" s="2">
+        <v>249.7613502550125</v>
+      </c>
+      <c r="C44" s="2">
+        <v>31.50441224275364</v>
+      </c>
+      <c r="D44" s="2">
+        <v>89.46780061095126</v>
+      </c>
+      <c r="E44" s="2">
+        <v>92.31769759105312</v>
+      </c>
+      <c r="F44" s="2">
+        <v>25.69309524112278</v>
+      </c>
+      <c r="G44" s="2">
+        <v>10.77834456913173</v>
+      </c>
+      <c r="H44" s="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" s="1">
+        <v>46132</v>
+      </c>
+      <c r="B45" s="2">
+        <v>288.824123178335</v>
+      </c>
+      <c r="C45" s="2">
+        <v>42.36635189480252</v>
+      </c>
+      <c r="D45" s="2">
+        <v>129.1712352487305</v>
+      </c>
+      <c r="E45" s="2">
+        <v>107.0414793449309</v>
+      </c>
+      <c r="F45" s="2">
+        <v>7.084813880191909</v>
+      </c>
+      <c r="G45" s="2">
+        <v>3.160242809679152</v>
+      </c>
+      <c r="H45" s="3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="1">
+        <v>46133</v>
+      </c>
+      <c r="B46" s="2">
+        <v>260.8965785061465</v>
+      </c>
+      <c r="C46" s="2">
+        <v>40.30407802194357</v>
+      </c>
+      <c r="D46" s="2">
+        <v>151.8822429773853</v>
+      </c>
+      <c r="E46" s="2">
+        <v>57.75635954093602</v>
+      </c>
+      <c r="F46" s="2">
+        <v>8.765534364117517</v>
+      </c>
+      <c r="G46" s="2">
+        <v>2.188363601764043</v>
+      </c>
+      <c r="H46" s="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B47" s="2">
+        <v>212.8907304516042</v>
+      </c>
+      <c r="C47" s="2">
+        <v>32.27424128419823</v>
+      </c>
+      <c r="D47" s="2">
+        <v>115.4994636634427</v>
+      </c>
+      <c r="E47" s="2">
+        <v>48.54623563612501</v>
+      </c>
+      <c r="F47" s="2">
+        <v>14.17942682902018</v>
+      </c>
+      <c r="G47" s="2">
+        <v>2.391363038818041</v>
+      </c>
+      <c r="H47" s="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B48" s="2">
+        <v>218.9280812006692</v>
+      </c>
+      <c r="C48" s="2">
+        <v>33.38276323295302</v>
+      </c>
+      <c r="D48" s="2">
+        <v>106.304737093548</v>
+      </c>
+      <c r="E48" s="2">
+        <v>64.60221893481082</v>
+      </c>
+      <c r="F48" s="2">
+        <v>13.08933916727702</v>
+      </c>
+      <c r="G48" s="2">
+        <v>1.549022772080368</v>
+      </c>
+      <c r="H48" s="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" s="1">
+        <v>46136</v>
+      </c>
+      <c r="B49" s="2">
+        <v>243.5352080432605</v>
+      </c>
+      <c r="C49" s="2">
+        <v>37.10335299352805</v>
+      </c>
+      <c r="D49" s="2">
+        <v>148.7460722376282</v>
+      </c>
+      <c r="E49" s="2">
+        <v>41.9854927673522</v>
+      </c>
+      <c r="F49" s="2">
+        <v>13.08109723409017</v>
+      </c>
+      <c r="G49" s="2">
+        <v>2.619192810661884</v>
+      </c>
+      <c r="H49" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" s="1">
+        <v>46137</v>
+      </c>
+      <c r="B50" s="2">
+        <v>295.5410275634233</v>
+      </c>
+      <c r="C50" s="2">
+        <v>45.03800446298387</v>
+      </c>
+      <c r="D50" s="2">
+        <v>159.6257019741647</v>
+      </c>
+      <c r="E50" s="2">
+        <v>79.94608134516412</v>
+      </c>
+      <c r="F50" s="2">
+        <v>8.576289774576823</v>
+      </c>
+      <c r="G50" s="2">
+        <v>2.354950006533828</v>
+      </c>
+      <c r="H50" s="3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="1">
+        <v>46138</v>
+      </c>
+      <c r="B51" s="2">
+        <v>281.2355133626817</v>
+      </c>
+      <c r="C51" s="2">
+        <v>42.84105554348893</v>
+      </c>
+      <c r="D51" s="2">
+        <v>97.31553551588621</v>
+      </c>
+      <c r="E51" s="2">
+        <v>133.8467120167447</v>
+      </c>
+      <c r="F51" s="2">
+        <v>2.745579155815972</v>
+      </c>
+      <c r="G51" s="2">
+        <v>4.486631130745842</v>
+      </c>
+      <c r="H51" s="3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="1">
+        <v>46139</v>
+      </c>
+      <c r="B52" s="2">
+        <v>214.7356720573704</v>
+      </c>
+      <c r="C52" s="2">
+        <v>31.84751321550873</v>
+      </c>
+      <c r="D52" s="2">
+        <v>80.54385508432985</v>
+      </c>
+      <c r="E52" s="2">
+        <v>97.50572902141346</v>
+      </c>
+      <c r="F52" s="2">
+        <v>3.601089180840386</v>
+      </c>
+      <c r="G52" s="2">
+        <v>1.23748555527793</v>
+      </c>
+      <c r="H52" s="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" s="1">
+        <v>46140</v>
+      </c>
+      <c r="B53" s="2">
+        <v>188.3966501657499</v>
+      </c>
+      <c r="C53" s="2">
+        <v>28.4410385724571</v>
+      </c>
+      <c r="D53" s="2">
+        <v>85.89948526518212</v>
+      </c>
+      <c r="E53" s="2">
+        <v>68.54402510571811</v>
+      </c>
+      <c r="F53" s="2">
+        <v>4.423320109049479</v>
+      </c>
+      <c r="G53" s="2">
+        <v>1.088781113343106</v>
+      </c>
+      <c r="H53" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" s="1">
+        <v>46141</v>
+      </c>
+      <c r="B54" s="2">
+        <v>250.7527417366662</v>
+      </c>
+      <c r="C54" s="2">
+        <v>36.03463883413209</v>
+      </c>
+      <c r="D54" s="2">
+        <v>115.5841033623078</v>
+      </c>
+      <c r="E54" s="2">
+        <v>92.17480784644683</v>
+      </c>
+      <c r="F54" s="2">
+        <v>3.25470106654697</v>
+      </c>
+      <c r="G54" s="2">
+        <v>3.704490627232525</v>
+      </c>
+      <c r="H54" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" s="1">
+        <v>46142</v>
+      </c>
+      <c r="B55" s="2">
+        <v>189.8929473854664</v>
+      </c>
+      <c r="C55" s="2">
+        <v>29.90951245903969</v>
+      </c>
+      <c r="D55" s="2">
+        <v>109.241959625139</v>
+      </c>
+      <c r="E55" s="2">
+        <v>49.2553244445059</v>
+      </c>
+      <c r="F55" s="2">
+        <v>0.0004016666611035665</v>
+      </c>
+      <c r="G55" s="2">
+        <v>1.485749190120647</v>
+      </c>
+      <c r="H55" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" s="1">
+        <v>46143</v>
+      </c>
+      <c r="B56" s="2">
+        <v>236.9741027833154</v>
+      </c>
+      <c r="C56" s="2">
+        <v>35.30577249864737</v>
+      </c>
+      <c r="D56" s="2">
+        <v>118.939983162243</v>
+      </c>
+      <c r="E56" s="2">
+        <v>79.02687909699148</v>
+      </c>
+      <c r="F56" s="2">
+        <v>0.289986384080516</v>
+      </c>
+      <c r="G56" s="2">
+        <v>3.411481641353005</v>
+      </c>
+      <c r="H56" s="3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" s="1">
+        <v>46144</v>
+      </c>
+      <c r="B57" s="2">
+        <v>287.6914919003316</v>
+      </c>
+      <c r="C57" s="2">
+        <v>45.85951106760237</v>
+      </c>
+      <c r="D57" s="2">
+        <v>168.6124217177565</v>
+      </c>
+      <c r="E57" s="2">
+        <v>68.90445611220267</v>
+      </c>
+      <c r="F57" s="2">
+        <v>1.737823571099175</v>
+      </c>
+      <c r="G57" s="2">
+        <v>2.577279431670904</v>
+      </c>
+      <c r="H57" s="3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" s="1">
+        <v>46145</v>
+      </c>
+      <c r="B58" s="2">
+        <v>259.709311512347</v>
+      </c>
+      <c r="C58" s="2">
+        <v>39.46693604773945</v>
+      </c>
+      <c r="D58" s="2">
+        <v>116.7329225043021</v>
+      </c>
+      <c r="E58" s="2">
+        <v>100.732365763055</v>
+      </c>
+      <c r="F58" s="2">
+        <v>0.9525635796123081</v>
+      </c>
+      <c r="G58" s="2">
+        <v>1.824523617638172</v>
+      </c>
+      <c r="H58" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" s="1">
+        <v>46146</v>
+      </c>
+      <c r="B59" s="2">
+        <v>419.1311424101785</v>
+      </c>
+      <c r="C59" s="2">
+        <v>52.99363439333108</v>
+      </c>
+      <c r="D59" s="2">
+        <v>240.5802804369272</v>
+      </c>
+      <c r="E59" s="2">
+        <v>94.28195947988786</v>
+      </c>
+      <c r="F59" s="2">
+        <v>14.12164852566189</v>
+      </c>
+      <c r="G59" s="2">
+        <v>17.15361957437048</v>
+      </c>
+      <c r="H59" s="3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" s="1">
+        <v>46147</v>
+      </c>
+      <c r="B60" s="2">
+        <v>461.1700450927418</v>
+      </c>
+      <c r="C60" s="2">
+        <v>65.63128696233292</v>
+      </c>
+      <c r="D60" s="2">
+        <v>198.2021644964359</v>
+      </c>
+      <c r="E60" s="2">
+        <v>163.891013423966</v>
+      </c>
+      <c r="F60" s="2">
+        <v>9.302166808984346</v>
+      </c>
+      <c r="G60" s="2">
+        <v>24.14341340102255</v>
+      </c>
+      <c r="H60" s="3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B61" s="2">
+        <v>448.6106826456667</v>
+      </c>
+      <c r="C61" s="2">
+        <v>61.99363578266568</v>
+      </c>
+      <c r="D61" s="2">
+        <v>187.4275651746192</v>
+      </c>
+      <c r="E61" s="2">
+        <v>147.7754280505743</v>
+      </c>
+      <c r="F61" s="2">
+        <v>20.66326173659828</v>
+      </c>
+      <c r="G61" s="2">
+        <v>30.75079190120929</v>
+      </c>
+      <c r="H61" s="3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B62" s="2">
+        <v>461.3554681082712</v>
+      </c>
+      <c r="C62" s="2">
+        <v>58.04814968847566</v>
+      </c>
+      <c r="D62" s="2">
+        <v>261.8794807807998</v>
+      </c>
+      <c r="E62" s="2">
+        <v>84.15174691715174</v>
+      </c>
+      <c r="F62" s="2">
+        <v>18.4203873065114</v>
+      </c>
+      <c r="G62" s="2">
+        <v>38.85570341533257</v>
+      </c>
+      <c r="H62" s="3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B63" s="2">
+        <v>457.7958089138443</v>
+      </c>
+      <c r="C63" s="2">
+        <v>58.10913231266869</v>
+      </c>
+      <c r="D63" s="2">
+        <v>250.7107381860125</v>
+      </c>
+      <c r="E63" s="2">
+        <v>96.61882178998655</v>
+      </c>
+      <c r="F63" s="2">
+        <v>7.685050275590685</v>
+      </c>
+      <c r="G63" s="2">
+        <v>44.67206634958585</v>
+      </c>
+      <c r="H63" s="3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" s="1">
         <v>46151</v>
       </c>
-      <c r="B28" s="2">
-        <v>75.06731561634069</v>
-      </c>
-      <c r="C28" s="2">
-        <v>3.368639426165157</v>
-      </c>
-      <c r="D28" s="2">
-        <v>53.57014715886157</v>
-      </c>
-      <c r="E28" s="2">
-        <v>12.20326773086356</v>
-      </c>
-      <c r="F28" s="2">
-        <v>1.48381475660536</v>
-      </c>
-      <c r="G28" s="2">
-        <v>4.441446543845037</v>
-      </c>
-      <c r="H28" s="3">
-        <v>31</v>
+      <c r="B64" s="2">
+        <v>395.0818778126832</v>
+      </c>
+      <c r="C64" s="2">
+        <v>54.21395854933395</v>
+      </c>
+      <c r="D64" s="2">
+        <v>222.4328021572411</v>
+      </c>
+      <c r="E64" s="2">
+        <v>92.66349213160989</v>
+      </c>
+      <c r="F64" s="2">
+        <v>5.081649458673265</v>
+      </c>
+      <c r="G64" s="2">
+        <v>20.68997551582495</v>
+      </c>
+      <c r="H64" s="3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" s="1">
+        <v>46152</v>
+      </c>
+      <c r="B65" s="2">
+        <v>361.5600983176836</v>
+      </c>
+      <c r="C65" s="2">
+        <v>40.06949561970102</v>
+      </c>
+      <c r="D65" s="2">
+        <v>186.7334606014937</v>
+      </c>
+      <c r="E65" s="2">
+        <v>104.1084193469418</v>
+      </c>
+      <c r="F65" s="2">
+        <v>0.5201874796549479</v>
+      </c>
+      <c r="G65" s="2">
+        <v>30.12853526989205</v>
+      </c>
+      <c r="H65" s="3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B66" s="2">
+        <v>413.562904932814</v>
+      </c>
+      <c r="C66" s="2">
+        <v>54.72469190753169</v>
+      </c>
+      <c r="D66" s="2">
+        <v>222.7241447033774</v>
+      </c>
+      <c r="E66" s="2">
+        <v>96.85184966677593</v>
+      </c>
+      <c r="F66" s="2">
+        <v>6.049973821640014</v>
+      </c>
+      <c r="G66" s="2">
+        <v>33.21224483348895</v>
+      </c>
+      <c r="H66" s="3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B67" s="2">
+        <v>19.42627348790152</v>
+      </c>
+      <c r="C67" s="2">
+        <v>1.07549778646893</v>
+      </c>
+      <c r="D67" s="2">
+        <v>11.33214605686565</v>
+      </c>
+      <c r="E67" s="2">
+        <v>5.68166633390718</v>
+      </c>
+      <c r="F67" s="2">
+        <v>0</v>
+      </c>
+      <c r="G67" s="2">
+        <v>1.33696331065976</v>
+      </c>
+      <c r="H67" s="3">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -1382,10 +2396,10 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <TaxCatchAll xmlns="0b1f5c80-8d6b-48f0-84f6-ea4845a21fc7" xsi:nil="true"/>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="98e5d340-1856-43f4-9776-f0c5fe464598">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="0b1f5c80-8d6b-48f0-84f6-ea4845a21fc7" xsi:nil="true"/>
     <Owner xmlns="98e5d340-1856-43f4-9776-f0c5fe464598">
       <UserInfo>
         <DisplayName/>
@@ -1398,13 +2412,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{899574BC-2C93-4D17-9BB9-96D199FD753F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A88F5B1-E88D-4B0C-A3B2-1EB931F7CB6A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D89CBE3-2C13-4F7D-86CC-DE708B6A9D91}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92323C12-1AF1-4716-8B15-FBF6AAE5516E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9DFB400B-8B07-420A-A9D0-9F621F8885C8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{901E97D0-7DE8-4064-B144-15137C0CF1C8}"/>
 </file>
--- a/sea_productive.xlsx
+++ b/sea_productive.xlsx
@@ -109,8 +109,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:H20" totalsRowShown="0">
-  <autoFilter ref="A1:H20"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:H133" totalsRowShown="0">
+  <autoFilter ref="A1:H133"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Date_Converted" dataDxfId="0"/>
     <tableColumn id="2" name="Staff Hour (In Hours)" dataDxfId="1"/>
@@ -410,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H133"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -441,496 +441,3434 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="1">
-        <v>46138</v>
+        <v>46027</v>
       </c>
       <c r="B2" s="2">
-        <v>67.48906637716624</v>
+        <v>870.3592249999955</v>
       </c>
       <c r="C2" s="2">
-        <v>13.72840667823951</v>
+        <v>109.3243527777779</v>
       </c>
       <c r="D2" s="2">
-        <v>23.58170555243889</v>
+        <v>485.6154972222233</v>
       </c>
       <c r="E2" s="2">
-        <v>29.79695525358121</v>
+        <v>198.6749333333332</v>
       </c>
       <c r="F2" s="2">
-        <v>0</v>
+        <v>6.482991666666666</v>
       </c>
       <c r="G2" s="2">
-        <v>0.3819988929066393</v>
+        <v>70.26145000000001</v>
       </c>
       <c r="H2" s="3">
-        <v>14</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1">
-        <v>46139</v>
+        <v>46028</v>
       </c>
       <c r="B3" s="2">
-        <v>214.7356720573704</v>
+        <v>689.8482027777785</v>
       </c>
       <c r="C3" s="2">
-        <v>31.84751321550873</v>
+        <v>87.08334722222217</v>
       </c>
       <c r="D3" s="2">
-        <v>80.54385508432985</v>
+        <v>327.4935416666669</v>
       </c>
       <c r="E3" s="2">
-        <v>97.50572902141346</v>
+        <v>199.0685111111113</v>
       </c>
       <c r="F3" s="2">
-        <v>3.601089180840386</v>
+        <v>18.61434166666667</v>
       </c>
       <c r="G3" s="2">
-        <v>1.23748555527793</v>
+        <v>57.58846111111109</v>
       </c>
       <c r="H3" s="3">
-        <v>24</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1">
-        <v>46140</v>
+        <v>46029</v>
       </c>
       <c r="B4" s="2">
-        <v>188.3966501657499</v>
+        <v>609.7531611111106</v>
       </c>
       <c r="C4" s="2">
-        <v>28.4410385724571</v>
+        <v>73.93671666666667</v>
       </c>
       <c r="D4" s="2">
-        <v>85.89948526518212</v>
+        <v>279.0145249999997</v>
       </c>
       <c r="E4" s="2">
-        <v>68.54402510571811</v>
+        <v>198.93525</v>
       </c>
       <c r="F4" s="2">
-        <v>4.423320109049479</v>
+        <v>14.85945277777778</v>
       </c>
       <c r="G4" s="2">
-        <v>1.088781113343106</v>
+        <v>43.0072166666667</v>
       </c>
       <c r="H4" s="3">
-        <v>21</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1">
-        <v>46141</v>
+        <v>46030</v>
       </c>
       <c r="B5" s="2">
-        <v>250.7527417366662</v>
+        <v>703.7190444444441</v>
       </c>
       <c r="C5" s="2">
-        <v>36.03463883413209</v>
+        <v>89.506675</v>
       </c>
       <c r="D5" s="2">
-        <v>115.5841033623078</v>
+        <v>319.1267166666676</v>
       </c>
       <c r="E5" s="2">
-        <v>92.17480784644683</v>
+        <v>205.2799055555557</v>
       </c>
       <c r="F5" s="2">
-        <v>3.25470106654697</v>
+        <v>9.191122222222223</v>
       </c>
       <c r="G5" s="2">
-        <v>3.704490627232525</v>
+        <v>80.61462499999995</v>
       </c>
       <c r="H5" s="3">
-        <v>28</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1">
-        <v>46142</v>
+        <v>46031</v>
       </c>
       <c r="B6" s="2">
-        <v>189.8929473854664</v>
+        <v>802.1030472222202</v>
       </c>
       <c r="C6" s="2">
-        <v>29.90951245903969</v>
+        <v>102.3932361111112</v>
       </c>
       <c r="D6" s="2">
-        <v>109.241959625139</v>
+        <v>283.2461750000002</v>
       </c>
       <c r="E6" s="2">
-        <v>49.2553244445059</v>
+        <v>322.0658972222225</v>
       </c>
       <c r="F6" s="2">
-        <v>0.0004016666611035665</v>
+        <v>7.614477777777776</v>
       </c>
       <c r="G6" s="2">
-        <v>1.485749190120647</v>
+        <v>86.7832611111111</v>
       </c>
       <c r="H6" s="3">
-        <v>21</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1">
-        <v>46143</v>
+        <v>46032</v>
       </c>
       <c r="B7" s="2">
-        <v>236.9741027833154</v>
+        <v>575.9244805555536</v>
       </c>
       <c r="C7" s="2">
-        <v>35.30577249864737</v>
+        <v>78.55605833333335</v>
       </c>
       <c r="D7" s="2">
-        <v>118.939983162243</v>
+        <v>225.4150916666671</v>
       </c>
       <c r="E7" s="2">
-        <v>79.02687909699148</v>
+        <v>241.2717472222219</v>
       </c>
       <c r="F7" s="2">
-        <v>0.289986384080516</v>
+        <v>4.460294444444444</v>
       </c>
       <c r="G7" s="2">
-        <v>3.411481641353005</v>
+        <v>26.22128888888892</v>
       </c>
       <c r="H7" s="3">
-        <v>26</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1">
-        <v>46144</v>
+        <v>46033</v>
       </c>
       <c r="B8" s="2">
-        <v>287.6914919003316</v>
+        <v>478.6889495968523</v>
       </c>
       <c r="C8" s="2">
-        <v>45.85951106760237</v>
+        <v>63.17197036028571</v>
       </c>
       <c r="D8" s="2">
-        <v>168.6124217177565</v>
+        <v>174.9906012168871</v>
       </c>
       <c r="E8" s="2">
-        <v>68.90445611220267</v>
+        <v>215.3876980227485</v>
       </c>
       <c r="F8" s="2">
-        <v>1.737823571099175</v>
+        <v>5.564221670871311</v>
       </c>
       <c r="G8" s="2">
-        <v>2.577279431670904</v>
+        <v>19.57445832605975</v>
       </c>
       <c r="H8" s="3">
-        <v>32</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1">
-        <v>46145</v>
+        <v>46034</v>
       </c>
       <c r="B9" s="2">
-        <v>259.709311512347</v>
+        <v>538.8706459594797</v>
       </c>
       <c r="C9" s="2">
-        <v>39.46693604773945</v>
+        <v>81.25861043076549</v>
       </c>
       <c r="D9" s="2">
-        <v>116.7329225043021</v>
+        <v>273.8099037591037</v>
       </c>
       <c r="E9" s="2">
-        <v>100.732365763055</v>
+        <v>170.8118203727901</v>
       </c>
       <c r="F9" s="2">
-        <v>0.9525635796123081</v>
+        <v>2.890012762049834</v>
       </c>
       <c r="G9" s="2">
-        <v>1.824523617638172</v>
+        <v>10.10029863477064</v>
       </c>
       <c r="H9" s="3">
-        <v>30</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1">
-        <v>46146</v>
+        <v>46035</v>
       </c>
       <c r="B10" s="2">
-        <v>419.1311424101785</v>
+        <v>761.5847269845382</v>
       </c>
       <c r="C10" s="2">
-        <v>52.99363439333108</v>
+        <v>108.65839220398</v>
       </c>
       <c r="D10" s="2">
-        <v>240.5802804369272</v>
+        <v>301.4864798627876</v>
       </c>
       <c r="E10" s="2">
-        <v>94.28195947988786</v>
+        <v>297.5387565107478</v>
       </c>
       <c r="F10" s="2">
-        <v>14.12164852566189</v>
+        <v>13.35832641177707</v>
       </c>
       <c r="G10" s="2">
-        <v>17.15361957437048</v>
+        <v>40.54277199524558</v>
       </c>
       <c r="H10" s="3">
-        <v>45</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1">
-        <v>46147</v>
+        <v>46036</v>
       </c>
       <c r="B11" s="2">
-        <v>461.1700450927418</v>
+        <v>695.9259910810532</v>
       </c>
       <c r="C11" s="2">
-        <v>65.63128696233292</v>
+        <v>107.5800351448523</v>
       </c>
       <c r="D11" s="2">
-        <v>198.2021644964359</v>
+        <v>284.6837500189907</v>
       </c>
       <c r="E11" s="2">
-        <v>163.891013423966</v>
+        <v>291.1289859531737</v>
       </c>
       <c r="F11" s="2">
-        <v>9.302166808984346</v>
+        <v>5.825442731910282</v>
       </c>
       <c r="G11" s="2">
-        <v>24.14341340102255</v>
+        <v>6.707777232126229</v>
       </c>
       <c r="H11" s="3">
-        <v>48</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1">
-        <v>46148</v>
+        <v>46037</v>
       </c>
       <c r="B12" s="2">
-        <v>432.174028924864</v>
+        <v>671.1972042616959</v>
       </c>
       <c r="C12" s="2">
-        <v>61.50509550624424</v>
+        <v>98.76288327197234</v>
       </c>
       <c r="D12" s="2">
-        <v>183.519471296191</v>
+        <v>309.2060813811722</v>
       </c>
       <c r="E12" s="2">
-        <v>143.1314799636768</v>
+        <v>231.1753541431493</v>
       </c>
       <c r="F12" s="2">
-        <v>20.66326173659828</v>
+        <v>4.341083312895563</v>
       </c>
       <c r="G12" s="2">
-        <v>23.35472042215367</v>
+        <v>27.71180215250649</v>
       </c>
       <c r="H12" s="3">
-        <v>47</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1">
-        <v>46149</v>
+        <v>46038</v>
       </c>
       <c r="B13" s="2">
-        <v>477.7921218290739</v>
+        <v>727.6272557478269</v>
       </c>
       <c r="C13" s="2">
-        <v>58.5366899648971</v>
+        <v>102.6136697828107</v>
       </c>
       <c r="D13" s="2">
-        <v>265.7875746592279</v>
+        <v>344.8199209656965</v>
       </c>
       <c r="E13" s="2">
-        <v>88.79569500404928</v>
+        <v>257.5119856116652</v>
       </c>
       <c r="F13" s="2">
-        <v>18.4203873065114</v>
+        <v>3.588485000762675</v>
       </c>
       <c r="G13" s="2">
-        <v>46.25177489438818</v>
+        <v>19.09319438689181</v>
       </c>
       <c r="H13" s="3">
-        <v>48</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1">
-        <v>46150</v>
+        <v>46039</v>
       </c>
       <c r="B14" s="2">
-        <v>464.465828065181</v>
+        <v>555.3779481605394</v>
       </c>
       <c r="C14" s="2">
-        <v>58.33146480507321</v>
+        <v>79.90752590695189</v>
       </c>
       <c r="D14" s="2">
-        <v>253.9418562295412</v>
+        <v>265.6075839785735</v>
       </c>
       <c r="E14" s="2">
-        <v>98.3429970378677</v>
+        <v>184.5748847363144</v>
       </c>
       <c r="F14" s="2">
-        <v>9.168865032196045</v>
+        <v>6.732187231911554</v>
       </c>
       <c r="G14" s="2">
-        <v>44.68064496050278</v>
+        <v>18.55576630678804</v>
       </c>
       <c r="H14" s="3">
-        <v>47</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1">
-        <v>46151</v>
+        <v>46040</v>
       </c>
       <c r="B15" s="2">
-        <v>393.5683658931549</v>
+        <v>341.9881691647321</v>
       </c>
       <c r="C15" s="2">
-        <v>55.97988689406051</v>
+        <v>40.62446678247716</v>
       </c>
       <c r="D15" s="2">
-        <v>220.8472105113546</v>
+        <v>180.8399822125573</v>
       </c>
       <c r="E15" s="2">
-        <v>92.46018882524223</v>
+        <v>79.94454567413052</v>
       </c>
       <c r="F15" s="2">
-        <v>3.597834702067905</v>
+        <v>3.119818088743422</v>
       </c>
       <c r="G15" s="2">
-        <v>20.68324496042966</v>
+        <v>37.45935640682363</v>
       </c>
       <c r="H15" s="3">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1">
-        <v>46152</v>
+        <v>46041</v>
       </c>
       <c r="B16" s="2">
-        <v>374.8264867857471</v>
+        <v>599.6276699694445</v>
       </c>
       <c r="C16" s="2">
-        <v>38.08123478256994</v>
+        <v>85.83478604051803</v>
       </c>
       <c r="D16" s="2">
-        <v>186.8254608627574</v>
+        <v>299.4419111630502</v>
       </c>
       <c r="E16" s="2">
-        <v>103.4819746318128</v>
+        <v>194.7941374891207</v>
       </c>
       <c r="F16" s="2">
-        <v>0.5201874796549479</v>
+        <v>11.05915583001243</v>
       </c>
       <c r="G16" s="2">
-        <v>45.91762902895196</v>
+        <v>8.497679446743181</v>
       </c>
       <c r="H16" s="3">
-        <v>37</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1">
-        <v>46153</v>
+        <v>46042</v>
       </c>
       <c r="B17" s="2">
-        <v>395.1400092329421</v>
+        <v>587.4077676989552</v>
       </c>
       <c r="C17" s="2">
-        <v>54.72469190753169</v>
+        <v>81.63061187920884</v>
       </c>
       <c r="D17" s="2">
-        <v>220.9866180444716</v>
+        <v>274.5014420836378</v>
       </c>
       <c r="E17" s="2">
-        <v>95.95742244039145</v>
+        <v>180.7802391660213</v>
       </c>
       <c r="F17" s="2">
-        <v>6.049973821640014</v>
+        <v>19.98333271933927</v>
       </c>
       <c r="G17" s="2">
-        <v>17.42130301890739</v>
+        <v>30.51214185074799</v>
       </c>
       <c r="H17" s="3">
-        <v>42</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1">
-        <v>46154</v>
+        <v>46043</v>
       </c>
       <c r="B18" s="2">
-        <v>379.6062239715126</v>
+        <v>591.0984517348967</v>
       </c>
       <c r="C18" s="2">
-        <v>57.83367447672619</v>
+        <v>88.20246525119576</v>
       </c>
       <c r="D18" s="2">
-        <v>175.8828664412515</v>
+        <v>317.7767403945699</v>
       </c>
       <c r="E18" s="2">
-        <v>134.8248550862736</v>
+        <v>162.6628264543331</v>
       </c>
       <c r="F18" s="2">
-        <v>6.542398575428459</v>
+        <v>14.54747441675928</v>
       </c>
       <c r="G18" s="2">
-        <v>4.522429391832815</v>
+        <v>7.908945218038538</v>
       </c>
       <c r="H18" s="3">
-        <v>42</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1">
-        <v>46155</v>
+        <v>46044</v>
       </c>
       <c r="B19" s="2">
-        <v>356.1126963547902</v>
+        <v>680.5080901290709</v>
       </c>
       <c r="C19" s="2">
-        <v>52.09104818314314</v>
+        <v>97.08717194033166</v>
       </c>
       <c r="D19" s="2">
-        <v>163.543779765487</v>
+        <v>377.0371651016941</v>
       </c>
       <c r="E19" s="2">
-        <v>127.1168416849027</v>
+        <v>150.69846418906</v>
       </c>
       <c r="F19" s="2">
-        <v>4.55594245062934</v>
+        <v>19.27562391178476</v>
       </c>
       <c r="G19" s="2">
-        <v>8.805084270627962</v>
+        <v>36.40966498620032</v>
       </c>
       <c r="H19" s="3">
-        <v>40</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1">
+        <v>46045</v>
+      </c>
+      <c r="B20" s="2">
+        <v>631.8702255137399</v>
+      </c>
+      <c r="C20" s="2">
+        <v>91.02462374263339</v>
+      </c>
+      <c r="D20" s="2">
+        <v>374.0637261639887</v>
+      </c>
+      <c r="E20" s="2">
+        <v>145.9214479508499</v>
+      </c>
+      <c r="F20" s="2">
+        <v>13.38683493733406</v>
+      </c>
+      <c r="G20" s="2">
+        <v>7.473592718933812</v>
+      </c>
+      <c r="H20" s="3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="1">
+        <v>46046</v>
+      </c>
+      <c r="B21" s="2">
+        <v>479.9514119131149</v>
+      </c>
+      <c r="C21" s="2">
+        <v>67.32620158491864</v>
+      </c>
+      <c r="D21" s="2">
+        <v>277.9474398669818</v>
+      </c>
+      <c r="E21" s="2">
+        <v>104.4146869857195</v>
+      </c>
+      <c r="F21" s="2">
+        <v>10.93036391443676</v>
+      </c>
+      <c r="G21" s="2">
+        <v>19.3327195610582</v>
+      </c>
+      <c r="H21" s="3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="1">
+        <v>46047</v>
+      </c>
+      <c r="B22" s="2">
+        <v>476.0347405183204</v>
+      </c>
+      <c r="C22" s="2">
+        <v>66.00302634186215</v>
+      </c>
+      <c r="D22" s="2">
+        <v>223.2965749443998</v>
+      </c>
+      <c r="E22" s="2">
+        <v>169.7882882522709</v>
+      </c>
+      <c r="F22" s="2">
+        <v>11.16649990200996</v>
+      </c>
+      <c r="G22" s="2">
+        <v>5.780351077777644</v>
+      </c>
+      <c r="H22" s="3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="1">
+        <v>46048</v>
+      </c>
+      <c r="B23" s="2">
+        <v>557.0829673989894</v>
+      </c>
+      <c r="C23" s="2">
+        <v>85.82935461607244</v>
+      </c>
+      <c r="D23" s="2">
+        <v>311.8878644436225</v>
+      </c>
+      <c r="E23" s="2">
+        <v>138.3848575125893</v>
+      </c>
+      <c r="F23" s="2">
+        <v>13.63944004267454</v>
+      </c>
+      <c r="G23" s="2">
+        <v>7.341450784030473</v>
+      </c>
+      <c r="H23" s="3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="1">
+        <v>46049</v>
+      </c>
+      <c r="B24" s="2">
+        <v>505.0955326890552</v>
+      </c>
+      <c r="C24" s="2">
+        <v>78.72282151401043</v>
+      </c>
+      <c r="D24" s="2">
+        <v>283.9247974454508</v>
+      </c>
+      <c r="E24" s="2">
+        <v>126.6682330969555</v>
+      </c>
+      <c r="F24" s="2">
+        <v>8.746882258521186</v>
+      </c>
+      <c r="G24" s="2">
+        <v>7.032798374117249</v>
+      </c>
+      <c r="H24" s="3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="1">
+        <v>46050</v>
+      </c>
+      <c r="B25" s="2">
+        <v>504.4835933730731</v>
+      </c>
+      <c r="C25" s="2">
+        <v>80.10125669735588</v>
+      </c>
+      <c r="D25" s="2">
+        <v>232.3213673150043</v>
+      </c>
+      <c r="E25" s="2">
+        <v>179.6531440567805</v>
+      </c>
+      <c r="F25" s="2">
+        <v>7.981907250285149</v>
+      </c>
+      <c r="G25" s="2">
+        <v>4.425918053647297</v>
+      </c>
+      <c r="H25" s="3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="1">
+        <v>46051</v>
+      </c>
+      <c r="B26" s="2">
+        <v>521.2858124377971</v>
+      </c>
+      <c r="C26" s="2">
+        <v>81.15885744273663</v>
+      </c>
+      <c r="D26" s="2">
+        <v>238.8037387839757</v>
+      </c>
+      <c r="E26" s="2">
+        <v>181.9827654995427</v>
+      </c>
+      <c r="F26" s="2">
+        <v>15.27975654608674</v>
+      </c>
+      <c r="G26" s="2">
+        <v>4.060694165455384</v>
+      </c>
+      <c r="H26" s="3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="1">
+        <v>46052</v>
+      </c>
+      <c r="B27" s="2">
+        <v>647.5044455310936</v>
+      </c>
+      <c r="C27" s="2">
+        <v>98.50745945625835</v>
+      </c>
+      <c r="D27" s="2">
+        <v>304.4402415947544</v>
+      </c>
+      <c r="E27" s="2">
+        <v>223.9297258566465</v>
+      </c>
+      <c r="F27" s="2">
+        <v>15.52433970080482</v>
+      </c>
+      <c r="G27" s="2">
+        <v>5.102678922629501</v>
+      </c>
+      <c r="H27" s="3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="1">
+        <v>46053</v>
+      </c>
+      <c r="B28" s="2">
+        <v>491.051932502114</v>
+      </c>
+      <c r="C28" s="2">
+        <v>75.86040930001272</v>
+      </c>
+      <c r="D28" s="2">
+        <v>233.1665459883875</v>
+      </c>
+      <c r="E28" s="2">
+        <v>169.9930807559689</v>
+      </c>
+      <c r="F28" s="2">
+        <v>8.264972279866537</v>
+      </c>
+      <c r="G28" s="2">
+        <v>3.766924177878277</v>
+      </c>
+      <c r="H28" s="3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="1">
+        <v>46054</v>
+      </c>
+      <c r="B29" s="2">
+        <v>458.3183966223779</v>
+      </c>
+      <c r="C29" s="2">
+        <v>70.29105648969507</v>
+      </c>
+      <c r="D29" s="2">
+        <v>201.6564623200943</v>
+      </c>
+      <c r="E29" s="2">
+        <v>178.0143144863876</v>
+      </c>
+      <c r="F29" s="2">
+        <v>3.178162818882201</v>
+      </c>
+      <c r="G29" s="2">
+        <v>5.178400507319153</v>
+      </c>
+      <c r="H29" s="3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="1">
+        <v>46055</v>
+      </c>
+      <c r="B30" s="2">
+        <v>650.6602207764706</v>
+      </c>
+      <c r="C30" s="2">
+        <v>96.42241118174724</v>
+      </c>
+      <c r="D30" s="2">
+        <v>250.9526818819889</v>
+      </c>
+      <c r="E30" s="2">
+        <v>281.088011335684</v>
+      </c>
+      <c r="F30" s="2">
+        <v>6.283223289523334</v>
+      </c>
+      <c r="G30" s="2">
+        <v>15.91389308752722</v>
+      </c>
+      <c r="H30" s="3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="1">
+        <v>46056</v>
+      </c>
+      <c r="B31" s="2">
+        <v>650.7959142961573</v>
+      </c>
+      <c r="C31" s="2">
+        <v>96.58789493243528</v>
+      </c>
+      <c r="D31" s="2">
+        <v>239.4381515701074</v>
+      </c>
+      <c r="E31" s="2">
+        <v>280.4370941649332</v>
+      </c>
+      <c r="F31" s="2">
+        <v>10.48267115195028</v>
+      </c>
+      <c r="G31" s="2">
+        <v>23.85010247673</v>
+      </c>
+      <c r="H31" s="3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="1">
+        <v>46057</v>
+      </c>
+      <c r="B32" s="2">
+        <v>594.6842099135278</v>
+      </c>
+      <c r="C32" s="2">
+        <v>88.38247825495722</v>
+      </c>
+      <c r="D32" s="2">
+        <v>222.977461413191</v>
+      </c>
+      <c r="E32" s="2">
+        <v>250.8782049608096</v>
+      </c>
+      <c r="F32" s="2">
+        <v>17.84425720681111</v>
+      </c>
+      <c r="G32" s="2">
+        <v>14.60180807775806</v>
+      </c>
+      <c r="H32" s="3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="1">
+        <v>46058</v>
+      </c>
+      <c r="B33" s="2">
+        <v>533.8853038501935</v>
+      </c>
+      <c r="C33" s="2">
+        <v>80.24967716719308</v>
+      </c>
+      <c r="D33" s="2">
+        <v>193.7848422473126</v>
+      </c>
+      <c r="E33" s="2">
+        <v>220.218044832137</v>
+      </c>
+      <c r="F33" s="2">
+        <v>30.71155985192221</v>
+      </c>
+      <c r="G33" s="2">
+        <v>8.921179751631387</v>
+      </c>
+      <c r="H33" s="3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="1">
+        <v>46059</v>
+      </c>
+      <c r="B34" s="2">
+        <v>502.8489898180218</v>
+      </c>
+      <c r="C34" s="2">
+        <v>69.98073047820445</v>
+      </c>
+      <c r="D34" s="2">
+        <v>176.4636924276704</v>
+      </c>
+      <c r="E34" s="2">
+        <v>217.8899980104544</v>
+      </c>
+      <c r="F34" s="2">
+        <v>22.90703134731279</v>
+      </c>
+      <c r="G34" s="2">
+        <v>15.60753755437944</v>
+      </c>
+      <c r="H34" s="3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="1">
+        <v>46060</v>
+      </c>
+      <c r="B35" s="2">
+        <v>499.0569376407652</v>
+      </c>
+      <c r="C35" s="2">
+        <v>71.24509206573362</v>
+      </c>
+      <c r="D35" s="2">
+        <v>186.3225820479333</v>
+      </c>
+      <c r="E35" s="2">
+        <v>212.7963784709946</v>
+      </c>
+      <c r="F35" s="2">
+        <v>23.49184669036666</v>
+      </c>
+      <c r="G35" s="2">
+        <v>5.201038365736111</v>
+      </c>
+      <c r="H35" s="3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="1">
+        <v>46061</v>
+      </c>
+      <c r="B36" s="2">
+        <v>476.4751409247824</v>
+      </c>
+      <c r="C36" s="2">
+        <v>67.00184772701022</v>
+      </c>
+      <c r="D36" s="2">
+        <v>162.2501243117009</v>
+      </c>
+      <c r="E36" s="2">
+        <v>212.464636306031</v>
+      </c>
+      <c r="F36" s="2">
+        <v>16.95067667215712</v>
+      </c>
+      <c r="G36" s="2">
+        <v>17.80785590788343</v>
+      </c>
+      <c r="H36" s="3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="1">
+        <v>46062</v>
+      </c>
+      <c r="B37" s="2">
+        <v>455.4862566126254</v>
+      </c>
+      <c r="C37" s="2">
+        <v>68.8753784880042</v>
+      </c>
+      <c r="D37" s="2">
+        <v>184.5939835173057</v>
+      </c>
+      <c r="E37" s="2">
+        <v>168.4562760415508</v>
+      </c>
+      <c r="F37" s="2">
+        <v>17.16392665339841</v>
+      </c>
+      <c r="G37" s="2">
+        <v>16.39669191236634</v>
+      </c>
+      <c r="H37" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="1">
+        <v>46063</v>
+      </c>
+      <c r="B38" s="2">
+        <v>633.0418946752806</v>
+      </c>
+      <c r="C38" s="2">
+        <v>96.31106729050477</v>
+      </c>
+      <c r="D38" s="2">
+        <v>239.2519968002662</v>
+      </c>
+      <c r="E38" s="2">
+        <v>257.0165906603469</v>
+      </c>
+      <c r="F38" s="2">
+        <v>29.79283985786968</v>
+      </c>
+      <c r="G38" s="2">
+        <v>10.66940006629305</v>
+      </c>
+      <c r="H38" s="3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="1">
+        <v>46064</v>
+      </c>
+      <c r="B39" s="2">
+        <v>567.9781500475357</v>
+      </c>
+      <c r="C39" s="2">
+        <v>88.07333260992336</v>
+      </c>
+      <c r="D39" s="2">
+        <v>228.8688585546613</v>
+      </c>
+      <c r="E39" s="2">
+        <v>217.3030797396021</v>
+      </c>
+      <c r="F39" s="2">
+        <v>26.44818690220515</v>
+      </c>
+      <c r="G39" s="2">
+        <v>7.28469224114385</v>
+      </c>
+      <c r="H39" s="3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="1">
+        <v>46065</v>
+      </c>
+      <c r="B40" s="2">
+        <v>612.8597231307994</v>
+      </c>
+      <c r="C40" s="2">
+        <v>95.84318573587471</v>
+      </c>
+      <c r="D40" s="2">
+        <v>282.7483857384246</v>
+      </c>
+      <c r="E40" s="2">
+        <v>208.6029543809593</v>
+      </c>
+      <c r="F40" s="2">
+        <v>19.41120592329237</v>
+      </c>
+      <c r="G40" s="2">
+        <v>6.253991352248316</v>
+      </c>
+      <c r="H40" s="3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="1">
+        <v>46066</v>
+      </c>
+      <c r="B41" s="2">
+        <v>581.1016823712017</v>
+      </c>
+      <c r="C41" s="2">
+        <v>89.61718286885156</v>
+      </c>
+      <c r="D41" s="2">
+        <v>315.4246239677651</v>
+      </c>
+      <c r="E41" s="2">
+        <v>146.6727867614561</v>
+      </c>
+      <c r="F41" s="2">
+        <v>22.09380348894331</v>
+      </c>
+      <c r="G41" s="2">
+        <v>7.293285284185679</v>
+      </c>
+      <c r="H41" s="3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" s="1">
+        <v>46067</v>
+      </c>
+      <c r="B42" s="2">
+        <v>411.5550675604613</v>
+      </c>
+      <c r="C42" s="2">
+        <v>51.8297838115361</v>
+      </c>
+      <c r="D42" s="2">
+        <v>291.5703612403142</v>
+      </c>
+      <c r="E42" s="2">
+        <v>52.48331473061272</v>
+      </c>
+      <c r="F42" s="2">
+        <v>7.100836112035646</v>
+      </c>
+      <c r="G42" s="2">
+        <v>8.570771665962594</v>
+      </c>
+      <c r="H42" s="3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" s="1">
+        <v>46068</v>
+      </c>
+      <c r="B43" s="2">
+        <v>260.3619419842492</v>
+      </c>
+      <c r="C43" s="2">
+        <v>35.22770898183187</v>
+      </c>
+      <c r="D43" s="2">
+        <v>193.4860157430131</v>
+      </c>
+      <c r="E43" s="2">
+        <v>23.76956054259396</v>
+      </c>
+      <c r="F43" s="2">
+        <v>3.107844231790966</v>
+      </c>
+      <c r="G43" s="2">
+        <v>4.770812485019366</v>
+      </c>
+      <c r="H43" s="3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="1">
+        <v>46069</v>
+      </c>
+      <c r="B44" s="2">
+        <v>460.2949149160201</v>
+      </c>
+      <c r="C44" s="2">
+        <v>65.10196759916015</v>
+      </c>
+      <c r="D44" s="2">
+        <v>265.9389389503551</v>
+      </c>
+      <c r="E44" s="2">
+        <v>121.507330558062</v>
+      </c>
+      <c r="F44" s="2">
+        <v>0.0008430555793974135</v>
+      </c>
+      <c r="G44" s="2">
+        <v>7.74583475286348</v>
+      </c>
+      <c r="H44" s="3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" s="1">
+        <v>46070</v>
+      </c>
+      <c r="B45" s="2">
+        <v>505.9405817090337</v>
+      </c>
+      <c r="C45" s="2">
+        <v>76.26649897865951</v>
+      </c>
+      <c r="D45" s="2">
+        <v>267.8688417878028</v>
+      </c>
+      <c r="E45" s="2">
+        <v>152.1853886934494</v>
+      </c>
+      <c r="F45" s="2">
+        <v>0.4085580645004908</v>
+      </c>
+      <c r="G45" s="2">
+        <v>9.211294184621527</v>
+      </c>
+      <c r="H45" s="3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="1">
+        <v>46071</v>
+      </c>
+      <c r="B46" s="2">
+        <v>485.9780614789823</v>
+      </c>
+      <c r="C46" s="2">
+        <v>74.10316600927048</v>
+      </c>
+      <c r="D46" s="2">
+        <v>246.6417179708079</v>
+      </c>
+      <c r="E46" s="2">
+        <v>158.4391919338206</v>
+      </c>
+      <c r="F46" s="2">
+        <v>0.005327222115463681</v>
+      </c>
+      <c r="G46" s="2">
+        <v>6.788658342967845</v>
+      </c>
+      <c r="H46" s="3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" s="1">
+        <v>46072</v>
+      </c>
+      <c r="B47" s="2">
+        <v>488.9715352456096</v>
+      </c>
+      <c r="C47" s="2">
+        <v>69.37446195304393</v>
+      </c>
+      <c r="D47" s="2">
+        <v>250.9151613933262</v>
+      </c>
+      <c r="E47" s="2">
+        <v>143.1137700467474</v>
+      </c>
+      <c r="F47" s="2">
+        <v>0.01060916615857018</v>
+      </c>
+      <c r="G47" s="2">
+        <v>24.41372604284746</v>
+      </c>
+      <c r="H47" s="3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" s="1">
+        <v>46073</v>
+      </c>
+      <c r="B48" s="2">
+        <v>501.1660536703341</v>
+      </c>
+      <c r="C48" s="2">
+        <v>73.28168327344788</v>
+      </c>
+      <c r="D48" s="2">
+        <v>201.530560697463</v>
+      </c>
+      <c r="E48" s="2">
+        <v>216.4507551646315</v>
+      </c>
+      <c r="F48" s="2">
+        <v>0.2642161051432292</v>
+      </c>
+      <c r="G48" s="2">
+        <v>9.638838429648377</v>
+      </c>
+      <c r="H48" s="3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" s="1">
+        <v>46074</v>
+      </c>
+      <c r="B49" s="2">
+        <v>532.3037113665127</v>
+      </c>
+      <c r="C49" s="2">
+        <v>78.24373054970573</v>
+      </c>
+      <c r="D49" s="2">
+        <v>270.8200137587544</v>
+      </c>
+      <c r="E49" s="2">
+        <v>166.4627392706606</v>
+      </c>
+      <c r="F49" s="2">
+        <v>9.406091172960069</v>
+      </c>
+      <c r="G49" s="2">
+        <v>7.371136614431937</v>
+      </c>
+      <c r="H49" s="3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" s="1">
+        <v>46075</v>
+      </c>
+      <c r="B50" s="2">
+        <v>422.927504637348</v>
+      </c>
+      <c r="C50" s="2">
+        <v>51.69091657645173</v>
+      </c>
+      <c r="D50" s="2">
+        <v>302.0715386486661</v>
+      </c>
+      <c r="E50" s="2">
+        <v>50.55938741105298</v>
+      </c>
+      <c r="F50" s="2">
+        <v>7.31284731441074</v>
+      </c>
+      <c r="G50" s="2">
+        <v>11.29281468676636</v>
+      </c>
+      <c r="H50" s="3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="1">
+        <v>46076</v>
+      </c>
+      <c r="B51" s="2">
+        <v>330.6445013545801</v>
+      </c>
+      <c r="C51" s="2">
+        <v>45.35751960549089</v>
+      </c>
+      <c r="D51" s="2">
+        <v>255.7745137417126</v>
+      </c>
+      <c r="E51" s="2">
+        <v>19.30053476255387</v>
+      </c>
+      <c r="F51" s="2">
+        <v>5.301868567268054</v>
+      </c>
+      <c r="G51" s="2">
+        <v>4.9100646775547</v>
+      </c>
+      <c r="H51" s="3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="1">
+        <v>46077</v>
+      </c>
+      <c r="B52" s="2">
+        <v>537.6028399167869</v>
+      </c>
+      <c r="C52" s="2">
+        <v>73.05643182824055</v>
+      </c>
+      <c r="D52" s="2">
+        <v>320.9377575550712</v>
+      </c>
+      <c r="E52" s="2">
+        <v>121.8424082935519</v>
+      </c>
+      <c r="F52" s="2">
+        <v>11.15243501368496</v>
+      </c>
+      <c r="G52" s="2">
+        <v>10.61380722623836</v>
+      </c>
+      <c r="H52" s="3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" s="1">
+        <v>46078</v>
+      </c>
+      <c r="B53" s="2">
+        <v>515.6547520694044</v>
+      </c>
+      <c r="C53" s="2">
+        <v>68.3127365039289</v>
+      </c>
+      <c r="D53" s="2">
+        <v>275.7670619828057</v>
+      </c>
+      <c r="E53" s="2">
+        <v>161.3605071942343</v>
+      </c>
+      <c r="F53" s="2">
+        <v>4.135703069898817</v>
+      </c>
+      <c r="G53" s="2">
+        <v>6.078743318536629</v>
+      </c>
+      <c r="H53" s="3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" s="1">
+        <v>46079</v>
+      </c>
+      <c r="B54" s="2">
+        <v>520.6994602496316</v>
+      </c>
+      <c r="C54" s="2">
+        <v>75.4929056516952</v>
+      </c>
+      <c r="D54" s="2">
+        <v>302.5701680172673</v>
+      </c>
+      <c r="E54" s="2">
+        <v>123.3893893976096</v>
+      </c>
+      <c r="F54" s="2">
+        <v>12.50072026782566</v>
+      </c>
+      <c r="G54" s="2">
+        <v>6.746276915233789</v>
+      </c>
+      <c r="H54" s="3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" s="1">
+        <v>46080</v>
+      </c>
+      <c r="B55" s="2">
+        <v>567.007965755986</v>
+      </c>
+      <c r="C55" s="2">
+        <v>84.97182482411878</v>
+      </c>
+      <c r="D55" s="2">
+        <v>346.93418324426</v>
+      </c>
+      <c r="E55" s="2">
+        <v>110.5410324129628</v>
+      </c>
+      <c r="F55" s="2">
+        <v>13.08757857428657</v>
+      </c>
+      <c r="G55" s="2">
+        <v>11.47334670035789</v>
+      </c>
+      <c r="H55" s="3">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" s="1">
+        <v>46081</v>
+      </c>
+      <c r="B56" s="2">
+        <v>469.2419034465082</v>
+      </c>
+      <c r="C56" s="2">
+        <v>69.4649432122045</v>
+      </c>
+      <c r="D56" s="2">
+        <v>303.328485388598</v>
+      </c>
+      <c r="E56" s="2">
+        <v>82.75760264482763</v>
+      </c>
+      <c r="F56" s="2">
+        <v>6.107532770633697</v>
+      </c>
+      <c r="G56" s="2">
+        <v>7.583339430244329</v>
+      </c>
+      <c r="H56" s="3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" s="1">
+        <v>46082</v>
+      </c>
+      <c r="B57" s="2">
+        <v>474.8586472173935</v>
+      </c>
+      <c r="C57" s="2">
+        <v>69.6427754144205</v>
+      </c>
+      <c r="D57" s="2">
+        <v>249.4279874015041</v>
+      </c>
+      <c r="E57" s="2">
+        <v>143.7194427354137</v>
+      </c>
+      <c r="F57" s="2">
+        <v>6.55002609004577</v>
+      </c>
+      <c r="G57" s="2">
+        <v>5.518415576009494</v>
+      </c>
+      <c r="H57" s="3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" s="1">
+        <v>46083</v>
+      </c>
+      <c r="B58" s="2">
+        <v>525.644441024526</v>
+      </c>
+      <c r="C58" s="2">
+        <v>73.32283486458991</v>
+      </c>
+      <c r="D58" s="2">
+        <v>219.9624210150126</v>
+      </c>
+      <c r="E58" s="2">
+        <v>198.2846274922043</v>
+      </c>
+      <c r="F58" s="2">
+        <v>3.559508378770616</v>
+      </c>
+      <c r="G58" s="2">
+        <v>30.5150492739486</v>
+      </c>
+      <c r="H58" s="3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" s="1">
+        <v>46084</v>
+      </c>
+      <c r="B59" s="2">
+        <v>539.9847266317536</v>
+      </c>
+      <c r="C59" s="2">
+        <v>74.94955445274711</v>
+      </c>
+      <c r="D59" s="2">
+        <v>238.6860020077874</v>
+      </c>
+      <c r="E59" s="2">
+        <v>182.5835487650128</v>
+      </c>
+      <c r="F59" s="2">
+        <v>13.87591089910931</v>
+      </c>
+      <c r="G59" s="2">
+        <v>29.88971050709693</v>
+      </c>
+      <c r="H59" s="3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" s="1">
+        <v>46085</v>
+      </c>
+      <c r="B60" s="2">
+        <v>652.0207947547051</v>
+      </c>
+      <c r="C60" s="2">
+        <v>87.2538680783059</v>
+      </c>
+      <c r="D60" s="2">
+        <v>190.7186813584632</v>
+      </c>
+      <c r="E60" s="2">
+        <v>328.3260291573405</v>
+      </c>
+      <c r="F60" s="2">
+        <v>2.60505912039015</v>
+      </c>
+      <c r="G60" s="2">
+        <v>43.11715704020526</v>
+      </c>
+      <c r="H60" s="3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" s="1">
+        <v>46086</v>
+      </c>
+      <c r="B61" s="2">
+        <v>552.5136747725202</v>
+      </c>
+      <c r="C61" s="2">
+        <v>72.99988324473301</v>
+      </c>
+      <c r="D61" s="2">
+        <v>139.0270460216515</v>
+      </c>
+      <c r="E61" s="2">
+        <v>287.3805466105044</v>
+      </c>
+      <c r="F61" s="2">
+        <v>2.225114700827334</v>
+      </c>
+      <c r="G61" s="2">
+        <v>50.88108419480398</v>
+      </c>
+      <c r="H61" s="3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" s="1">
+        <v>46087</v>
+      </c>
+      <c r="B62" s="2">
+        <v>594.3467251807834</v>
+      </c>
+      <c r="C62" s="2">
+        <v>78.27638512012031</v>
+      </c>
+      <c r="D62" s="2">
+        <v>272.398257439687</v>
+      </c>
+      <c r="E62" s="2">
+        <v>195.1403145207962</v>
+      </c>
+      <c r="F62" s="2">
+        <v>7.218209352791309</v>
+      </c>
+      <c r="G62" s="2">
+        <v>41.31355874738863</v>
+      </c>
+      <c r="H62" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" s="1">
+        <v>46088</v>
+      </c>
+      <c r="B63" s="2">
+        <v>541.586126327228</v>
+      </c>
+      <c r="C63" s="2">
+        <v>73.05037977587845</v>
+      </c>
+      <c r="D63" s="2">
+        <v>305.4501313268414</v>
+      </c>
+      <c r="E63" s="2">
+        <v>114.1681032194694</v>
+      </c>
+      <c r="F63" s="2">
+        <v>11.33450496256351</v>
+      </c>
+      <c r="G63" s="2">
+        <v>37.58300704247525</v>
+      </c>
+      <c r="H63" s="3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" s="1">
+        <v>46089</v>
+      </c>
+      <c r="B64" s="2">
+        <v>436.5674449626025</v>
+      </c>
+      <c r="C64" s="2">
+        <v>60.06546828939683</v>
+      </c>
+      <c r="D64" s="2">
+        <v>241.043025218475</v>
+      </c>
+      <c r="E64" s="2">
+        <v>123.2995011541827</v>
+      </c>
+      <c r="F64" s="2">
+        <v>3.857798608144124</v>
+      </c>
+      <c r="G64" s="2">
+        <v>8.301651692403894</v>
+      </c>
+      <c r="H64" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" s="1">
+        <v>46090</v>
+      </c>
+      <c r="B65" s="2">
+        <v>324.4999544986751</v>
+      </c>
+      <c r="C65" s="2">
+        <v>44.80263996061352</v>
+      </c>
+      <c r="D65" s="2">
+        <v>197.820755520256</v>
+      </c>
+      <c r="E65" s="2">
+        <v>50.984941473893</v>
+      </c>
+      <c r="F65" s="2">
+        <v>3.03712106956376</v>
+      </c>
+      <c r="G65" s="2">
+        <v>27.85449647434884</v>
+      </c>
+      <c r="H65" s="3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B66" s="2">
+        <v>409.9205860815937</v>
+      </c>
+      <c r="C66" s="2">
+        <v>58.11957640674379</v>
+      </c>
+      <c r="D66" s="2">
+        <v>227.6981644950414</v>
+      </c>
+      <c r="E66" s="2">
+        <v>98.1988255889631</v>
+      </c>
+      <c r="F66" s="2">
+        <v>6.998535788688395</v>
+      </c>
+      <c r="G66" s="2">
+        <v>18.90548380215704</v>
+      </c>
+      <c r="H66" s="3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B67" s="2">
+        <v>365.9466353011513</v>
+      </c>
+      <c r="C67" s="2">
+        <v>50.45479373759694</v>
+      </c>
+      <c r="D67" s="2">
+        <v>198.2627522670757</v>
+      </c>
+      <c r="E67" s="2">
+        <v>95.180791445018</v>
+      </c>
+      <c r="F67" s="2">
+        <v>9.195928547117445</v>
+      </c>
+      <c r="G67" s="2">
+        <v>12.8523693043432</v>
+      </c>
+      <c r="H67" s="3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B68" s="2">
+        <v>386.4303433498911</v>
+      </c>
+      <c r="C68" s="2">
+        <v>48.78738393863042</v>
+      </c>
+      <c r="D68" s="2">
+        <v>196.9286540739342</v>
+      </c>
+      <c r="E68" s="2">
+        <v>99.77775136638847</v>
+      </c>
+      <c r="F68" s="2">
+        <v>6.650347009433641</v>
+      </c>
+      <c r="G68" s="2">
+        <v>34.28620696150439</v>
+      </c>
+      <c r="H68" s="3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B69" s="2">
+        <v>429.2763768525934</v>
+      </c>
+      <c r="C69" s="2">
+        <v>64.09907946538077</v>
+      </c>
+      <c r="D69" s="2">
+        <v>257.6882236965482</v>
+      </c>
+      <c r="E69" s="2">
+        <v>86.1237277468625</v>
+      </c>
+      <c r="F69" s="2">
+        <v>13.42511066390408</v>
+      </c>
+      <c r="G69" s="2">
+        <v>7.940235279897848</v>
+      </c>
+      <c r="H69" s="3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" s="1">
+        <v>46095</v>
+      </c>
+      <c r="B70" s="2">
+        <v>450.3057350144028</v>
+      </c>
+      <c r="C70" s="2">
+        <v>67.1063798524936</v>
+      </c>
+      <c r="D70" s="2">
+        <v>329.8650853912341</v>
+      </c>
+      <c r="E70" s="2">
+        <v>33.15675891608983</v>
+      </c>
+      <c r="F70" s="2">
+        <v>7.979291646083196</v>
+      </c>
+      <c r="G70" s="2">
+        <v>12.19821920850211</v>
+      </c>
+      <c r="H70" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71" s="1">
+        <v>46096</v>
+      </c>
+      <c r="B71" s="2">
+        <v>347.4651230987844</v>
+      </c>
+      <c r="C71" s="2">
+        <v>50.11702934110433</v>
+      </c>
+      <c r="D71" s="2">
+        <v>274.3363245417126</v>
+      </c>
+      <c r="E71" s="2">
+        <v>16.3684872214848</v>
+      </c>
+      <c r="F71" s="2">
+        <v>2.380206146240234</v>
+      </c>
+      <c r="G71" s="2">
+        <v>4.263075848242475</v>
+      </c>
+      <c r="H71" s="3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B72" s="2">
+        <v>376.8600094530786</v>
+      </c>
+      <c r="C72" s="2">
+        <v>53.76107375714514</v>
+      </c>
+      <c r="D72" s="2">
+        <v>288.8538153159756</v>
+      </c>
+      <c r="E72" s="2">
+        <v>19.10829601754745</v>
+      </c>
+      <c r="F72" s="2">
+        <v>8.712412985894415</v>
+      </c>
+      <c r="G72" s="2">
+        <v>6.424411376516025</v>
+      </c>
+      <c r="H72" s="3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" s="1">
+        <v>46098</v>
+      </c>
+      <c r="B73" s="2">
+        <v>335.2342758695714</v>
+      </c>
+      <c r="C73" s="2">
+        <v>42.22733177123747</v>
+      </c>
+      <c r="D73" s="2">
+        <v>229.0004088479798</v>
+      </c>
+      <c r="E73" s="2">
+        <v>30.96059875281321</v>
+      </c>
+      <c r="F73" s="2">
+        <v>11.40589873439736</v>
+      </c>
+      <c r="G73" s="2">
+        <v>21.64003776314358</v>
+      </c>
+      <c r="H73" s="3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74" s="1">
+        <v>46099</v>
+      </c>
+      <c r="B74" s="2">
+        <v>294.3944040113553</v>
+      </c>
+      <c r="C74" s="2">
+        <v>40.26306771715482</v>
+      </c>
+      <c r="D74" s="2">
+        <v>138.3663314127156</v>
+      </c>
+      <c r="E74" s="2">
+        <v>104.9077739987605</v>
+      </c>
+      <c r="F74" s="2">
+        <v>6.778992815117041</v>
+      </c>
+      <c r="G74" s="2">
+        <v>4.078238067607292</v>
+      </c>
+      <c r="H74" s="3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75" s="1">
+        <v>46100</v>
+      </c>
+      <c r="B75" s="2">
+        <v>290.9819456108308</v>
+      </c>
+      <c r="C75" s="2">
+        <v>40.59091454254256</v>
+      </c>
+      <c r="D75" s="2">
+        <v>118.4801314308888</v>
+      </c>
+      <c r="E75" s="2">
+        <v>112.9840515926315</v>
+      </c>
+      <c r="F75" s="2">
+        <v>8.285319689114889</v>
+      </c>
+      <c r="G75" s="2">
+        <v>10.64152835565309</v>
+      </c>
+      <c r="H75" s="3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" s="1">
+        <v>46101</v>
+      </c>
+      <c r="B76" s="2">
+        <v>356.7918768416779</v>
+      </c>
+      <c r="C76" s="2">
+        <v>53.27758774060756</v>
+      </c>
+      <c r="D76" s="2">
+        <v>170.4474076943575</v>
+      </c>
+      <c r="E76" s="2">
+        <v>114.0028993722796</v>
+      </c>
+      <c r="F76" s="2">
+        <v>13.30206065036356</v>
+      </c>
+      <c r="G76" s="2">
+        <v>5.761921384069654</v>
+      </c>
+      <c r="H76" s="3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77" s="1">
+        <v>46102</v>
+      </c>
+      <c r="B77" s="2">
+        <v>428.9770823672869</v>
+      </c>
+      <c r="C77" s="2">
+        <v>64.94292565504711</v>
+      </c>
+      <c r="D77" s="2">
+        <v>219.4155451001475</v>
+      </c>
+      <c r="E77" s="2">
+        <v>133.4568338182486</v>
+      </c>
+      <c r="F77" s="2">
+        <v>7.102920854356554</v>
+      </c>
+      <c r="G77" s="2">
+        <v>4.05885693948716</v>
+      </c>
+      <c r="H77" s="3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" s="1">
+        <v>46103</v>
+      </c>
+      <c r="B78" s="2">
+        <v>375.8202519112937</v>
+      </c>
+      <c r="C78" s="2">
+        <v>55.25804654869768</v>
+      </c>
+      <c r="D78" s="2">
+        <v>251.8758890359712</v>
+      </c>
+      <c r="E78" s="2">
+        <v>61.10367273522334</v>
+      </c>
+      <c r="F78" s="2">
+        <v>3.551864988009135</v>
+      </c>
+      <c r="G78" s="2">
+        <v>4.030778603392343</v>
+      </c>
+      <c r="H78" s="3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B79" s="2">
+        <v>295.4472508376661</v>
+      </c>
+      <c r="C79" s="2">
+        <v>20.32542846687966</v>
+      </c>
+      <c r="D79" s="2">
+        <v>252.5314511058635</v>
+      </c>
+      <c r="E79" s="2">
+        <v>12.3895491556906</v>
+      </c>
+      <c r="F79" s="2">
+        <v>7.138337923685709</v>
+      </c>
+      <c r="G79" s="2">
+        <v>3.062484185546637</v>
+      </c>
+      <c r="H79" s="3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="A80" s="1">
+        <v>46105</v>
+      </c>
+      <c r="B80" s="2">
+        <v>299.7152285023261</v>
+      </c>
+      <c r="C80" s="2">
+        <v>34.16942481944958</v>
+      </c>
+      <c r="D80" s="2">
+        <v>218.5515340258926</v>
+      </c>
+      <c r="E80" s="2">
+        <v>36.57108552712533</v>
+      </c>
+      <c r="F80" s="2">
+        <v>8.667285250557793</v>
+      </c>
+      <c r="G80" s="2">
+        <v>1.755898879300803</v>
+      </c>
+      <c r="H80" s="3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8">
+      <c r="A81" s="1">
+        <v>46106</v>
+      </c>
+      <c r="B81" s="2">
+        <v>349.7252967067911</v>
+      </c>
+      <c r="C81" s="2">
+        <v>38.04424941298034</v>
+      </c>
+      <c r="D81" s="2">
+        <v>169.0896796379818</v>
+      </c>
+      <c r="E81" s="2">
+        <v>127.3610126167867</v>
+      </c>
+      <c r="F81" s="2">
+        <v>4.895261433919271</v>
+      </c>
+      <c r="G81" s="2">
+        <v>10.33509360512305</v>
+      </c>
+      <c r="H81" s="3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
+      <c r="A82" s="1">
+        <v>46107</v>
+      </c>
+      <c r="B82" s="2">
+        <v>289.2031242050795</v>
+      </c>
+      <c r="C82" s="2">
+        <v>29.71496361927854</v>
+      </c>
+      <c r="D82" s="2">
+        <v>147.3965038874249</v>
+      </c>
+      <c r="E82" s="2">
+        <v>97.49975534978427</v>
+      </c>
+      <c r="F82" s="2">
+        <v>13.13339579264323</v>
+      </c>
+      <c r="G82" s="2">
+        <v>1.458505555948553</v>
+      </c>
+      <c r="H82" s="3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
+      <c r="A83" s="1">
+        <v>46108</v>
+      </c>
+      <c r="B83" s="2">
+        <v>332.5057696863616</v>
+      </c>
+      <c r="C83" s="2">
+        <v>49.92647149648931</v>
+      </c>
+      <c r="D83" s="2">
+        <v>143.0506417225136</v>
+      </c>
+      <c r="E83" s="2">
+        <v>127.5189474205259</v>
+      </c>
+      <c r="F83" s="2">
+        <v>9.410011845595307</v>
+      </c>
+      <c r="G83" s="2">
+        <v>2.599697201237496</v>
+      </c>
+      <c r="H83" s="3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8">
+      <c r="A84" s="1">
+        <v>46109</v>
+      </c>
+      <c r="B84" s="2">
+        <v>402.784444574003</v>
+      </c>
+      <c r="C84" s="2">
+        <v>58.55442659868135</v>
+      </c>
+      <c r="D84" s="2">
+        <v>150.5464853307794</v>
+      </c>
+      <c r="E84" s="2">
+        <v>187.5175101825885</v>
+      </c>
+      <c r="F84" s="2">
+        <v>2.802114723192321</v>
+      </c>
+      <c r="G84" s="2">
+        <v>3.363907738761562</v>
+      </c>
+      <c r="H84" s="3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8">
+      <c r="A85" s="1">
+        <v>46110</v>
+      </c>
+      <c r="B85" s="2">
+        <v>313.8472739612301</v>
+      </c>
+      <c r="C85" s="2">
+        <v>45.09727938546074</v>
+      </c>
+      <c r="D85" s="2">
+        <v>138.2112484407435</v>
+      </c>
+      <c r="E85" s="2">
+        <v>125.7445075329952</v>
+      </c>
+      <c r="F85" s="2">
+        <v>2.103562786314222</v>
+      </c>
+      <c r="G85" s="2">
+        <v>2.690675815716386</v>
+      </c>
+      <c r="H85" s="3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8">
+      <c r="A86" s="1">
+        <v>46111</v>
+      </c>
+      <c r="B86" s="2">
+        <v>322.4934733793967</v>
+      </c>
+      <c r="C86" s="2">
+        <v>49.43798138876756</v>
+      </c>
+      <c r="D86" s="2">
+        <v>139.0268761372566</v>
+      </c>
+      <c r="E86" s="2">
+        <v>127.2150895330227</v>
+      </c>
+      <c r="F86" s="2">
+        <v>4.576561868720584</v>
+      </c>
+      <c r="G86" s="2">
+        <v>2.236964451629254</v>
+      </c>
+      <c r="H86" s="3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8">
+      <c r="A87" s="1">
+        <v>46112</v>
+      </c>
+      <c r="B87" s="2">
+        <v>303.7321328057344</v>
+      </c>
+      <c r="C87" s="2">
+        <v>40.37584235525794</v>
+      </c>
+      <c r="D87" s="2">
+        <v>117.6803280255028</v>
+      </c>
+      <c r="E87" s="2">
+        <v>116.1597747703724</v>
+      </c>
+      <c r="F87" s="2">
+        <v>2.950167168511285</v>
+      </c>
+      <c r="G87" s="2">
+        <v>26.56602048608992</v>
+      </c>
+      <c r="H87" s="3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8">
+      <c r="A88" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B88" s="2">
+        <v>319.3030338970054</v>
+      </c>
+      <c r="C88" s="2">
+        <v>46.25189561208089</v>
+      </c>
+      <c r="D88" s="2">
+        <v>144.7031512825646</v>
+      </c>
+      <c r="E88" s="2">
+        <v>122.4700969688015</v>
+      </c>
+      <c r="F88" s="2">
+        <v>1.583625554177496</v>
+      </c>
+      <c r="G88" s="2">
+        <v>4.294264479380929</v>
+      </c>
+      <c r="H88" s="3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8">
+      <c r="A89" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B89" s="2">
+        <v>249.3237649363755</v>
+      </c>
+      <c r="C89" s="2">
+        <v>34.14573048230675</v>
+      </c>
+      <c r="D89" s="2">
+        <v>131.3198983922829</v>
+      </c>
+      <c r="E89" s="2">
+        <v>74.81185791517298</v>
+      </c>
+      <c r="F89" s="2">
+        <v>5.118818070226245</v>
+      </c>
+      <c r="G89" s="2">
+        <v>3.92746007638673</v>
+      </c>
+      <c r="H89" s="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8">
+      <c r="A90" s="1">
+        <v>46115</v>
+      </c>
+      <c r="B90" s="2">
+        <v>268.9178836139819</v>
+      </c>
+      <c r="C90" s="2">
+        <v>37.51144920309385</v>
+      </c>
+      <c r="D90" s="2">
+        <v>135.4633324013651</v>
+      </c>
+      <c r="E90" s="2">
+        <v>90.26212058136447</v>
+      </c>
+      <c r="F90" s="2">
+        <v>3.177322836981879</v>
+      </c>
+      <c r="G90" s="2">
+        <v>2.503658591176694</v>
+      </c>
+      <c r="H90" s="3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8">
+      <c r="A91" s="1">
+        <v>46116</v>
+      </c>
+      <c r="B91" s="2">
+        <v>303.6367755822258</v>
+      </c>
+      <c r="C91" s="2">
+        <v>44.93887431705991</v>
+      </c>
+      <c r="D91" s="2">
+        <v>146.1341548401697</v>
+      </c>
+      <c r="E91" s="2">
+        <v>107.8033502957473</v>
+      </c>
+      <c r="F91" s="2">
+        <v>0.3177908325195313</v>
+      </c>
+      <c r="G91" s="2">
+        <v>4.442605296729339</v>
+      </c>
+      <c r="H91" s="3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8">
+      <c r="A92" s="1">
+        <v>46117</v>
+      </c>
+      <c r="B92" s="2">
+        <v>247.6604666448655</v>
+      </c>
+      <c r="C92" s="2">
+        <v>37.31087130957905</v>
+      </c>
+      <c r="D92" s="2">
+        <v>101.1153714916266</v>
+      </c>
+      <c r="E92" s="2">
+        <v>105.6791180143089</v>
+      </c>
+      <c r="F92" s="2">
+        <v>0.7310330579016059</v>
+      </c>
+      <c r="G92" s="2">
+        <v>2.824072771449275</v>
+      </c>
+      <c r="H92" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8">
+      <c r="A93" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B93" s="2">
+        <v>278.419135855818</v>
+      </c>
+      <c r="C93" s="2">
+        <v>40.90526046557916</v>
+      </c>
+      <c r="D93" s="2">
+        <v>113.4851632866058</v>
+      </c>
+      <c r="E93" s="2">
+        <v>115.5748859669285</v>
+      </c>
+      <c r="F93" s="2">
+        <v>6.939007533950001</v>
+      </c>
+      <c r="G93" s="2">
+        <v>1.514818602754722</v>
+      </c>
+      <c r="H93" s="3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8">
+      <c r="A94" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B94" s="2">
+        <v>230.8485234164545</v>
+      </c>
+      <c r="C94" s="2">
+        <v>33.5997541394711</v>
+      </c>
+      <c r="D94" s="2">
+        <v>136.9581287599222</v>
+      </c>
+      <c r="E94" s="2">
+        <v>54.47087058120198</v>
+      </c>
+      <c r="F94" s="2">
+        <v>4.414253269</v>
+      </c>
+      <c r="G94" s="2">
+        <v>1.405516666859167</v>
+      </c>
+      <c r="H94" s="3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8">
+      <c r="A95" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B95" s="2">
+        <v>228.1333058620449</v>
+      </c>
+      <c r="C95" s="2">
+        <v>33.06274953275555</v>
+      </c>
+      <c r="D95" s="2">
+        <v>113.0856507790818</v>
+      </c>
+      <c r="E95" s="2">
+        <v>76.97759416255616</v>
+      </c>
+      <c r="F95" s="2">
+        <v>3.011536644424722</v>
+      </c>
+      <c r="G95" s="2">
+        <v>1.995774743226945</v>
+      </c>
+      <c r="H95" s="3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8">
+      <c r="A96" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B96" s="2">
+        <v>297.1016302107516</v>
+      </c>
+      <c r="C96" s="2">
+        <v>36.18292973088221</v>
+      </c>
+      <c r="D96" s="2">
+        <v>175.316936202696</v>
+      </c>
+      <c r="E96" s="2">
+        <v>82.27988902510619</v>
+      </c>
+      <c r="F96" s="2">
+        <v>1.4295705417975</v>
+      </c>
+      <c r="G96" s="2">
+        <v>1.89230471027</v>
+      </c>
+      <c r="H96" s="3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8">
+      <c r="A97" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B97" s="2">
+        <v>347.218266497713</v>
+      </c>
+      <c r="C97" s="2">
+        <v>38.52266610309333</v>
+      </c>
+      <c r="D97" s="2">
+        <v>222.1838408280753</v>
+      </c>
+      <c r="E97" s="2">
+        <v>77.99762816862945</v>
+      </c>
+      <c r="F97" s="2">
+        <v>5.830113325692222</v>
+      </c>
+      <c r="G97" s="2">
+        <v>2.684018072223056</v>
+      </c>
+      <c r="H97" s="3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8">
+      <c r="A98" s="1">
+        <v>46123</v>
+      </c>
+      <c r="B98" s="2">
+        <v>294.3882017277197</v>
+      </c>
+      <c r="C98" s="2">
+        <v>35.89891134952138</v>
+      </c>
+      <c r="D98" s="2">
+        <v>180.6336997641309</v>
+      </c>
+      <c r="E98" s="2">
+        <v>70.06368427267189</v>
+      </c>
+      <c r="F98" s="2">
+        <v>6.295680517719166</v>
+      </c>
+      <c r="G98" s="2">
+        <v>1.496225823675834</v>
+      </c>
+      <c r="H98" s="3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8">
+      <c r="A99" s="1">
+        <v>46124</v>
+      </c>
+      <c r="B99" s="2">
+        <v>284.1758304901777</v>
+      </c>
+      <c r="C99" s="2">
+        <v>33.93063012375887</v>
+      </c>
+      <c r="D99" s="2">
+        <v>173.7150034441519</v>
+      </c>
+      <c r="E99" s="2">
+        <v>73.08620774998155</v>
+      </c>
+      <c r="F99" s="2">
+        <v>1.102830262083333</v>
+      </c>
+      <c r="G99" s="2">
+        <v>2.341158910201987</v>
+      </c>
+      <c r="H99" s="3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8">
+      <c r="A100" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B100" s="2">
+        <v>266.5787076621151</v>
+      </c>
+      <c r="C100" s="2">
+        <v>39.97386097616619</v>
+      </c>
+      <c r="D100" s="2">
+        <v>95.89368505627745</v>
+      </c>
+      <c r="E100" s="2">
+        <v>123.1481949153129</v>
+      </c>
+      <c r="F100" s="2">
+        <v>2.248729739718967</v>
+      </c>
+      <c r="G100" s="2">
+        <v>5.314236974639611</v>
+      </c>
+      <c r="H100" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8">
+      <c r="A101" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B101" s="2">
+        <v>273.6781417201752</v>
+      </c>
+      <c r="C101" s="2">
+        <v>40.0413355584277</v>
+      </c>
+      <c r="D101" s="2">
+        <v>103.511928198818</v>
+      </c>
+      <c r="E101" s="2">
+        <v>117.2581249379449</v>
+      </c>
+      <c r="F101" s="2">
+        <v>7.059696611232228</v>
+      </c>
+      <c r="G101" s="2">
+        <v>5.807056413752337</v>
+      </c>
+      <c r="H101" s="3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8">
+      <c r="A102" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B102" s="2">
+        <v>298.2914358288205</v>
+      </c>
+      <c r="C102" s="2">
+        <v>47.16884657353162</v>
+      </c>
+      <c r="D102" s="2">
+        <v>119.399162515108</v>
+      </c>
+      <c r="E102" s="2">
+        <v>117.7262078565638</v>
+      </c>
+      <c r="F102" s="2">
+        <v>12.05913498222828</v>
+      </c>
+      <c r="G102" s="2">
+        <v>1.938083901388778</v>
+      </c>
+      <c r="H102" s="3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8">
+      <c r="A103" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B103" s="2">
+        <v>273.4501550801098</v>
+      </c>
+      <c r="C103" s="2">
+        <v>39.51949952118927</v>
+      </c>
+      <c r="D103" s="2">
+        <v>120.8711398820165</v>
+      </c>
+      <c r="E103" s="2">
+        <v>100.8949301929772</v>
+      </c>
+      <c r="F103" s="2">
+        <v>8.75364024238454</v>
+      </c>
+      <c r="G103" s="2">
+        <v>3.410945241542326</v>
+      </c>
+      <c r="H103" s="3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8">
+      <c r="A104" s="1">
+        <v>46129</v>
+      </c>
+      <c r="B104" s="2">
+        <v>320.9850380516891</v>
+      </c>
+      <c r="C104" s="2">
+        <v>43.6269740500715</v>
+      </c>
+      <c r="D104" s="2">
+        <v>133.4939823072486</v>
+      </c>
+      <c r="E104" s="2">
+        <v>108.2581891838058</v>
+      </c>
+      <c r="F104" s="2">
+        <v>17.38662732382615</v>
+      </c>
+      <c r="G104" s="2">
+        <v>18.21926518673698</v>
+      </c>
+      <c r="H104" s="3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8">
+      <c r="A105" s="1">
+        <v>46130</v>
+      </c>
+      <c r="B105" s="2">
+        <v>308.5183830143159</v>
+      </c>
+      <c r="C105" s="2">
+        <v>46.30651540866329</v>
+      </c>
+      <c r="D105" s="2">
+        <v>166.1900152229249</v>
+      </c>
+      <c r="E105" s="2">
+        <v>84.06776373089188</v>
+      </c>
+      <c r="F105" s="2">
+        <v>8.05202755873402</v>
+      </c>
+      <c r="G105" s="2">
+        <v>3.902061093101899</v>
+      </c>
+      <c r="H105" s="3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8">
+      <c r="A106" s="1">
+        <v>46131</v>
+      </c>
+      <c r="B106" s="2">
+        <v>249.7613502550125</v>
+      </c>
+      <c r="C106" s="2">
+        <v>31.50441224275364</v>
+      </c>
+      <c r="D106" s="2">
+        <v>89.46780061095126</v>
+      </c>
+      <c r="E106" s="2">
+        <v>92.31769759105312</v>
+      </c>
+      <c r="F106" s="2">
+        <v>25.69309524112278</v>
+      </c>
+      <c r="G106" s="2">
+        <v>10.77834456913173</v>
+      </c>
+      <c r="H106" s="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8">
+      <c r="A107" s="1">
+        <v>46132</v>
+      </c>
+      <c r="B107" s="2">
+        <v>289.8090406613999</v>
+      </c>
+      <c r="C107" s="2">
+        <v>42.36635189480252</v>
+      </c>
+      <c r="D107" s="2">
+        <v>129.1712352487305</v>
+      </c>
+      <c r="E107" s="2">
+        <v>107.0414793449309</v>
+      </c>
+      <c r="F107" s="2">
+        <v>7.084813880191909</v>
+      </c>
+      <c r="G107" s="2">
+        <v>4.145160292744015</v>
+      </c>
+      <c r="H107" s="3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8">
+      <c r="A108" s="1">
+        <v>46133</v>
+      </c>
+      <c r="B108" s="2">
+        <v>268.9945581863138</v>
+      </c>
+      <c r="C108" s="2">
+        <v>40.30407802194357</v>
+      </c>
+      <c r="D108" s="2">
+        <v>151.8822429773853</v>
+      </c>
+      <c r="E108" s="2">
+        <v>57.75635954093602</v>
+      </c>
+      <c r="F108" s="2">
+        <v>8.765534364117517</v>
+      </c>
+      <c r="G108" s="2">
+        <v>10.28634328193135</v>
+      </c>
+      <c r="H108" s="3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8">
+      <c r="A109" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B109" s="2">
+        <v>213.3406962682079</v>
+      </c>
+      <c r="C109" s="2">
+        <v>32.27424128419823</v>
+      </c>
+      <c r="D109" s="2">
+        <v>115.4994636634427</v>
+      </c>
+      <c r="E109" s="2">
+        <v>48.54623563612501</v>
+      </c>
+      <c r="F109" s="2">
+        <v>14.17942682902018</v>
+      </c>
+      <c r="G109" s="2">
+        <v>2.841328855421808</v>
+      </c>
+      <c r="H109" s="3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8">
+      <c r="A110" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B110" s="2">
+        <v>231.1654229627881</v>
+      </c>
+      <c r="C110" s="2">
+        <v>33.38276323295302</v>
+      </c>
+      <c r="D110" s="2">
+        <v>106.304737093548</v>
+      </c>
+      <c r="E110" s="2">
+        <v>64.60221893481082</v>
+      </c>
+      <c r="F110" s="2">
+        <v>13.08933916727702</v>
+      </c>
+      <c r="G110" s="2">
+        <v>13.78636453419924</v>
+      </c>
+      <c r="H110" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8">
+      <c r="A111" s="1">
+        <v>46136</v>
+      </c>
+      <c r="B111" s="2">
+        <v>243.5352080432605</v>
+      </c>
+      <c r="C111" s="2">
+        <v>37.10335299352805</v>
+      </c>
+      <c r="D111" s="2">
+        <v>148.7460722376282</v>
+      </c>
+      <c r="E111" s="2">
+        <v>41.9854927673522</v>
+      </c>
+      <c r="F111" s="2">
+        <v>13.08109723409017</v>
+      </c>
+      <c r="G111" s="2">
+        <v>2.619192810661884</v>
+      </c>
+      <c r="H111" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8">
+      <c r="A112" s="1">
+        <v>46137</v>
+      </c>
+      <c r="B112" s="2">
+        <v>295.7370811828081</v>
+      </c>
+      <c r="C112" s="2">
+        <v>45.03800446298387</v>
+      </c>
+      <c r="D112" s="2">
+        <v>159.6257019741647</v>
+      </c>
+      <c r="E112" s="2">
+        <v>79.94608134516412</v>
+      </c>
+      <c r="F112" s="2">
+        <v>8.576289774576823</v>
+      </c>
+      <c r="G112" s="2">
+        <v>2.551003625918594</v>
+      </c>
+      <c r="H112" s="3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8">
+      <c r="A113" s="1">
+        <v>46138</v>
+      </c>
+      <c r="B113" s="2">
+        <v>281.039459743297</v>
+      </c>
+      <c r="C113" s="2">
+        <v>42.84105554348893</v>
+      </c>
+      <c r="D113" s="2">
+        <v>97.31553551588621</v>
+      </c>
+      <c r="E113" s="2">
+        <v>133.8467120167447</v>
+      </c>
+      <c r="F113" s="2">
+        <v>2.745579155815972</v>
+      </c>
+      <c r="G113" s="2">
+        <v>4.290577511361076</v>
+      </c>
+      <c r="H113" s="3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8">
+      <c r="A114" s="1">
+        <v>46139</v>
+      </c>
+      <c r="B114" s="2">
+        <v>214.7356720573704</v>
+      </c>
+      <c r="C114" s="2">
+        <v>31.84751321550873</v>
+      </c>
+      <c r="D114" s="2">
+        <v>80.54385508432985</v>
+      </c>
+      <c r="E114" s="2">
+        <v>97.50572902141346</v>
+      </c>
+      <c r="F114" s="2">
+        <v>3.601089180840386</v>
+      </c>
+      <c r="G114" s="2">
+        <v>1.23748555527793</v>
+      </c>
+      <c r="H114" s="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8">
+      <c r="A115" s="1">
+        <v>46140</v>
+      </c>
+      <c r="B115" s="2">
+        <v>188.3966501657499</v>
+      </c>
+      <c r="C115" s="2">
+        <v>28.4410385724571</v>
+      </c>
+      <c r="D115" s="2">
+        <v>85.89948526518212</v>
+      </c>
+      <c r="E115" s="2">
+        <v>68.54402510571811</v>
+      </c>
+      <c r="F115" s="2">
+        <v>4.423320109049479</v>
+      </c>
+      <c r="G115" s="2">
+        <v>1.088781113343106</v>
+      </c>
+      <c r="H115" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8">
+      <c r="A116" s="1">
+        <v>46141</v>
+      </c>
+      <c r="B116" s="2">
+        <v>250.7527417366662</v>
+      </c>
+      <c r="C116" s="2">
+        <v>36.03463883413209</v>
+      </c>
+      <c r="D116" s="2">
+        <v>115.5841033623078</v>
+      </c>
+      <c r="E116" s="2">
+        <v>92.17480784644683</v>
+      </c>
+      <c r="F116" s="2">
+        <v>3.25470106654697</v>
+      </c>
+      <c r="G116" s="2">
+        <v>3.704490627232525</v>
+      </c>
+      <c r="H116" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8">
+      <c r="A117" s="1">
+        <v>46142</v>
+      </c>
+      <c r="B117" s="2">
+        <v>189.8929473854664</v>
+      </c>
+      <c r="C117" s="2">
+        <v>29.90951245903969</v>
+      </c>
+      <c r="D117" s="2">
+        <v>109.241959625139</v>
+      </c>
+      <c r="E117" s="2">
+        <v>49.2553244445059</v>
+      </c>
+      <c r="F117" s="2">
+        <v>0.0004016666611035665</v>
+      </c>
+      <c r="G117" s="2">
+        <v>1.485749190120647</v>
+      </c>
+      <c r="H117" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8">
+      <c r="A118" s="1">
+        <v>46143</v>
+      </c>
+      <c r="B118" s="2">
+        <v>236.9741027833154</v>
+      </c>
+      <c r="C118" s="2">
+        <v>35.30577249864737</v>
+      </c>
+      <c r="D118" s="2">
+        <v>118.939983162243</v>
+      </c>
+      <c r="E118" s="2">
+        <v>79.02687909699148</v>
+      </c>
+      <c r="F118" s="2">
+        <v>0.289986384080516</v>
+      </c>
+      <c r="G118" s="2">
+        <v>3.411481641353005</v>
+      </c>
+      <c r="H118" s="3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8">
+      <c r="A119" s="1">
+        <v>46144</v>
+      </c>
+      <c r="B119" s="2">
+        <v>287.6914919003316</v>
+      </c>
+      <c r="C119" s="2">
+        <v>45.85951106760237</v>
+      </c>
+      <c r="D119" s="2">
+        <v>168.6124217177565</v>
+      </c>
+      <c r="E119" s="2">
+        <v>68.90445611220267</v>
+      </c>
+      <c r="F119" s="2">
+        <v>1.737823571099175</v>
+      </c>
+      <c r="G119" s="2">
+        <v>2.577279431670904</v>
+      </c>
+      <c r="H119" s="3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8">
+      <c r="A120" s="1">
+        <v>46145</v>
+      </c>
+      <c r="B120" s="2">
+        <v>259.709311512347</v>
+      </c>
+      <c r="C120" s="2">
+        <v>39.46693604773945</v>
+      </c>
+      <c r="D120" s="2">
+        <v>116.7329225043021</v>
+      </c>
+      <c r="E120" s="2">
+        <v>100.732365763055</v>
+      </c>
+      <c r="F120" s="2">
+        <v>0.9525635796123081</v>
+      </c>
+      <c r="G120" s="2">
+        <v>1.824523617638172</v>
+      </c>
+      <c r="H120" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8">
+      <c r="A121" s="1">
+        <v>46146</v>
+      </c>
+      <c r="B121" s="2">
+        <v>419.1311424101785</v>
+      </c>
+      <c r="C121" s="2">
+        <v>52.99363439333108</v>
+      </c>
+      <c r="D121" s="2">
+        <v>240.5802804369272</v>
+      </c>
+      <c r="E121" s="2">
+        <v>94.28195947988786</v>
+      </c>
+      <c r="F121" s="2">
+        <v>14.12164852566189</v>
+      </c>
+      <c r="G121" s="2">
+        <v>17.15361957437048</v>
+      </c>
+      <c r="H121" s="3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8">
+      <c r="A122" s="1">
+        <v>46147</v>
+      </c>
+      <c r="B122" s="2">
+        <v>461.1700450927418</v>
+      </c>
+      <c r="C122" s="2">
+        <v>65.63128696233292</v>
+      </c>
+      <c r="D122" s="2">
+        <v>198.2021644964359</v>
+      </c>
+      <c r="E122" s="2">
+        <v>163.891013423966</v>
+      </c>
+      <c r="F122" s="2">
+        <v>9.302166808984346</v>
+      </c>
+      <c r="G122" s="2">
+        <v>24.14341340102255</v>
+      </c>
+      <c r="H122" s="3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8">
+      <c r="A123" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B123" s="2">
+        <v>466.2641320422157</v>
+      </c>
+      <c r="C123" s="2">
+        <v>62.21521133740743</v>
+      </c>
+      <c r="D123" s="2">
+        <v>198.1629329651708</v>
+      </c>
+      <c r="E123" s="2">
+        <v>148.7892066645457</v>
+      </c>
+      <c r="F123" s="2">
+        <v>20.66326173659828</v>
+      </c>
+      <c r="G123" s="2">
+        <v>36.43351933849355</v>
+      </c>
+      <c r="H123" s="3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8">
+      <c r="A124" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B124" s="2">
+        <v>443.7020187117221</v>
+      </c>
+      <c r="C124" s="2">
+        <v>57.82657413373391</v>
+      </c>
+      <c r="D124" s="2">
+        <v>251.1441129902481</v>
+      </c>
+      <c r="E124" s="2">
+        <v>83.1379683031804</v>
+      </c>
+      <c r="F124" s="2">
+        <v>18.4203873065114</v>
+      </c>
+      <c r="G124" s="2">
+        <v>33.17297597804831</v>
+      </c>
+      <c r="H124" s="3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8">
+      <c r="A125" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B125" s="2">
+        <v>480.8483295536414</v>
+      </c>
+      <c r="C125" s="2">
+        <v>58.33146480507321</v>
+      </c>
+      <c r="D125" s="2">
+        <v>258.3310568022438</v>
+      </c>
+      <c r="E125" s="2">
+        <v>99.85353925357262</v>
+      </c>
+      <c r="F125" s="2">
+        <v>9.168865032196045</v>
+      </c>
+      <c r="G125" s="2">
+        <v>55.16340366055568</v>
+      </c>
+      <c r="H125" s="3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8">
+      <c r="A126" s="1">
+        <v>46151</v>
+      </c>
+      <c r="B126" s="2">
+        <v>403.4146453784468</v>
+      </c>
+      <c r="C126" s="2">
+        <v>56.43632439278894</v>
+      </c>
+      <c r="D126" s="2">
+        <v>225.4862104357495</v>
+      </c>
+      <c r="E126" s="2">
+        <v>94.02020162944578</v>
+      </c>
+      <c r="F126" s="2">
+        <v>3.597834702067905</v>
+      </c>
+      <c r="G126" s="2">
+        <v>23.87407421839475</v>
+      </c>
+      <c r="H126" s="3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8">
+      <c r="A127" s="1">
+        <v>46152</v>
+      </c>
+      <c r="B127" s="2">
+        <v>366.7096568270566</v>
+      </c>
+      <c r="C127" s="2">
+        <v>37.82357867028978</v>
+      </c>
+      <c r="D127" s="2">
+        <v>182.1121856646157</v>
+      </c>
+      <c r="E127" s="2">
+        <v>103.3205951165822</v>
+      </c>
+      <c r="F127" s="2">
+        <v>0.5201874796549479</v>
+      </c>
+      <c r="G127" s="2">
+        <v>42.93310989591397</v>
+      </c>
+      <c r="H127" s="3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8">
+      <c r="A128" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B128" s="2">
+        <v>377.0280582178803</v>
+      </c>
+      <c r="C128" s="2">
+        <v>54.52591052108341</v>
+      </c>
+      <c r="D128" s="2">
+        <v>216.6716927455159</v>
+      </c>
+      <c r="E128" s="2">
+        <v>93.04824693571362</v>
+      </c>
+      <c r="F128" s="2">
+        <v>6.049973821640014</v>
+      </c>
+      <c r="G128" s="2">
+        <v>6.732234193927401</v>
+      </c>
+      <c r="H128" s="3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8">
+      <c r="A129" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B129" s="2">
+        <v>379.6062239715126</v>
+      </c>
+      <c r="C129" s="2">
+        <v>57.83367447672619</v>
+      </c>
+      <c r="D129" s="2">
+        <v>175.8828664412515</v>
+      </c>
+      <c r="E129" s="2">
+        <v>134.8248550862736</v>
+      </c>
+      <c r="F129" s="2">
+        <v>6.542398575428459</v>
+      </c>
+      <c r="G129" s="2">
+        <v>4.522429391832815</v>
+      </c>
+      <c r="H129" s="3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8">
+      <c r="A130" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B130" s="2">
+        <v>356.1126963547902</v>
+      </c>
+      <c r="C130" s="2">
+        <v>52.09104818314314</v>
+      </c>
+      <c r="D130" s="2">
+        <v>163.543779765487</v>
+      </c>
+      <c r="E130" s="2">
+        <v>127.1168416849027</v>
+      </c>
+      <c r="F130" s="2">
+        <v>4.55594245062934</v>
+      </c>
+      <c r="G130" s="2">
+        <v>8.805084270627962</v>
+      </c>
+      <c r="H130" s="3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8">
+      <c r="A131" s="1">
         <v>46156</v>
       </c>
-      <c r="B20" s="2">
-        <v>46.49617131621059</v>
-      </c>
-      <c r="C20" s="2">
-        <v>2.403140558203062</v>
-      </c>
-      <c r="D20" s="2">
-        <v>38.6203146943657</v>
-      </c>
-      <c r="E20" s="2">
-        <v>4.723173014207019</v>
-      </c>
-      <c r="F20" s="2">
-        <v>0</v>
-      </c>
-      <c r="G20" s="2">
-        <v>0.7495430494348209</v>
-      </c>
-      <c r="H20" s="3">
-        <v>18</v>
+      <c r="B131" s="2">
+        <v>234.388172803368</v>
+      </c>
+      <c r="C131" s="2">
+        <v>35.36008517614669</v>
+      </c>
+      <c r="D131" s="2">
+        <v>155.5257809511034</v>
+      </c>
+      <c r="E131" s="2">
+        <v>37.78273525775307</v>
+      </c>
+      <c r="F131" s="2">
+        <v>3.245013933777809</v>
+      </c>
+      <c r="G131" s="2">
+        <v>2.474557484587034</v>
+      </c>
+      <c r="H131" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8">
+      <c r="A132" s="1">
+        <v>46157</v>
+      </c>
+      <c r="B132" s="2">
+        <v>372.7857293612001</v>
+      </c>
+      <c r="C132" s="2">
+        <v>53.17792652921544</v>
+      </c>
+      <c r="D132" s="2">
+        <v>234.9279307102257</v>
+      </c>
+      <c r="E132" s="2">
+        <v>58.68878510475766</v>
+      </c>
+      <c r="F132" s="2">
+        <v>20.82498308830791</v>
+      </c>
+      <c r="G132" s="2">
+        <v>5.166103928693467</v>
+      </c>
+      <c r="H132" s="3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8">
+      <c r="A133" s="1">
+        <v>46158</v>
+      </c>
+      <c r="B133" s="2">
+        <v>44.58656913130648</v>
+      </c>
+      <c r="C133" s="2">
+        <v>2.016788872215483</v>
+      </c>
+      <c r="D133" s="2">
+        <v>36.85850997149117</v>
+      </c>
+      <c r="E133" s="2">
+        <v>4.168973335027695</v>
+      </c>
+      <c r="F133" s="2">
+        <v>0.0008799999952316285</v>
+      </c>
+      <c r="G133" s="2">
+        <v>1.541416952576902</v>
+      </c>
+      <c r="H133" s="3">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1190,13 +4128,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57F610D0-9A5B-4E92-9E94-C88108467CA7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{425149DC-E80D-4A1F-B52C-C6CDF561DE9D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4B86DF0-6B4F-4519-B2E6-5349B5B7D41E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94AFFB77-9BD3-45E5-BBFA-7889D001E992}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C4CBCFB-77EA-486C-B046-BB36FA849F25}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8DC2A8DB-4702-49ED-95E8-52EED28644BF}"/>
 </file>
--- a/sea_productive.xlsx
+++ b/sea_productive.xlsx
@@ -1588,7 +1588,7 @@
         <v>46189</v>
       </c>
       <c r="B46" s="2">
-        <v>559.9029498254058</v>
+        <v>559.9029498254057</v>
       </c>
       <c r="C46" s="2">
         <v>86.83317798834656</v>
@@ -1614,7 +1614,7 @@
         <v>46190</v>
       </c>
       <c r="B47" s="2">
-        <v>560.2161258628878</v>
+        <v>560.2161258628877</v>
       </c>
       <c r="C47" s="2">
         <v>85.99718828550824</v>
@@ -2282,13 +2282,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB6DF627-4BC2-47B9-8F2B-1843EF5B50FF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A99BB5E-09DC-40F9-8151-0E8730FE2818}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{498F09DB-363A-40EE-B24B-65082A608CA3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A1AE0BF-9F39-49B3-AA48-D3F626A05FD4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ABAA12AD-D5AE-426A-91EF-FCB02CC9495A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D60475F-62D5-4D60-9165-A97D956683BD}"/>
 </file>
--- a/sea_productive.xlsx
+++ b/sea_productive.xlsx
@@ -444,7 +444,7 @@
         <v>46145</v>
       </c>
       <c r="B2" s="2">
-        <v>56.63781269884772</v>
+        <v>55.89077435245117</v>
       </c>
       <c r="C2" s="2">
         <v>10.91819050696161</v>
@@ -459,10 +459,10 @@
         <v>0.4118199849128723</v>
       </c>
       <c r="G2" s="2">
-        <v>0.8545891811284754</v>
+        <v>0.1075508347319232</v>
       </c>
       <c r="H2" s="3">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -470,25 +470,25 @@
         <v>46146</v>
       </c>
       <c r="B3" s="2">
-        <v>414.0545019403203</v>
+        <v>413.3386083363597</v>
       </c>
       <c r="C3" s="2">
         <v>54.21702079334193</v>
       </c>
       <c r="D3" s="2">
-        <v>243.2551806651097</v>
+        <v>243.6698231686362</v>
       </c>
       <c r="E3" s="2">
-        <v>94.83616142813324</v>
+        <v>94.43755697578813</v>
       </c>
       <c r="F3" s="2">
         <v>14.12164852566189</v>
       </c>
       <c r="G3" s="2">
-        <v>7.624490528073576</v>
+        <v>6.892558872931533</v>
       </c>
       <c r="H3" s="3">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -496,25 +496,25 @@
         <v>46147</v>
       </c>
       <c r="B4" s="2">
-        <v>454.4989173647332</v>
+        <v>454.3400681990287</v>
       </c>
       <c r="C4" s="2">
         <v>67.11056335664716</v>
       </c>
       <c r="D4" s="2">
-        <v>198.9861384709386</v>
+        <v>198.5714959674121</v>
       </c>
       <c r="E4" s="2">
-        <v>167.2255314703451</v>
+        <v>166.7348309266236</v>
       </c>
       <c r="F4" s="2">
         <v>10.46814377838539</v>
       </c>
       <c r="G4" s="2">
-        <v>10.70854028841688</v>
+        <v>11.45503416996035</v>
       </c>
       <c r="H4" s="3">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -522,7 +522,7 @@
         <v>46148</v>
       </c>
       <c r="B5" s="2">
-        <v>436.6506427187338</v>
+        <v>437.276570502382</v>
       </c>
       <c r="C5" s="2">
         <v>63.46380384975009</v>
@@ -531,16 +531,16 @@
         <v>186.9585496249329</v>
       </c>
       <c r="E5" s="2">
-        <v>150.2979666419327</v>
+        <v>150.6561171919273</v>
       </c>
       <c r="F5" s="2">
         <v>21.37913979831669</v>
       </c>
       <c r="G5" s="2">
-        <v>14.55118280380136</v>
+        <v>14.81896003745496</v>
       </c>
       <c r="H5" s="3">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -548,25 +548,25 @@
         <v>46149</v>
       </c>
       <c r="B6" s="2">
-        <v>439.4210215263338</v>
+        <v>444.2742240612147</v>
       </c>
       <c r="C6" s="2">
         <v>58.67641829248932</v>
       </c>
       <c r="D6" s="2">
-        <v>266.9623615944034</v>
+        <v>270.4838541099409</v>
       </c>
       <c r="E6" s="2">
-        <v>86.33040546071199</v>
+        <v>87.93365047744578</v>
       </c>
       <c r="F6" s="2">
         <v>18.4203873065114</v>
       </c>
       <c r="G6" s="2">
-        <v>9.031448872217702</v>
+        <v>8.759913874827326</v>
       </c>
       <c r="H6" s="3">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -574,25 +574,25 @@
         <v>46150</v>
       </c>
       <c r="B7" s="2">
-        <v>445.0878839737632</v>
+        <v>450.0989330640891</v>
       </c>
       <c r="C7" s="2">
         <v>59.646116171413</v>
       </c>
       <c r="D7" s="2">
-        <v>260.7381423690957</v>
+        <v>263.237734024297</v>
       </c>
       <c r="E7" s="2">
-        <v>100.0343964777059</v>
+        <v>102.1929853049583</v>
       </c>
       <c r="F7" s="2">
         <v>9.384459751976861</v>
       </c>
       <c r="G7" s="2">
-        <v>15.28476920357181</v>
+        <v>15.63763781144387</v>
       </c>
       <c r="H7" s="3">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -600,22 +600,22 @@
         <v>46151</v>
       </c>
       <c r="B8" s="2">
-        <v>381.4133165819741</v>
+        <v>378.6972102263865</v>
       </c>
       <c r="C8" s="2">
         <v>56.43632439278894</v>
       </c>
       <c r="D8" s="2">
-        <v>222.3331687769506</v>
+        <v>221.288545715797</v>
       </c>
       <c r="E8" s="2">
-        <v>93.00997799679223</v>
+        <v>92.07241583815465</v>
       </c>
       <c r="F8" s="2">
         <v>3.597834702067905</v>
       </c>
       <c r="G8" s="2">
-        <v>6.036010713374449</v>
+        <v>5.302089577578008</v>
       </c>
       <c r="H8" s="3">
         <v>42</v>
@@ -626,22 +626,22 @@
         <v>46152</v>
       </c>
       <c r="B9" s="2">
-        <v>331.2683595132083</v>
+        <v>329.4926000411891</v>
       </c>
       <c r="C9" s="2">
-        <v>37.62513672828674</v>
+        <v>37.82357867028978</v>
       </c>
       <c r="D9" s="2">
-        <v>181.3810765262859</v>
+        <v>179.2377609757996</v>
       </c>
       <c r="E9" s="2">
-        <v>103.9610143279367</v>
+        <v>103.3205951165822</v>
       </c>
       <c r="F9" s="2">
         <v>0.5201874796549479</v>
       </c>
       <c r="G9" s="2">
-        <v>7.780944451044003</v>
+        <v>8.59047779886259</v>
       </c>
       <c r="H9" s="3">
         <v>37</v>
@@ -652,25 +652,25 @@
         <v>46153</v>
       </c>
       <c r="B10" s="2">
-        <v>384.4894239609828</v>
+        <v>379.9891656656123</v>
       </c>
       <c r="C10" s="2">
-        <v>56.06407076676687</v>
+        <v>55.86562882476382</v>
       </c>
       <c r="D10" s="2">
-        <v>221.7592152312357</v>
+        <v>218.9260696721367</v>
       </c>
       <c r="E10" s="2">
-        <v>96.15483164238434</v>
+        <v>94.58222416689826</v>
       </c>
       <c r="F10" s="2">
         <v>6.049973821640014</v>
       </c>
       <c r="G10" s="2">
-        <v>4.461332498955954</v>
+        <v>4.565269180173572</v>
       </c>
       <c r="H10" s="3">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -678,7 +678,7 @@
         <v>46154</v>
       </c>
       <c r="B11" s="2">
-        <v>377.0187723600243</v>
+        <v>376.3494728958648</v>
       </c>
       <c r="C11" s="2">
         <v>57.83367447672619</v>
@@ -687,16 +687,16 @@
         <v>174.4059461533775</v>
       </c>
       <c r="E11" s="2">
-        <v>135.3743706536293</v>
+        <v>134.8248550862736</v>
       </c>
       <c r="F11" s="2">
         <v>6.542398575428459</v>
       </c>
       <c r="G11" s="2">
-        <v>2.86238250086291</v>
+        <v>2.742598604059054</v>
       </c>
       <c r="H11" s="3">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -704,25 +704,25 @@
         <v>46155</v>
       </c>
       <c r="B12" s="2">
-        <v>362.9539499442398</v>
+        <v>363.0605671824302</v>
       </c>
       <c r="C12" s="2">
         <v>53.32550095078018</v>
       </c>
       <c r="D12" s="2">
-        <v>167.4918061768879</v>
+        <v>167.1647595022655</v>
       </c>
       <c r="E12" s="2">
-        <v>129.483646106513</v>
+        <v>130.0182619517959</v>
       </c>
       <c r="F12" s="2">
         <v>4.55594245062934</v>
       </c>
       <c r="G12" s="2">
-        <v>8.097054259429376</v>
+        <v>7.996102326959371</v>
       </c>
       <c r="H12" s="3">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -730,25 +730,25 @@
         <v>46156</v>
       </c>
       <c r="B13" s="2">
-        <v>243.548394508904</v>
+        <v>243.4188689459819</v>
       </c>
       <c r="C13" s="2">
         <v>36.57011935662892</v>
       </c>
       <c r="D13" s="2">
-        <v>160.82266568633</v>
+        <v>161.1497123609525</v>
       </c>
       <c r="E13" s="2">
-        <v>38.32825414678289</v>
+        <v>38.28427192483511</v>
       </c>
       <c r="F13" s="2">
         <v>5.004319489333365</v>
       </c>
       <c r="G13" s="2">
-        <v>2.823035829828845</v>
+        <v>2.410445814232031</v>
       </c>
       <c r="H13" s="3">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -756,7 +756,7 @@
         <v>46157</v>
       </c>
       <c r="B14" s="2">
-        <v>372.4060935061414</v>
+        <v>371.5868649025664</v>
       </c>
       <c r="C14" s="2">
         <v>53.17792652921544</v>
@@ -765,16 +765,16 @@
         <v>234.9011579322246</v>
       </c>
       <c r="E14" s="2">
-        <v>58.92634453986034</v>
+        <v>58.68878510475766</v>
       </c>
       <c r="F14" s="2">
         <v>20.82498308830791</v>
       </c>
       <c r="G14" s="2">
-        <v>4.57568141653306</v>
+        <v>3.994012248060769</v>
       </c>
       <c r="H14" s="3">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -782,25 +782,25 @@
         <v>46158</v>
       </c>
       <c r="B15" s="2">
-        <v>437.8438536056379</v>
+        <v>437.8700297472708</v>
       </c>
       <c r="C15" s="2">
         <v>61.91067844582928</v>
       </c>
       <c r="D15" s="2">
-        <v>236.7376107286745</v>
+        <v>236.6874654512273</v>
       </c>
       <c r="E15" s="2">
-        <v>124.37217670492</v>
+        <v>124.667381695095</v>
       </c>
       <c r="F15" s="2">
         <v>10.49331111394697</v>
       </c>
       <c r="G15" s="2">
-        <v>4.330076612267229</v>
+        <v>4.111193041172292</v>
       </c>
       <c r="H15" s="3">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -808,22 +808,22 @@
         <v>46159</v>
       </c>
       <c r="B16" s="2">
-        <v>421.6484577972752</v>
+        <v>421.9364205232325</v>
       </c>
       <c r="C16" s="2">
         <v>61.63815071587761</v>
       </c>
       <c r="D16" s="2">
-        <v>226.4644382859746</v>
+        <v>226.5145835634218</v>
       </c>
       <c r="E16" s="2">
-        <v>109.483779323101</v>
+        <v>109.0880901545949</v>
       </c>
       <c r="F16" s="2">
         <v>19.19578698227803</v>
       </c>
       <c r="G16" s="2">
-        <v>4.866302490043971</v>
+        <v>5.499809107060234</v>
       </c>
       <c r="H16" s="3">
         <v>47</v>
@@ -834,25 +834,25 @@
         <v>46160</v>
       </c>
       <c r="B17" s="2">
-        <v>457.3327171403309</v>
+        <v>459.8057927140402</v>
       </c>
       <c r="C17" s="2">
         <v>65.02296937387851</v>
       </c>
       <c r="D17" s="2">
-        <v>238.34538109531</v>
+        <v>239.0683241512047</v>
       </c>
       <c r="E17" s="2">
-        <v>141.3581021924457</v>
+        <v>141.9770963627405</v>
       </c>
       <c r="F17" s="2">
         <v>8.453966156178051</v>
       </c>
       <c r="G17" s="2">
-        <v>4.152298322518667</v>
+        <v>5.283436670038435</v>
       </c>
       <c r="H17" s="3">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -860,25 +860,25 @@
         <v>46161</v>
       </c>
       <c r="B18" s="2">
-        <v>443.2927685417028</v>
+        <v>440.7398888487245</v>
       </c>
       <c r="C18" s="2">
         <v>64.94705421076881</v>
       </c>
       <c r="D18" s="2">
-        <v>282.9677019663611</v>
+        <v>282.2790075184198</v>
       </c>
       <c r="E18" s="2">
-        <v>85.69119264836941</v>
+        <v>85.34774236939847</v>
       </c>
       <c r="F18" s="2">
         <v>4.484815831647979</v>
       </c>
       <c r="G18" s="2">
-        <v>5.202003884555565</v>
+        <v>3.681268918489416</v>
       </c>
       <c r="H18" s="3">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -886,25 +886,25 @@
         <v>46162</v>
       </c>
       <c r="B19" s="2">
-        <v>468.4392237278178</v>
+        <v>468.8858050986897</v>
       </c>
       <c r="C19" s="2">
         <v>63.38425459636582</v>
       </c>
       <c r="D19" s="2">
-        <v>285.0690337274069</v>
+        <v>284.9717917908573</v>
       </c>
       <c r="E19" s="2">
-        <v>101.5070158561919</v>
+        <v>101.1591803078043</v>
       </c>
       <c r="F19" s="2">
-        <v>12.30370622899797</v>
+        <v>12.24100789441003</v>
       </c>
       <c r="G19" s="2">
-        <v>6.175213318855191</v>
+        <v>7.129570509252242</v>
       </c>
       <c r="H19" s="3">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -912,25 +912,25 @@
         <v>46163</v>
       </c>
       <c r="B20" s="2">
-        <v>477.9843499757846</v>
+        <v>478.6751132961363</v>
       </c>
       <c r="C20" s="2">
         <v>61.96484072920349</v>
       </c>
       <c r="D20" s="2">
-        <v>284.9575382738726</v>
+        <v>285.0406335481339</v>
       </c>
       <c r="E20" s="2">
-        <v>110.0205801740537</v>
+        <v>110.4918618327959</v>
       </c>
       <c r="F20" s="2">
-        <v>15.30466214931674</v>
+        <v>15.36736048390468</v>
       </c>
       <c r="G20" s="2">
-        <v>5.736728649338087</v>
+        <v>5.810416702098316</v>
       </c>
       <c r="H20" s="3">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -938,25 +938,25 @@
         <v>46164</v>
       </c>
       <c r="B21" s="2">
-        <v>530.4697181483027</v>
+        <v>529.6431565014439</v>
       </c>
       <c r="C21" s="2">
         <v>71.11584687573215</v>
       </c>
       <c r="D21" s="2">
-        <v>293.2532805327036</v>
+        <v>293.4078935867672</v>
       </c>
       <c r="E21" s="2">
-        <v>144.9508134031213</v>
+        <v>144.5266048049844</v>
       </c>
       <c r="F21" s="2">
         <v>9.257010967466567</v>
       </c>
       <c r="G21" s="2">
-        <v>11.89276636927906</v>
+        <v>11.33580026649352</v>
       </c>
       <c r="H21" s="3">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -964,25 +964,25 @@
         <v>46165</v>
       </c>
       <c r="B22" s="2">
-        <v>464.3598031623206</v>
+        <v>468.19422290011</v>
       </c>
       <c r="C22" s="2">
         <v>64.13465089950297</v>
       </c>
       <c r="D22" s="2">
-        <v>259.7757710188255</v>
+        <v>263.910166033138</v>
       </c>
       <c r="E22" s="2">
-        <v>124.7735762169047</v>
+        <v>125.0144075967951</v>
       </c>
       <c r="F22" s="2">
         <v>9.230215831995011</v>
       </c>
       <c r="G22" s="2">
-        <v>6.445589195092519</v>
+        <v>5.904782538678911</v>
       </c>
       <c r="H22" s="3">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -990,25 +990,25 @@
         <v>46166</v>
       </c>
       <c r="B23" s="2">
-        <v>429.5998329424879</v>
+        <v>425.8899093005413</v>
       </c>
       <c r="C23" s="2">
         <v>60.45049316045311</v>
       </c>
       <c r="D23" s="2">
-        <v>260.8247757598447</v>
+        <v>256.6903807455322</v>
       </c>
       <c r="E23" s="2">
-        <v>97.54833170731862</v>
+        <v>97.38895559310913</v>
       </c>
       <c r="F23" s="2">
         <v>7.015295081337293</v>
       </c>
       <c r="G23" s="2">
-        <v>3.760937233534124</v>
+        <v>4.344784720109569</v>
       </c>
       <c r="H23" s="3">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1016,7 +1016,7 @@
         <v>46167</v>
       </c>
       <c r="B24" s="2">
-        <v>449.9170330949004</v>
+        <v>450.3463289314219</v>
       </c>
       <c r="C24" s="2">
         <v>65.20023656696081</v>
@@ -1025,16 +1025,16 @@
         <v>264.1583806956394</v>
       </c>
       <c r="E24" s="2">
-        <v>104.461828720433</v>
+        <v>104.6142923324597</v>
       </c>
       <c r="F24" s="2">
         <v>12.33950681063864</v>
       </c>
       <c r="G24" s="2">
-        <v>3.757080301228497</v>
+        <v>4.033912525723378</v>
       </c>
       <c r="H24" s="3">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1042,7 +1042,7 @@
         <v>46168</v>
       </c>
       <c r="B25" s="2">
-        <v>425.2713941824322</v>
+        <v>424.5010291889859</v>
       </c>
       <c r="C25" s="2">
         <v>64.09616127169795</v>
@@ -1051,16 +1051,16 @@
         <v>228.0174184114714</v>
       </c>
       <c r="E25" s="2">
-        <v>116.3346559348785</v>
+        <v>115.9387362028907</v>
       </c>
       <c r="F25" s="2">
         <v>12.60105107221339</v>
       </c>
       <c r="G25" s="2">
-        <v>4.222107492171021</v>
+        <v>3.847662230712465</v>
       </c>
       <c r="H25" s="3">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1068,7 +1068,7 @@
         <v>46169</v>
       </c>
       <c r="B26" s="2">
-        <v>421.795273984741</v>
+        <v>422.7831606380186</v>
       </c>
       <c r="C26" s="2">
         <v>59.70068479498227</v>
@@ -1077,16 +1077,16 @@
         <v>230.6331180820242</v>
       </c>
       <c r="E26" s="2">
-        <v>112.8740993396772</v>
+        <v>113.1952037920223</v>
       </c>
       <c r="F26" s="2">
         <v>5.595605574448903</v>
       </c>
       <c r="G26" s="2">
-        <v>12.99176619360844</v>
+        <v>13.65854839454095</v>
       </c>
       <c r="H26" s="3">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1094,7 +1094,7 @@
         <v>46170</v>
       </c>
       <c r="B27" s="2">
-        <v>441.3439338848243</v>
+        <v>441.1834608295146</v>
       </c>
       <c r="C27" s="2">
         <v>66.62872838914394</v>
@@ -1103,13 +1103,13 @@
         <v>198.5628028688249</v>
       </c>
       <c r="E27" s="2">
-        <v>146.9776370322704</v>
+        <v>146.8064159222444</v>
       </c>
       <c r="F27" s="2">
         <v>25.66743728227086</v>
       </c>
       <c r="G27" s="2">
-        <v>3.507328312314219</v>
+        <v>3.518076367030541</v>
       </c>
       <c r="H27" s="3">
         <v>50</v>
@@ -1120,25 +1120,25 @@
         <v>46171</v>
       </c>
       <c r="B28" s="2">
-        <v>440.0035668998046</v>
+        <v>439.7450916358911</v>
       </c>
       <c r="C28" s="2">
         <v>67.68836898499065</v>
       </c>
       <c r="D28" s="2">
-        <v>196.5094897181706</v>
+        <v>196.1088091761785</v>
       </c>
       <c r="E28" s="2">
-        <v>146.5159403079831</v>
+        <v>146.9072044740866</v>
       </c>
       <c r="F28" s="2">
         <v>25.59759373386701</v>
       </c>
       <c r="G28" s="2">
-        <v>3.692174154793223</v>
+        <v>3.443115266768469</v>
       </c>
       <c r="H28" s="3">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1146,22 +1146,22 @@
         <v>46172</v>
       </c>
       <c r="B29" s="2">
-        <v>431.5727150983071</v>
+        <v>430.3435647940426</v>
       </c>
       <c r="C29" s="2">
         <v>65.43556219644017</v>
       </c>
       <c r="D29" s="2">
-        <v>174.1269446700397</v>
+        <v>174.5276252120319</v>
       </c>
       <c r="E29" s="2">
-        <v>165.3394317207938</v>
+        <v>164.1210275519099</v>
       </c>
       <c r="F29" s="2">
         <v>23.22854289551576</v>
       </c>
       <c r="G29" s="2">
-        <v>3.442233615517616</v>
+        <v>3.030806938144896</v>
       </c>
       <c r="H29" s="3">
         <v>48</v>
@@ -1172,7 +1172,7 @@
         <v>46173</v>
       </c>
       <c r="B30" s="2">
-        <v>377.4449796525471</v>
+        <v>377.8219960417847</v>
       </c>
       <c r="C30" s="2">
         <v>54.52546137109399</v>
@@ -1181,16 +1181,16 @@
         <v>125.5399093836711</v>
       </c>
       <c r="E30" s="2">
-        <v>189.7216624881824</v>
+        <v>189.6331005358034</v>
       </c>
       <c r="F30" s="2">
         <v>5.171210860212644</v>
       </c>
       <c r="G30" s="2">
-        <v>2.486735549387005</v>
+        <v>2.952313891003529</v>
       </c>
       <c r="H30" s="3">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1198,25 +1198,25 @@
         <v>46174</v>
       </c>
       <c r="B31" s="2">
-        <v>342.1178030184351</v>
+        <v>341.2375304889125</v>
       </c>
       <c r="C31" s="2">
         <v>51.14938748227225</v>
       </c>
       <c r="D31" s="2">
-        <v>133.9718404052976</v>
+        <v>133.8724517910669</v>
       </c>
       <c r="E31" s="2">
-        <v>152.6235281613505</v>
+        <v>152.2576814675698</v>
       </c>
       <c r="F31" s="2">
         <v>1.241344733668698</v>
       </c>
       <c r="G31" s="2">
-        <v>3.131702235846056</v>
+        <v>2.716665014334851</v>
       </c>
       <c r="H31" s="3">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1224,25 +1224,25 @@
         <v>46175</v>
       </c>
       <c r="B32" s="2">
-        <v>372.5990264993968</v>
+        <v>374.5122915462467</v>
       </c>
       <c r="C32" s="2">
         <v>54.4082614989082</v>
       </c>
       <c r="D32" s="2">
-        <v>126.4727543268705</v>
+        <v>126.5721429411011</v>
       </c>
       <c r="E32" s="2">
-        <v>179.9391667378983</v>
+        <v>181.0926276055682</v>
       </c>
       <c r="F32" s="2">
         <v>7.361756133900748</v>
       </c>
       <c r="G32" s="2">
-        <v>4.417087801819046</v>
+        <v>5.07750336676836</v>
       </c>
       <c r="H32" s="3">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1250,7 +1250,7 @@
         <v>46176</v>
       </c>
       <c r="B33" s="2">
-        <v>429.4029575993164</v>
+        <v>434.0226809536792</v>
       </c>
       <c r="C33" s="2">
         <v>67.42696238872905</v>
@@ -1259,16 +1259,16 @@
         <v>170.2548987122255</v>
       </c>
       <c r="E33" s="2">
-        <v>180.7911403011117</v>
+        <v>180.4964816910856</v>
       </c>
       <c r="F33" s="2">
-        <v>8.878907595690753</v>
+        <v>13.60963594855534</v>
       </c>
       <c r="G33" s="2">
-        <v>2.051048601559467</v>
+        <v>2.234702213083704</v>
       </c>
       <c r="H33" s="3">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1276,22 +1276,22 @@
         <v>46177</v>
       </c>
       <c r="B34" s="2">
-        <v>468.4208662372426</v>
+        <v>468.3330873585754</v>
       </c>
       <c r="C34" s="2">
         <v>71.60701902108887</v>
       </c>
       <c r="D34" s="2">
-        <v>156.3280899901538</v>
+        <v>156.5192188862313</v>
       </c>
       <c r="E34" s="2">
-        <v>235.9033871833856</v>
+        <v>235.8476308032249</v>
       </c>
       <c r="F34" s="2">
         <v>2.529644486755133</v>
       </c>
       <c r="G34" s="2">
-        <v>2.052725555859247</v>
+        <v>1.829574161275135</v>
       </c>
       <c r="H34" s="3">
         <v>53</v>
@@ -1302,25 +1302,25 @@
         <v>46178</v>
       </c>
       <c r="B35" s="2">
-        <v>456.5394617110356</v>
+        <v>455.0873055720526</v>
       </c>
       <c r="C35" s="2">
         <v>66.41595884060021</v>
       </c>
       <c r="D35" s="2">
-        <v>174.6613052953757</v>
+        <v>173.6225694369087</v>
       </c>
       <c r="E35" s="2">
-        <v>208.0475139563779</v>
+        <v>207.5402478354673</v>
       </c>
       <c r="F35" s="2">
         <v>3.752658105542262</v>
       </c>
       <c r="G35" s="2">
-        <v>3.662025513139605</v>
+        <v>3.755871353534102</v>
       </c>
       <c r="H35" s="3">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1328,25 +1328,25 @@
         <v>46179</v>
       </c>
       <c r="B36" s="2">
-        <v>575.6325700216096</v>
+        <v>576.2215892271137</v>
       </c>
       <c r="C36" s="2">
         <v>83.97443571782151</v>
       </c>
       <c r="D36" s="2">
-        <v>332.1799317447709</v>
+        <v>331.6509128900734</v>
       </c>
       <c r="E36" s="2">
-        <v>140.9357109232718</v>
+        <v>142.2005581498782</v>
       </c>
       <c r="F36" s="2">
         <v>15.52388052582741</v>
       </c>
       <c r="G36" s="2">
-        <v>3.018611109917984</v>
+        <v>2.871801943513047</v>
       </c>
       <c r="H36" s="3">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1354,25 +1354,25 @@
         <v>46180</v>
       </c>
       <c r="B37" s="2">
-        <v>453.1814693303385</v>
+        <v>454.6577168097244</v>
       </c>
       <c r="C37" s="2">
         <v>66.66324131687897</v>
       </c>
       <c r="D37" s="2">
-        <v>307.6634653138374</v>
+        <v>309.0163872378987</v>
       </c>
       <c r="E37" s="2">
-        <v>65.31585545734812</v>
+        <v>65.37228878977812</v>
       </c>
       <c r="F37" s="2">
         <v>9.39727887502975</v>
       </c>
       <c r="G37" s="2">
-        <v>4.141628367244266</v>
+        <v>4.208520590138829</v>
       </c>
       <c r="H37" s="3">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1380,22 +1380,22 @@
         <v>46181</v>
       </c>
       <c r="B38" s="2">
-        <v>527.9421818973805</v>
+        <v>527.8267796703364</v>
       </c>
       <c r="C38" s="2">
         <v>79.45765820018249</v>
       </c>
       <c r="D38" s="2">
-        <v>344.1204681872478</v>
+        <v>344.141261246981</v>
       </c>
       <c r="E38" s="2">
-        <v>90.9126854888774</v>
+        <v>90.82284771722327</v>
       </c>
       <c r="F38" s="2">
         <v>11.27943529278868</v>
       </c>
       <c r="G38" s="2">
-        <v>2.171934728284056</v>
+        <v>2.125577213160901</v>
       </c>
       <c r="H38" s="3">
         <v>59</v>
@@ -1406,25 +1406,25 @@
         <v>46182</v>
       </c>
       <c r="B39" s="2">
-        <v>461.5870980743593</v>
+        <v>466.1924222558258</v>
       </c>
       <c r="C39" s="2">
-        <v>61.04306413347315</v>
+        <v>61.27560801721074</v>
       </c>
       <c r="D39" s="2">
-        <v>306.6287070725395</v>
+        <v>310.0753143031424</v>
       </c>
       <c r="E39" s="2">
-        <v>87.87540693110709</v>
+        <v>88.55108554315055</v>
       </c>
       <c r="F39" s="2">
         <v>1.617553892218404</v>
       </c>
       <c r="G39" s="2">
-        <v>4.422366045021142</v>
+        <v>4.672860500103691</v>
       </c>
       <c r="H39" s="3">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1432,25 +1432,25 @@
         <v>46183</v>
       </c>
       <c r="B40" s="2">
-        <v>436.0672282424441</v>
+        <v>432.1338837918933</v>
       </c>
       <c r="C40" s="2">
-        <v>67.17203577347591</v>
+        <v>66.93949188973832</v>
       </c>
       <c r="D40" s="2">
-        <v>297.6579666916999</v>
+        <v>294.5641425195151</v>
       </c>
       <c r="E40" s="2">
-        <v>62.56852907133754</v>
+        <v>62.06843795234285</v>
       </c>
       <c r="F40" s="2">
         <v>4.642064766022894</v>
       </c>
       <c r="G40" s="2">
-        <v>4.026631939907869</v>
+        <v>3.91974666427407</v>
       </c>
       <c r="H40" s="3">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1458,22 +1458,22 @@
         <v>46184</v>
       </c>
       <c r="B41" s="2">
-        <v>554.3957433592218</v>
+        <v>553.5415055935437</v>
       </c>
       <c r="C41" s="2">
         <v>84.05988391743533</v>
       </c>
       <c r="D41" s="2">
-        <v>383.4395459154075</v>
+        <v>382.6983767567899</v>
       </c>
       <c r="E41" s="2">
-        <v>72.43549136207542</v>
+        <v>72.323165532394</v>
       </c>
       <c r="F41" s="2">
         <v>9.764884691110089</v>
       </c>
       <c r="G41" s="2">
-        <v>4.695937473193432</v>
+        <v>4.69519469581441</v>
       </c>
       <c r="H41" s="3">
         <v>62</v>
@@ -1484,25 +1484,25 @@
         <v>46185</v>
       </c>
       <c r="B42" s="2">
-        <v>511.2165958997122</v>
+        <v>511.1338158756009</v>
       </c>
       <c r="C42" s="2">
         <v>76.53958491009453</v>
       </c>
       <c r="D42" s="2">
-        <v>389.137493228644</v>
+        <v>389.2051337663298</v>
       </c>
       <c r="E42" s="2">
-        <v>41.75982220377359</v>
+        <v>41.84944608815015</v>
       </c>
       <c r="F42" s="2">
         <v>0.3350302833980984</v>
       </c>
       <c r="G42" s="2">
-        <v>3.444665273802045</v>
+        <v>3.204620827628403</v>
       </c>
       <c r="H42" s="3">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1510,25 +1510,25 @@
         <v>46186</v>
       </c>
       <c r="B43" s="2">
-        <v>556.0023630160824</v>
+        <v>556.0549677464932</v>
       </c>
       <c r="C43" s="2">
         <v>80.51038289707179</v>
       </c>
       <c r="D43" s="2">
-        <v>422.8416566389881</v>
+        <v>423.0944924806968</v>
       </c>
       <c r="E43" s="2">
-        <v>39.20157142944893</v>
+        <v>38.94095670860106</v>
       </c>
       <c r="F43" s="2">
         <v>9.53586372671028</v>
       </c>
       <c r="G43" s="2">
-        <v>3.912888323863347</v>
+        <v>3.973271933413214</v>
       </c>
       <c r="H43" s="3">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -1536,25 +1536,25 @@
         <v>46187</v>
       </c>
       <c r="B44" s="2">
-        <v>594.3410389521069</v>
+        <v>595.9186403420085</v>
       </c>
       <c r="C44" s="2">
         <v>88.09860914289123</v>
       </c>
       <c r="D44" s="2">
-        <v>415.5397509348841</v>
+        <v>417.0944159437503</v>
       </c>
       <c r="E44" s="2">
-        <v>69.30273362259898</v>
+        <v>69.580570844089</v>
       </c>
       <c r="F44" s="2">
         <v>17.2234505489303</v>
       </c>
       <c r="G44" s="2">
-        <v>4.176008591691239</v>
+        <v>3.921107751236608</v>
       </c>
       <c r="H44" s="3">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -1562,25 +1562,25 @@
         <v>46188</v>
       </c>
       <c r="B45" s="2">
-        <v>692.5029946091925</v>
+        <v>690.6648354301507</v>
       </c>
       <c r="C45" s="2">
         <v>104.0308738398839</v>
       </c>
       <c r="D45" s="2">
-        <v>490.401674675146</v>
+        <v>488.5516804960528</v>
       </c>
       <c r="E45" s="2">
-        <v>81.58293862534079</v>
+        <v>81.48068223654408</v>
       </c>
       <c r="F45" s="2">
         <v>11.34252719957795</v>
       </c>
       <c r="G45" s="2">
-        <v>5.144980269243889</v>
+        <v>5.259071658091981</v>
       </c>
       <c r="H45" s="3">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -1588,22 +1588,22 @@
         <v>46189</v>
       </c>
       <c r="B46" s="2">
-        <v>559.9029498254057</v>
+        <v>560.5004015058905</v>
       </c>
       <c r="C46" s="2">
         <v>86.83317798834656</v>
       </c>
       <c r="D46" s="2">
-        <v>390.6575794694971</v>
+        <v>390.9777167032312</v>
       </c>
       <c r="E46" s="2">
-        <v>68.22081553100553</v>
+        <v>68.53269914294953</v>
       </c>
       <c r="F46" s="2">
         <v>9.254956585880782</v>
       </c>
       <c r="G46" s="2">
-        <v>4.936420250675744</v>
+        <v>4.901851085482372</v>
       </c>
       <c r="H46" s="3">
         <v>64</v>
@@ -1614,25 +1614,25 @@
         <v>46190</v>
       </c>
       <c r="B47" s="2">
-        <v>560.2161258628877</v>
+        <v>559.2741983800129</v>
       </c>
       <c r="C47" s="2">
         <v>85.99718828550824</v>
       </c>
       <c r="D47" s="2">
-        <v>339.730543201532</v>
+        <v>339.6435470827745</v>
       </c>
       <c r="E47" s="2">
-        <v>108.3978219571081</v>
+        <v>108.0865672339947</v>
       </c>
       <c r="F47" s="2">
         <v>22.68011492705121</v>
       </c>
       <c r="G47" s="2">
-        <v>3.410457491688172</v>
+        <v>2.866780850684219</v>
       </c>
       <c r="H47" s="3">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -1640,25 +1640,25 @@
         <v>46191</v>
       </c>
       <c r="B48" s="2">
-        <v>583.6353955855066</v>
+        <v>584.2865864060664</v>
       </c>
       <c r="C48" s="2">
         <v>88.57013395031862</v>
       </c>
       <c r="D48" s="2">
-        <v>355.2978627800098</v>
+        <v>355.4164097226147</v>
       </c>
       <c r="E48" s="2">
-        <v>112.9148320098283</v>
+        <v>112.9093931214491</v>
       </c>
       <c r="F48" s="2">
         <v>21.10650358147091</v>
       </c>
       <c r="G48" s="2">
-        <v>5.744555486158157</v>
+        <v>6.282638252492373</v>
       </c>
       <c r="H48" s="3">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -1666,25 +1666,25 @@
         <v>46192</v>
       </c>
       <c r="B49" s="2">
-        <v>572.777934636923</v>
+        <v>572.4935504562845</v>
       </c>
       <c r="C49" s="2">
         <v>86.46528525314032</v>
       </c>
       <c r="D49" s="2">
-        <v>378.4277838708023</v>
+        <v>378.204789423518</v>
       </c>
       <c r="E49" s="2">
-        <v>85.12219067882333</v>
+        <v>85.02483207046157</v>
       </c>
       <c r="F49" s="2">
         <v>19.35815287135541</v>
       </c>
       <c r="G49" s="2">
-        <v>3.404521962801615</v>
+        <v>3.440490837809112</v>
       </c>
       <c r="H49" s="3">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -1692,25 +1692,25 @@
         <v>46193</v>
       </c>
       <c r="B50" s="2">
-        <v>503.3038891262024</v>
+        <v>503.1755077418065</v>
       </c>
       <c r="C50" s="2">
         <v>74.89360260545189</v>
       </c>
       <c r="D50" s="2">
-        <v>320.5034032364572</v>
+        <v>320.7408593504845</v>
       </c>
       <c r="E50" s="2">
-        <v>94.65212384854236</v>
+        <v>94.32564661649677</v>
       </c>
       <c r="F50" s="2">
         <v>9.558529440079679</v>
       </c>
       <c r="G50" s="2">
-        <v>3.696229995671246</v>
+        <v>3.656869729293717</v>
       </c>
       <c r="H50" s="3">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -1718,25 +1718,25 @@
         <v>46194</v>
       </c>
       <c r="B51" s="2">
-        <v>637.4616176414477</v>
+        <v>637.3905051625652</v>
       </c>
       <c r="C51" s="2">
         <v>95.90632836029205</v>
       </c>
       <c r="D51" s="2">
-        <v>336.2911864768345</v>
+        <v>336.3849373302074</v>
       </c>
       <c r="E51" s="2">
-        <v>194.8916807792933</v>
+        <v>195.2003307908026</v>
       </c>
       <c r="F51" s="2">
         <v>6.734717848350605</v>
       </c>
       <c r="G51" s="2">
-        <v>3.637704176677184</v>
+        <v>3.164190832912508</v>
       </c>
       <c r="H51" s="3">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -1744,25 +1744,25 @@
         <v>46195</v>
       </c>
       <c r="B52" s="2">
-        <v>736.1351018212148</v>
+        <v>734.3007544983274</v>
       </c>
       <c r="C52" s="2">
-        <v>110.078755646944</v>
+        <v>111.0390040117502</v>
       </c>
       <c r="D52" s="2">
-        <v>491.135043491503</v>
+        <v>490.1270887461773</v>
       </c>
       <c r="E52" s="2">
-        <v>112.7280878632122</v>
+        <v>112.643346468769</v>
       </c>
       <c r="F52" s="2">
-        <v>13.62300844991373</v>
+        <v>11.41097001132866</v>
       </c>
       <c r="G52" s="2">
-        <v>8.570206369641754</v>
+        <v>9.080345260302225</v>
       </c>
       <c r="H52" s="3">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -1770,25 +1770,25 @@
         <v>46196</v>
       </c>
       <c r="B53" s="2">
-        <v>611.1453758021894</v>
+        <v>611.2288515404896</v>
       </c>
       <c r="C53" s="2">
-        <v>92.84357877842199</v>
+        <v>93.03504790819298</v>
       </c>
       <c r="D53" s="2">
-        <v>397.4705841158972</v>
+        <v>398.3756868967559</v>
       </c>
       <c r="E53" s="2">
-        <v>108.2327223167217</v>
+        <v>108.4273350974648</v>
       </c>
       <c r="F53" s="2">
-        <v>8.341949476699034</v>
+        <v>7.461677469246918</v>
       </c>
       <c r="G53" s="2">
-        <v>4.256541114449501</v>
+        <v>3.929104168828991</v>
       </c>
       <c r="H53" s="3">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -1796,25 +1796,25 @@
         <v>46197</v>
       </c>
       <c r="B54" s="2">
-        <v>640.0146139002602</v>
+        <v>640.7906935729511</v>
       </c>
       <c r="C54" s="2">
-        <v>95.09286527998745</v>
+        <v>94.7467027723872</v>
       </c>
       <c r="D54" s="2">
-        <v>392.6886445068578</v>
+        <v>392.5012989544134</v>
       </c>
       <c r="E54" s="2">
-        <v>137.0910299544075</v>
+        <v>137.0982543977968</v>
       </c>
       <c r="F54" s="2">
-        <v>9.008651915639639</v>
+        <v>9.790704373402727</v>
       </c>
       <c r="G54" s="2">
-        <v>6.133422243367725</v>
+        <v>6.653733074950934</v>
       </c>
       <c r="H54" s="3">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -1822,25 +1822,25 @@
         <v>46198</v>
       </c>
       <c r="B55" s="2">
-        <v>659.2259646965367</v>
+        <v>654.6555003750542</v>
       </c>
       <c r="C55" s="2">
-        <v>100.6343098697671</v>
+        <v>99.82875488279022</v>
       </c>
       <c r="D55" s="2">
-        <v>347.4873515786546</v>
+        <v>348.2091718366892</v>
       </c>
       <c r="E55" s="2">
-        <v>196.7139203434934</v>
+        <v>196.0954206308805</v>
       </c>
       <c r="F55" s="2">
-        <v>10.9691101436317</v>
+        <v>7.112393305516905</v>
       </c>
       <c r="G55" s="2">
-        <v>3.397541928038829</v>
+        <v>3.386028886226316</v>
       </c>
       <c r="H55" s="3">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -1848,25 +1848,25 @@
         <v>46199</v>
       </c>
       <c r="B56" s="2">
-        <v>576.1092459827729</v>
+        <v>572.4179709932462</v>
       </c>
       <c r="C56" s="2">
         <v>86.65318611479827</v>
       </c>
       <c r="D56" s="2">
-        <v>365.4194858072626</v>
+        <v>363.1631280462061</v>
       </c>
       <c r="E56" s="2">
-        <v>115.7374690370365</v>
+        <v>115.639536789517</v>
       </c>
       <c r="F56" s="2">
         <v>3.566435883757141</v>
       </c>
       <c r="G56" s="2">
-        <v>4.732669139918354</v>
+        <v>3.395684158967601</v>
       </c>
       <c r="H56" s="3">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -1874,25 +1874,25 @@
         <v>46200</v>
       </c>
       <c r="B57" s="2">
-        <v>526.6533368890482</v>
+        <v>541.2471974875341</v>
       </c>
       <c r="C57" s="2">
         <v>76.5272191665513</v>
       </c>
       <c r="D57" s="2">
-        <v>380.4822699995916</v>
+        <v>387.7153775086562</v>
       </c>
       <c r="E57" s="2">
-        <v>56.47948424131348</v>
+        <v>58.57090567260822</v>
       </c>
       <c r="F57" s="2">
-        <v>9.511145702368683</v>
+        <v>13.45675266308917</v>
       </c>
       <c r="G57" s="2">
-        <v>3.652478612552708</v>
+        <v>4.976203309958801</v>
       </c>
       <c r="H57" s="3">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -1900,25 +1900,25 @@
         <v>46201</v>
       </c>
       <c r="B58" s="2">
-        <v>536.1417453044792</v>
+        <v>532.0353511185624</v>
       </c>
       <c r="C58" s="2">
-        <v>79.01425581148351</v>
+        <v>79.84643359092624</v>
       </c>
       <c r="D58" s="2">
-        <v>376.1298415653221</v>
+        <v>372.1093140586649</v>
       </c>
       <c r="E58" s="2">
-        <v>66.61215069577615</v>
+        <v>65.54490704716598</v>
       </c>
       <c r="F58" s="2">
-        <v>9.484224990771876</v>
+        <v>9.968694189985593</v>
       </c>
       <c r="G58" s="2">
-        <v>4.900336685544914</v>
+        <v>4.565066676239173</v>
       </c>
       <c r="H58" s="3">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -1926,25 +1926,25 @@
         <v>46202</v>
       </c>
       <c r="B59" s="2">
-        <v>729.5970524741944</v>
+        <v>722.8430643999193</v>
       </c>
       <c r="C59" s="2">
-        <v>109.0568683280031</v>
+        <v>108.2246905485604</v>
       </c>
       <c r="D59" s="2">
-        <v>431.9084959045285</v>
+        <v>430.4269000686816</v>
       </c>
       <c r="E59" s="2">
-        <v>161.1349130550296</v>
+        <v>160.8659597318475</v>
       </c>
       <c r="F59" s="2">
-        <v>22.48371908488373</v>
+        <v>18.05364292494953</v>
       </c>
       <c r="G59" s="2">
-        <v>5.013056101749341</v>
+        <v>5.271871125880215</v>
       </c>
       <c r="H59" s="3">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -1952,25 +1952,25 @@
         <v>46203</v>
       </c>
       <c r="B60" s="2">
-        <v>557.5461445148637</v>
+        <v>560.6617400656658</v>
       </c>
       <c r="C60" s="2">
-        <v>83.59095062429596</v>
+        <v>84.70736809500279</v>
       </c>
       <c r="D60" s="2">
-        <v>381.651288483497</v>
+        <v>381.5174215418331</v>
       </c>
       <c r="E60" s="2">
-        <v>80.57408084570172</v>
+        <v>80.44674362433091</v>
       </c>
       <c r="F60" s="2">
-        <v>7.62483008734054</v>
+        <v>9.667639574110508</v>
       </c>
       <c r="G60" s="2">
-        <v>4.104994474028548</v>
+        <v>4.322567230388522</v>
       </c>
       <c r="H60" s="3">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -1978,25 +1978,25 @@
         <v>46204</v>
       </c>
       <c r="B61" s="2">
-        <v>579.9889915863578</v>
+        <v>576.9139946316087</v>
       </c>
       <c r="C61" s="2">
-        <v>88.91234534914912</v>
+        <v>87.79592787844228</v>
       </c>
       <c r="D61" s="2">
-        <v>365.1939375303093</v>
+        <v>365.3278044719733</v>
       </c>
       <c r="E61" s="2">
-        <v>117.7356856209723</v>
+        <v>117.6961397890933</v>
       </c>
       <c r="F61" s="2">
-        <v>4.026442253142595</v>
+        <v>1.983632766372628</v>
       </c>
       <c r="G61" s="2">
-        <v>4.120580832784374</v>
+        <v>4.110489725727174</v>
       </c>
       <c r="H61" s="3">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -2004,7 +2004,7 @@
         <v>46205</v>
       </c>
       <c r="B62" s="2">
-        <v>99.97650864320727</v>
+        <v>100.4405864187518</v>
       </c>
       <c r="C62" s="2">
         <v>13.72336661054387</v>
@@ -2013,13 +2013,13 @@
         <v>62.62739028412305</v>
       </c>
       <c r="E62" s="2">
-        <v>23.57268369293875</v>
+        <v>23.82942896780041</v>
       </c>
       <c r="F62" s="2">
         <v>0</v>
       </c>
       <c r="G62" s="2">
-        <v>0.05306805560158358</v>
+        <v>0.2604005562845204</v>
       </c>
       <c r="H62" s="3">
         <v>26</v>
@@ -2282,13 +2282,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A99BB5E-09DC-40F9-8151-0E8730FE2818}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74F9F91E-F9E7-4F99-B6C4-C78A0CEA3D83}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A1AE0BF-9F39-49B3-AA48-D3F626A05FD4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1E90D80-96F3-4720-8FCD-0DB673581496}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D60475F-62D5-4D60-9165-A97D956683BD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42EB1D5B-200F-4F75-A12B-4A98F8ABC273}"/>
 </file>
--- a/sea_productive.xlsx
+++ b/sea_productive.xlsx
@@ -109,8 +109,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:H62" totalsRowShown="0">
-  <autoFilter ref="A1:H62"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:H79" totalsRowShown="0">
+  <autoFilter ref="A1:H79"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Date_Converted" dataDxfId="0"/>
     <tableColumn id="2" name="Staff Hour (In Hours)" dataDxfId="1"/>
@@ -410,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -522,16 +522,16 @@
         <v>46148</v>
       </c>
       <c r="B5" s="2">
-        <v>437.276570502382</v>
+        <v>444.7392335724779</v>
       </c>
       <c r="C5" s="2">
         <v>63.46380384975009</v>
       </c>
       <c r="D5" s="2">
-        <v>186.9585496249329</v>
+        <v>193.7754124224051</v>
       </c>
       <c r="E5" s="2">
-        <v>150.6561171919273</v>
+        <v>151.301917464551</v>
       </c>
       <c r="F5" s="2">
         <v>21.37913979831669</v>
@@ -548,16 +548,16 @@
         <v>46149</v>
       </c>
       <c r="B6" s="2">
-        <v>444.2742240612147</v>
+        <v>436.8115609911188</v>
       </c>
       <c r="C6" s="2">
         <v>58.67641829248932</v>
       </c>
       <c r="D6" s="2">
-        <v>270.4838541099409</v>
+        <v>263.6669913124686</v>
       </c>
       <c r="E6" s="2">
-        <v>87.93365047744578</v>
+        <v>87.28785020482209</v>
       </c>
       <c r="F6" s="2">
         <v>18.4203873065114</v>
@@ -782,7 +782,7 @@
         <v>46158</v>
       </c>
       <c r="B15" s="2">
-        <v>437.8700297472708</v>
+        <v>437.8702025250428</v>
       </c>
       <c r="C15" s="2">
         <v>61.91067844582928</v>
@@ -791,7 +791,7 @@
         <v>236.6874654512273</v>
       </c>
       <c r="E15" s="2">
-        <v>124.667381695095</v>
+        <v>124.667554472867</v>
       </c>
       <c r="F15" s="2">
         <v>10.49331111394697</v>
@@ -808,7 +808,7 @@
         <v>46159</v>
       </c>
       <c r="B16" s="2">
-        <v>421.9364205232325</v>
+        <v>421.9362477454605</v>
       </c>
       <c r="C16" s="2">
         <v>61.63815071587761</v>
@@ -817,7 +817,7 @@
         <v>226.5145835634218</v>
       </c>
       <c r="E16" s="2">
-        <v>109.0880901545949</v>
+        <v>109.0879173768229</v>
       </c>
       <c r="F16" s="2">
         <v>19.19578698227803</v>
@@ -1276,7 +1276,7 @@
         <v>46177</v>
       </c>
       <c r="B34" s="2">
-        <v>468.3330873585754</v>
+        <v>468.3333093030267</v>
       </c>
       <c r="C34" s="2">
         <v>71.60701902108887</v>
@@ -1291,7 +1291,7 @@
         <v>2.529644486755133</v>
       </c>
       <c r="G34" s="2">
-        <v>1.829574161275135</v>
+        <v>1.829796105726467</v>
       </c>
       <c r="H34" s="3">
         <v>53</v>
@@ -1302,7 +1302,7 @@
         <v>46178</v>
       </c>
       <c r="B35" s="2">
-        <v>455.0873055720526</v>
+        <v>455.0870836276013</v>
       </c>
       <c r="C35" s="2">
         <v>66.41595884060021</v>
@@ -1317,7 +1317,7 @@
         <v>3.752658105542262</v>
       </c>
       <c r="G35" s="2">
-        <v>3.755871353534102</v>
+        <v>3.75564940908277</v>
       </c>
       <c r="H35" s="3">
         <v>53</v>
@@ -1744,25 +1744,25 @@
         <v>46195</v>
       </c>
       <c r="B52" s="2">
-        <v>734.3007544983274</v>
+        <v>728.2143144278158</v>
       </c>
       <c r="C52" s="2">
-        <v>111.0390040117502</v>
+        <v>110.078755646944</v>
       </c>
       <c r="D52" s="2">
-        <v>490.1270887461773</v>
+        <v>491.7079259635728</v>
       </c>
       <c r="E52" s="2">
-        <v>112.643346468769</v>
+        <v>113.1629511831825</v>
       </c>
       <c r="F52" s="2">
-        <v>11.41097001132866</v>
+        <v>4.318107207657563</v>
       </c>
       <c r="G52" s="2">
-        <v>9.080345260302225</v>
+        <v>8.946574426458941</v>
       </c>
       <c r="H52" s="3">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -1770,25 +1770,25 @@
         <v>46196</v>
       </c>
       <c r="B53" s="2">
-        <v>611.2288515404896</v>
+        <v>602.5023221313245</v>
       </c>
       <c r="C53" s="2">
-        <v>93.03504790819298</v>
+        <v>91.88333041361581</v>
       </c>
       <c r="D53" s="2">
-        <v>398.3756868967559</v>
+        <v>396.7948496793604</v>
       </c>
       <c r="E53" s="2">
-        <v>108.4273350974648</v>
+        <v>107.9070320497019</v>
       </c>
       <c r="F53" s="2">
-        <v>7.461677469246918</v>
+        <v>1.995150820033418</v>
       </c>
       <c r="G53" s="2">
-        <v>3.929104168828991</v>
+        <v>3.921959168612957</v>
       </c>
       <c r="H53" s="3">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -1796,10 +1796,10 @@
         <v>46197</v>
       </c>
       <c r="B54" s="2">
-        <v>640.7906935729511</v>
+        <v>632.2882656334931</v>
       </c>
       <c r="C54" s="2">
-        <v>94.7467027723872</v>
+        <v>93.94114778541028</v>
       </c>
       <c r="D54" s="2">
         <v>392.5012989544134</v>
@@ -1808,13 +1808,13 @@
         <v>137.0982543977968</v>
       </c>
       <c r="F54" s="2">
-        <v>9.790704373402727</v>
+        <v>2.093831420921617</v>
       </c>
       <c r="G54" s="2">
         <v>6.653733074950934</v>
       </c>
       <c r="H54" s="3">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -1874,7 +1874,7 @@
         <v>46200</v>
       </c>
       <c r="B57" s="2">
-        <v>541.2471974875341</v>
+        <v>534.5994860346261</v>
       </c>
       <c r="C57" s="2">
         <v>76.5272191665513</v>
@@ -1886,13 +1886,13 @@
         <v>58.57090567260822</v>
       </c>
       <c r="F57" s="2">
-        <v>13.45675266308917</v>
+        <v>6.809041210181183</v>
       </c>
       <c r="G57" s="2">
         <v>4.976203309958801</v>
       </c>
       <c r="H57" s="3">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -1900,10 +1900,10 @@
         <v>46201</v>
       </c>
       <c r="B58" s="2">
-        <v>532.0353511185624</v>
+        <v>522.4312191236528</v>
       </c>
       <c r="C58" s="2">
-        <v>79.84643359092624</v>
+        <v>79.01334997817295</v>
       </c>
       <c r="D58" s="2">
         <v>372.1093140586649</v>
@@ -1912,13 +1912,13 @@
         <v>65.54490704716598</v>
       </c>
       <c r="F58" s="2">
-        <v>9.968694189985593</v>
+        <v>1.197645807829168</v>
       </c>
       <c r="G58" s="2">
         <v>4.565066676239173</v>
       </c>
       <c r="H58" s="3">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -1926,7 +1926,7 @@
         <v>46202</v>
       </c>
       <c r="B59" s="2">
-        <v>722.8430643999193</v>
+        <v>713.5880962315314</v>
       </c>
       <c r="C59" s="2">
         <v>108.2246905485604</v>
@@ -1938,13 +1938,13 @@
         <v>160.8659597318475</v>
       </c>
       <c r="F59" s="2">
-        <v>18.05364292494953</v>
+        <v>8.800082812102305</v>
       </c>
       <c r="G59" s="2">
-        <v>5.271871125880215</v>
+        <v>5.270463070339627</v>
       </c>
       <c r="H59" s="3">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -1952,10 +1952,10 @@
         <v>46203</v>
       </c>
       <c r="B60" s="2">
-        <v>560.6617400656658</v>
+        <v>552.0862636072785</v>
       </c>
       <c r="C60" s="2">
-        <v>84.70736809500279</v>
+        <v>83.59095062429596</v>
       </c>
       <c r="D60" s="2">
         <v>381.5174215418331</v>
@@ -1964,13 +1964,13 @@
         <v>80.44674362433091</v>
       </c>
       <c r="F60" s="2">
-        <v>9.667639574110508</v>
+        <v>2.209647253139151</v>
       </c>
       <c r="G60" s="2">
-        <v>4.322567230388522</v>
+        <v>4.32150056367947</v>
       </c>
       <c r="H60" s="3">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -1978,7 +1978,7 @@
         <v>46204</v>
       </c>
       <c r="B61" s="2">
-        <v>576.9139946316087</v>
+        <v>577.0261210180392</v>
       </c>
       <c r="C61" s="2">
         <v>87.79592787844228</v>
@@ -1987,7 +1987,7 @@
         <v>365.3278044719733</v>
       </c>
       <c r="E61" s="2">
-        <v>117.6961397890933</v>
+        <v>117.8082661755238</v>
       </c>
       <c r="F61" s="2">
         <v>1.983632766372628</v>
@@ -2004,24 +2004,466 @@
         <v>46205</v>
       </c>
       <c r="B62" s="2">
-        <v>100.4405864187518</v>
+        <v>625.2918359013826</v>
       </c>
       <c r="C62" s="2">
-        <v>13.72336661054387</v>
+        <v>95.14655283102995</v>
       </c>
       <c r="D62" s="2">
-        <v>62.62739028412305</v>
+        <v>363.9662559058486</v>
       </c>
       <c r="E62" s="2">
-        <v>23.82942896780041</v>
+        <v>157.1658702265885</v>
       </c>
       <c r="F62" s="2">
+        <v>6.076995255053044</v>
+      </c>
+      <c r="G62" s="2">
+        <v>2.936161682862374</v>
+      </c>
+      <c r="H62" s="3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" s="1">
+        <v>46206</v>
+      </c>
+      <c r="B63" s="2">
+        <v>562.0971715082948</v>
+      </c>
+      <c r="C63" s="2">
+        <v>84.19896278513026</v>
+      </c>
+      <c r="D63" s="2">
+        <v>417.0041653406382</v>
+      </c>
+      <c r="E63" s="2">
+        <v>54.74139170158654</v>
+      </c>
+      <c r="F63" s="2">
+        <v>1.312381412221326</v>
+      </c>
+      <c r="G63" s="2">
+        <v>4.840270268718402</v>
+      </c>
+      <c r="H63" s="3">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" s="1">
+        <v>46207</v>
+      </c>
+      <c r="B64" s="2">
+        <v>488.7199974344266</v>
+      </c>
+      <c r="C64" s="2">
+        <v>74.6105107924425</v>
+      </c>
+      <c r="D64" s="2">
+        <v>390.7035432550721</v>
+      </c>
+      <c r="E64" s="2">
+        <v>16.03769221531149</v>
+      </c>
+      <c r="F64" s="2">
+        <v>2.341780861202214</v>
+      </c>
+      <c r="G64" s="2">
+        <v>5.026470310398274</v>
+      </c>
+      <c r="H64" s="3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" s="1">
+        <v>46208</v>
+      </c>
+      <c r="B65" s="2">
+        <v>445.6075174629781</v>
+      </c>
+      <c r="C65" s="2">
+        <v>64.45698472600016</v>
+      </c>
+      <c r="D65" s="2">
+        <v>358.672118858791</v>
+      </c>
+      <c r="E65" s="2">
+        <v>16.04883442458619</v>
+      </c>
+      <c r="F65" s="2">
+        <v>2.77095417757829</v>
+      </c>
+      <c r="G65" s="2">
+        <v>3.658625276022487</v>
+      </c>
+      <c r="H65" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" s="1">
+        <v>46209</v>
+      </c>
+      <c r="B66" s="2">
+        <v>586.0449892122567</v>
+      </c>
+      <c r="C66" s="2">
+        <v>87.18765038213382</v>
+      </c>
+      <c r="D66" s="2">
+        <v>467.1054873978837</v>
+      </c>
+      <c r="E66" s="2">
+        <v>23.14133029842387</v>
+      </c>
+      <c r="F66" s="2">
+        <v>0.509589439249701</v>
+      </c>
+      <c r="G66" s="2">
+        <v>8.093598361238838</v>
+      </c>
+      <c r="H66" s="3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" s="1">
+        <v>46210</v>
+      </c>
+      <c r="B67" s="2">
+        <v>564.6484385724092</v>
+      </c>
+      <c r="C67" s="2">
+        <v>84.76973347044185</v>
+      </c>
+      <c r="D67" s="2">
+        <v>418.3245414227439</v>
+      </c>
+      <c r="E67" s="2">
+        <v>55.92218720598301</v>
+      </c>
+      <c r="F67" s="2">
+        <v>1.697602289501164</v>
+      </c>
+      <c r="G67" s="2">
+        <v>3.934374183739225</v>
+      </c>
+      <c r="H67" s="3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" s="1">
+        <v>46211</v>
+      </c>
+      <c r="B68" s="2">
+        <v>632.0055214014678</v>
+      </c>
+      <c r="C68" s="2">
+        <v>96.50852614504984</v>
+      </c>
+      <c r="D68" s="2">
+        <v>458.2766077468534</v>
+      </c>
+      <c r="E68" s="2">
+        <v>69.35005389279996</v>
+      </c>
+      <c r="F68" s="2">
+        <v>3.322143905162811</v>
+      </c>
+      <c r="G68" s="2">
+        <v>4.548189711601784</v>
+      </c>
+      <c r="H68" s="3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" s="1">
+        <v>46212</v>
+      </c>
+      <c r="B69" s="2">
+        <v>742.169731908473</v>
+      </c>
+      <c r="C69" s="2">
+        <v>110.3296730077781</v>
+      </c>
+      <c r="D69" s="2">
+        <v>456.5257993651192</v>
+      </c>
+      <c r="E69" s="2">
+        <v>164.0756824428775</v>
+      </c>
+      <c r="F69" s="2">
+        <v>5.275150944979655</v>
+      </c>
+      <c r="G69" s="2">
+        <v>5.9634261477185</v>
+      </c>
+      <c r="H69" s="3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" s="1">
+        <v>46213</v>
+      </c>
+      <c r="B70" s="2">
+        <v>614.7573523755608</v>
+      </c>
+      <c r="C70" s="2">
+        <v>95.17944871806759</v>
+      </c>
+      <c r="D70" s="2">
+        <v>434.1687478929613</v>
+      </c>
+      <c r="E70" s="2">
+        <v>78.73497605886078</v>
+      </c>
+      <c r="F70" s="2">
+        <v>2.071894935187366</v>
+      </c>
+      <c r="G70" s="2">
+        <v>4.601424770462844</v>
+      </c>
+      <c r="H70" s="3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71" s="1">
+        <v>46214</v>
+      </c>
+      <c r="B71" s="2">
+        <v>514.0953517938563</v>
+      </c>
+      <c r="C71" s="2">
+        <v>77.70793817635571</v>
+      </c>
+      <c r="D71" s="2">
+        <v>368.4551580734</v>
+      </c>
+      <c r="E71" s="2">
+        <v>59.70851081874842</v>
+      </c>
+      <c r="F71" s="2">
+        <v>3.249283900905608</v>
+      </c>
+      <c r="G71" s="2">
+        <v>4.974460824446545</v>
+      </c>
+      <c r="H71" s="3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" s="1">
+        <v>46215</v>
+      </c>
+      <c r="B72" s="2">
+        <v>475.8595367106283</v>
+      </c>
+      <c r="C72" s="2">
+        <v>71.74412089688083</v>
+      </c>
+      <c r="D72" s="2">
+        <v>272.6910647534279</v>
+      </c>
+      <c r="E72" s="2">
+        <v>124.6068448546529</v>
+      </c>
+      <c r="F72" s="2">
+        <v>1.639308073586888</v>
+      </c>
+      <c r="G72" s="2">
+        <v>5.178198132079819</v>
+      </c>
+      <c r="H72" s="3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" s="1">
+        <v>46216</v>
+      </c>
+      <c r="B73" s="2">
+        <v>594.4718044420168</v>
+      </c>
+      <c r="C73" s="2">
+        <v>90.16857133635837</v>
+      </c>
+      <c r="D73" s="2">
+        <v>378.4891052879209</v>
+      </c>
+      <c r="E73" s="2">
+        <v>117.7833086080311</v>
+      </c>
+      <c r="F73" s="2">
+        <v>3.594000280151765</v>
+      </c>
+      <c r="G73" s="2">
+        <v>4.436818929554688</v>
+      </c>
+      <c r="H73" s="3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74" s="1">
+        <v>46217</v>
+      </c>
+      <c r="B74" s="2">
+        <v>527.1839222468353</v>
+      </c>
+      <c r="C74" s="2">
+        <v>77.32587205909192</v>
+      </c>
+      <c r="D74" s="2">
+        <v>315.7124448826598</v>
+      </c>
+      <c r="E74" s="2">
+        <v>128.8413770110967</v>
+      </c>
+      <c r="F74" s="2">
+        <v>2.485061644729641</v>
+      </c>
+      <c r="G74" s="2">
+        <v>2.819166649257143</v>
+      </c>
+      <c r="H74" s="3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75" s="1">
+        <v>46218</v>
+      </c>
+      <c r="B75" s="2">
+        <v>472.65193000921</v>
+      </c>
+      <c r="C75" s="2">
+        <v>69.26402191291253</v>
+      </c>
+      <c r="D75" s="2">
+        <v>268.1527121832501</v>
+      </c>
+      <c r="E75" s="2">
+        <v>121.6787937111159</v>
+      </c>
+      <c r="F75" s="2">
+        <v>10.7543958227502</v>
+      </c>
+      <c r="G75" s="2">
+        <v>2.802006379181209</v>
+      </c>
+      <c r="H75" s="3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" s="1">
+        <v>46219</v>
+      </c>
+      <c r="B76" s="2">
+        <v>529.1988022963695</v>
+      </c>
+      <c r="C76" s="2">
+        <v>78.45324518176416</v>
+      </c>
+      <c r="D76" s="2">
+        <v>326.3883416236244</v>
+      </c>
+      <c r="E76" s="2">
+        <v>105.1450085987503</v>
+      </c>
+      <c r="F76" s="2">
+        <v>17.01563105603887</v>
+      </c>
+      <c r="G76" s="2">
+        <v>2.196575836191833</v>
+      </c>
+      <c r="H76" s="3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77" s="1">
+        <v>46220</v>
+      </c>
+      <c r="B77" s="2">
+        <v>659.2443534049102</v>
+      </c>
+      <c r="C77" s="2">
+        <v>99.43320823275795</v>
+      </c>
+      <c r="D77" s="2">
+        <v>388.6798447955276</v>
+      </c>
+      <c r="E77" s="2">
+        <v>159.3750809382689</v>
+      </c>
+      <c r="F77" s="2">
+        <v>7.44786667280727</v>
+      </c>
+      <c r="G77" s="2">
+        <v>4.308352765548561</v>
+      </c>
+      <c r="H77" s="3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" s="1">
+        <v>46221</v>
+      </c>
+      <c r="B78" s="2">
+        <v>665.819533032289</v>
+      </c>
+      <c r="C78" s="2">
+        <v>97.59066768288392</v>
+      </c>
+      <c r="D78" s="2">
+        <v>411.3795556697076</v>
+      </c>
+      <c r="E78" s="2">
+        <v>148.1027885086733</v>
+      </c>
+      <c r="F78" s="2">
+        <v>2.97637890760166</v>
+      </c>
+      <c r="G78" s="2">
+        <v>5.77014226342241</v>
+      </c>
+      <c r="H78" s="3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79" s="1">
+        <v>46222</v>
+      </c>
+      <c r="B79" s="2">
+        <v>105.7307427331813</v>
+      </c>
+      <c r="C79" s="2">
+        <v>5.465027454681144</v>
+      </c>
+      <c r="D79" s="2">
+        <v>86.08593778660418</v>
+      </c>
+      <c r="E79" s="2">
+        <v>13.71762137329439</v>
+      </c>
+      <c r="F79" s="2">
         <v>0</v>
       </c>
-      <c r="G62" s="2">
-        <v>0.2604005562845204</v>
-      </c>
-      <c r="H62" s="3">
+      <c r="G79" s="2">
+        <v>0.4621561186015606</v>
+      </c>
+      <c r="H79" s="3">
         <v>26</v>
       </c>
     </row>
@@ -2282,13 +2724,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74F9F91E-F9E7-4F99-B6C4-C78A0CEA3D83}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38946F2B-F29E-40F1-9BA1-CFB02EC8C647}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1E90D80-96F3-4720-8FCD-0DB673581496}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB67F307-F6ED-4803-835D-CA06E5CE0261}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42EB1D5B-200F-4F75-A12B-4A98F8ABC273}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ADC59944-69D0-4688-BBBD-43908B1D0727}"/>
 </file>
--- a/sea_productive.xlsx
+++ b/sea_productive.xlsx
@@ -109,8 +109,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:H79" totalsRowShown="0">
-  <autoFilter ref="A1:H79"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:H86" totalsRowShown="0">
+  <autoFilter ref="A1:H86"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Date_Converted" dataDxfId="0"/>
     <tableColumn id="2" name="Staff Hour (In Hours)" dataDxfId="1"/>
@@ -410,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H79"/>
+  <dimension ref="A1:H86"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -782,7 +782,7 @@
         <v>46158</v>
       </c>
       <c r="B15" s="2">
-        <v>437.8702025250428</v>
+        <v>437.8700297472708</v>
       </c>
       <c r="C15" s="2">
         <v>61.91067844582928</v>
@@ -791,7 +791,7 @@
         <v>236.6874654512273</v>
       </c>
       <c r="E15" s="2">
-        <v>124.667554472867</v>
+        <v>124.667381695095</v>
       </c>
       <c r="F15" s="2">
         <v>10.49331111394697</v>
@@ -808,7 +808,7 @@
         <v>46159</v>
       </c>
       <c r="B16" s="2">
-        <v>421.9362477454605</v>
+        <v>421.9364205232325</v>
       </c>
       <c r="C16" s="2">
         <v>61.63815071587761</v>
@@ -817,7 +817,7 @@
         <v>226.5145835634218</v>
       </c>
       <c r="E16" s="2">
-        <v>109.0879173768229</v>
+        <v>109.0880901545949</v>
       </c>
       <c r="F16" s="2">
         <v>19.19578698227803</v>
@@ -1276,7 +1276,7 @@
         <v>46177</v>
       </c>
       <c r="B34" s="2">
-        <v>468.3333093030267</v>
+        <v>468.3330873585754</v>
       </c>
       <c r="C34" s="2">
         <v>71.60701902108887</v>
@@ -1291,7 +1291,7 @@
         <v>2.529644486755133</v>
       </c>
       <c r="G34" s="2">
-        <v>1.829796105726467</v>
+        <v>1.829574161275135</v>
       </c>
       <c r="H34" s="3">
         <v>53</v>
@@ -1302,7 +1302,7 @@
         <v>46178</v>
       </c>
       <c r="B35" s="2">
-        <v>455.0870836276013</v>
+        <v>455.0873055720526</v>
       </c>
       <c r="C35" s="2">
         <v>66.41595884060021</v>
@@ -1317,7 +1317,7 @@
         <v>3.752658105542262</v>
       </c>
       <c r="G35" s="2">
-        <v>3.75564940908277</v>
+        <v>3.755871353534102</v>
       </c>
       <c r="H35" s="3">
         <v>53</v>
@@ -2108,25 +2108,25 @@
         <v>46209</v>
       </c>
       <c r="B66" s="2">
-        <v>586.0449892122567</v>
+        <v>604.7909920751821</v>
       </c>
       <c r="C66" s="2">
-        <v>87.18765038213382</v>
+        <v>90.05370179180883</v>
       </c>
       <c r="D66" s="2">
-        <v>467.1054873978837</v>
+        <v>482.6386580151148</v>
       </c>
       <c r="E66" s="2">
-        <v>23.14133029842387</v>
+        <v>23.44468224617187</v>
       </c>
       <c r="F66" s="2">
         <v>0.509589439249701</v>
       </c>
       <c r="G66" s="2">
-        <v>8.093598361238838</v>
+        <v>8.137027249510089</v>
       </c>
       <c r="H66" s="3">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -2134,25 +2134,25 @@
         <v>46210</v>
       </c>
       <c r="B67" s="2">
-        <v>564.6484385724092</v>
+        <v>573.6393130574859</v>
       </c>
       <c r="C67" s="2">
-        <v>84.76973347044185</v>
+        <v>86.22402850218477</v>
       </c>
       <c r="D67" s="2">
-        <v>418.3245414227439</v>
+        <v>425.3380728222965</v>
       </c>
       <c r="E67" s="2">
-        <v>55.92218720598301</v>
+        <v>56.35162692803424</v>
       </c>
       <c r="F67" s="2">
-        <v>1.697602289501164</v>
+        <v>1.783218398872349</v>
       </c>
       <c r="G67" s="2">
-        <v>3.934374183739225</v>
+        <v>3.942366406098008</v>
       </c>
       <c r="H67" s="3">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -2160,25 +2160,25 @@
         <v>46211</v>
       </c>
       <c r="B68" s="2">
-        <v>632.0055214014678</v>
+        <v>641.01585805851</v>
       </c>
       <c r="C68" s="2">
-        <v>96.50852614504984</v>
+        <v>97.85630443973234</v>
       </c>
       <c r="D68" s="2">
-        <v>458.2766077468534</v>
+        <v>465.3737719445251</v>
       </c>
       <c r="E68" s="2">
-        <v>69.35005389279996</v>
+        <v>69.79082722776673</v>
       </c>
       <c r="F68" s="2">
         <v>3.322143905162811</v>
       </c>
       <c r="G68" s="2">
-        <v>4.548189711601784</v>
+        <v>4.672810541323075</v>
       </c>
       <c r="H68" s="3">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -2368,25 +2368,25 @@
         <v>46219</v>
       </c>
       <c r="B76" s="2">
-        <v>529.1988022963695</v>
+        <v>538.1213475401012</v>
       </c>
       <c r="C76" s="2">
-        <v>78.45324518176416</v>
+        <v>79.94225433840519</v>
       </c>
       <c r="D76" s="2">
-        <v>326.3883416236244</v>
+        <v>332.832859367326</v>
       </c>
       <c r="E76" s="2">
-        <v>105.1450085987503</v>
+        <v>105.6470327638442</v>
       </c>
       <c r="F76" s="2">
-        <v>17.01563105603887</v>
+        <v>17.49955801216264</v>
       </c>
       <c r="G76" s="2">
-        <v>2.196575836191833</v>
+        <v>2.199643058363193</v>
       </c>
       <c r="H76" s="3">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="77" spans="1:8">
@@ -2420,25 +2420,25 @@
         <v>46221</v>
       </c>
       <c r="B78" s="2">
-        <v>665.819533032289</v>
+        <v>674.9805713647297</v>
       </c>
       <c r="C78" s="2">
-        <v>97.59066768288392</v>
+        <v>99.08369464102499</v>
       </c>
       <c r="D78" s="2">
-        <v>411.3795556697076</v>
+        <v>418.3171798206113</v>
       </c>
       <c r="E78" s="2">
-        <v>148.1027885086733</v>
+        <v>148.7523665669625</v>
       </c>
       <c r="F78" s="2">
         <v>2.97637890760166</v>
       </c>
       <c r="G78" s="2">
-        <v>5.77014226342241</v>
+        <v>5.850951428529289</v>
       </c>
       <c r="H78" s="3">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="79" spans="1:8">
@@ -2446,25 +2446,207 @@
         <v>46222</v>
       </c>
       <c r="B79" s="2">
-        <v>105.7307427331813</v>
+        <v>578.6414719791273</v>
       </c>
       <c r="C79" s="2">
-        <v>5.465027454681144</v>
+        <v>86.5401217412643</v>
       </c>
       <c r="D79" s="2">
-        <v>86.08593778660418</v>
+        <v>439.3915368114422</v>
       </c>
       <c r="E79" s="2">
-        <v>13.71762137329439</v>
+        <v>41.99978443209935</v>
       </c>
       <c r="F79" s="2">
-        <v>0</v>
+        <v>3.771218627473961</v>
       </c>
       <c r="G79" s="2">
-        <v>0.4621561186015606</v>
+        <v>6.938810366847449</v>
       </c>
       <c r="H79" s="3">
-        <v>26</v>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="A80" s="1">
+        <v>46223</v>
+      </c>
+      <c r="B80" s="2">
+        <v>547.39860413207</v>
+      </c>
+      <c r="C80" s="2">
+        <v>81.47549627913757</v>
+      </c>
+      <c r="D80" s="2">
+        <v>416.6683187794755</v>
+      </c>
+      <c r="E80" s="2">
+        <v>34.53752444881532</v>
+      </c>
+      <c r="F80" s="2">
+        <v>6.957641750830743</v>
+      </c>
+      <c r="G80" s="2">
+        <v>7.759622873810844</v>
+      </c>
+      <c r="H80" s="3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8">
+      <c r="A81" s="1">
+        <v>46224</v>
+      </c>
+      <c r="B81" s="2">
+        <v>504.4733979579139</v>
+      </c>
+      <c r="C81" s="2">
+        <v>75.50612567741838</v>
+      </c>
+      <c r="D81" s="2">
+        <v>375.3173412815657</v>
+      </c>
+      <c r="E81" s="2">
+        <v>48.9593456641983</v>
+      </c>
+      <c r="F81" s="2">
+        <v>1.25775667178962</v>
+      </c>
+      <c r="G81" s="2">
+        <v>3.432828662941853</v>
+      </c>
+      <c r="H81" s="3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
+      <c r="A82" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B82" s="2">
+        <v>450.5082771122056</v>
+      </c>
+      <c r="C82" s="2">
+        <v>68.10940885631261</v>
+      </c>
+      <c r="D82" s="2">
+        <v>333.0898195902573</v>
+      </c>
+      <c r="E82" s="2">
+        <v>44.25153703402314</v>
+      </c>
+      <c r="F82" s="2">
+        <v>1.733442459255457</v>
+      </c>
+      <c r="G82" s="2">
+        <v>3.324069172357106</v>
+      </c>
+      <c r="H82" s="3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
+      <c r="A83" s="1">
+        <v>46226</v>
+      </c>
+      <c r="B83" s="2">
+        <v>535.0621526777708</v>
+      </c>
+      <c r="C83" s="2">
+        <v>79.53510711406668</v>
+      </c>
+      <c r="D83" s="2">
+        <v>405.0616924142274</v>
+      </c>
+      <c r="E83" s="2">
+        <v>37.75679362351593</v>
+      </c>
+      <c r="F83" s="2">
+        <v>7.109032284869916</v>
+      </c>
+      <c r="G83" s="2">
+        <v>5.599527241090933</v>
+      </c>
+      <c r="H83" s="3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8">
+      <c r="A84" s="1">
+        <v>46227</v>
+      </c>
+      <c r="B84" s="2">
+        <v>601.2953243564607</v>
+      </c>
+      <c r="C84" s="2">
+        <v>92.07236300205192</v>
+      </c>
+      <c r="D84" s="2">
+        <v>454.0617388668713</v>
+      </c>
+      <c r="E84" s="2">
+        <v>47.5690755702043</v>
+      </c>
+      <c r="F84" s="2">
+        <v>2.812200804866023</v>
+      </c>
+      <c r="G84" s="2">
+        <v>4.779287223584122</v>
+      </c>
+      <c r="H84" s="3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8">
+      <c r="A85" s="1">
+        <v>46228</v>
+      </c>
+      <c r="B85" s="2">
+        <v>674.8781956689303</v>
+      </c>
+      <c r="C85" s="2">
+        <v>100.3969372175717</v>
+      </c>
+      <c r="D85" s="2">
+        <v>517.6858870998446</v>
+      </c>
+      <c r="E85" s="2">
+        <v>49.57311746570669</v>
+      </c>
+      <c r="F85" s="2">
+        <v>1.96357804313302</v>
+      </c>
+      <c r="G85" s="2">
+        <v>5.258675842674242</v>
+      </c>
+      <c r="H85" s="3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8">
+      <c r="A86" s="1">
+        <v>46229</v>
+      </c>
+      <c r="B86" s="2">
+        <v>213.4132968744718</v>
+      </c>
+      <c r="C86" s="2">
+        <v>19.55002288936741</v>
+      </c>
+      <c r="D86" s="2">
+        <v>188.511463423421</v>
+      </c>
+      <c r="E86" s="2">
+        <v>4.893856120631098</v>
+      </c>
+      <c r="F86" s="2">
+        <v>0.01837083313200209</v>
+      </c>
+      <c r="G86" s="2">
+        <v>0.439583607920342</v>
+      </c>
+      <c r="H86" s="3">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -2724,13 +2906,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38946F2B-F29E-40F1-9BA1-CFB02EC8C647}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAC32DB2-8148-4A6C-8DBC-8B647A3D2A83}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB67F307-F6ED-4803-835D-CA06E5CE0261}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5D9655F-000B-4DD0-AFB3-9627B98E55A3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ADC59944-69D0-4688-BBBD-43908B1D0727}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27D8329F-3C75-4895-9DDC-6006FDBB1047}"/>
 </file>
--- a/sea_productive.xlsx
+++ b/sea_productive.xlsx
@@ -109,8 +109,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:H86" totalsRowShown="0">
-  <autoFilter ref="A1:H86"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:H90" totalsRowShown="0">
+  <autoFilter ref="A1:H90"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Date_Converted" dataDxfId="0"/>
     <tableColumn id="2" name="Staff Hour (In Hours)" dataDxfId="1"/>
@@ -410,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H86"/>
+  <dimension ref="A1:H90"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1276,7 +1276,7 @@
         <v>46177</v>
       </c>
       <c r="B34" s="2">
-        <v>468.3330873585754</v>
+        <v>468.3333093030267</v>
       </c>
       <c r="C34" s="2">
         <v>71.60701902108887</v>
@@ -1291,7 +1291,7 @@
         <v>2.529644486755133</v>
       </c>
       <c r="G34" s="2">
-        <v>1.829574161275135</v>
+        <v>1.829796105726467</v>
       </c>
       <c r="H34" s="3">
         <v>53</v>
@@ -1302,7 +1302,7 @@
         <v>46178</v>
       </c>
       <c r="B35" s="2">
-        <v>455.0873055720526</v>
+        <v>455.0870836276013</v>
       </c>
       <c r="C35" s="2">
         <v>66.41595884060021</v>
@@ -1317,7 +1317,7 @@
         <v>3.752658105542262</v>
       </c>
       <c r="G35" s="2">
-        <v>3.755871353534102</v>
+        <v>3.75564940908277</v>
       </c>
       <c r="H35" s="3">
         <v>53</v>
@@ -2108,7 +2108,7 @@
         <v>46209</v>
       </c>
       <c r="B66" s="2">
-        <v>604.7909920751821</v>
+        <v>604.7907679085206</v>
       </c>
       <c r="C66" s="2">
         <v>90.05370179180883</v>
@@ -2123,7 +2123,7 @@
         <v>0.509589439249701</v>
       </c>
       <c r="G66" s="2">
-        <v>8.137027249510089</v>
+        <v>8.136803082848589</v>
       </c>
       <c r="H66" s="3">
         <v>68</v>
@@ -2134,7 +2134,7 @@
         <v>46210</v>
       </c>
       <c r="B67" s="2">
-        <v>573.6393130574859</v>
+        <v>573.6395372241474</v>
       </c>
       <c r="C67" s="2">
         <v>86.22402850218477</v>
@@ -2149,7 +2149,7 @@
         <v>1.783218398872349</v>
       </c>
       <c r="G67" s="2">
-        <v>3.942366406098008</v>
+        <v>3.942590572759509</v>
       </c>
       <c r="H67" s="3">
         <v>65</v>
@@ -2602,22 +2602,22 @@
         <v>46228</v>
       </c>
       <c r="B85" s="2">
-        <v>674.8781956689303</v>
+        <v>675.9134851088204</v>
       </c>
       <c r="C85" s="2">
         <v>100.3969372175717</v>
       </c>
       <c r="D85" s="2">
-        <v>517.6858870998446</v>
+        <v>518.3581134789611</v>
       </c>
       <c r="E85" s="2">
-        <v>49.57311746570669</v>
+        <v>49.65858524487949</v>
       </c>
       <c r="F85" s="2">
         <v>1.96357804313302</v>
       </c>
       <c r="G85" s="2">
-        <v>5.258675842674242</v>
+        <v>5.536271124275194</v>
       </c>
       <c r="H85" s="3">
         <v>75</v>
@@ -2628,25 +2628,129 @@
         <v>46229</v>
       </c>
       <c r="B86" s="2">
-        <v>213.4132968744718</v>
+        <v>695.8043334684645</v>
       </c>
       <c r="C86" s="2">
-        <v>19.55002288936741</v>
+        <v>102.0543588986662</v>
       </c>
       <c r="D86" s="2">
-        <v>188.511463423421</v>
+        <v>529.0926234221748</v>
       </c>
       <c r="E86" s="2">
-        <v>4.893856120631098</v>
+        <v>59.76118891191151</v>
       </c>
       <c r="F86" s="2">
-        <v>0.01837083313200209</v>
+        <v>0.1376133308145735</v>
       </c>
       <c r="G86" s="2">
-        <v>0.439583607920342</v>
+        <v>4.758548904897438</v>
       </c>
       <c r="H86" s="3">
-        <v>42</v>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8">
+      <c r="A87" s="1">
+        <v>46230</v>
+      </c>
+      <c r="B87" s="2">
+        <v>597.3494747869665</v>
+      </c>
+      <c r="C87" s="2">
+        <v>91.60031418796214</v>
+      </c>
+      <c r="D87" s="2">
+        <v>434.9187237028897</v>
+      </c>
+      <c r="E87" s="2">
+        <v>56.97330014417155</v>
+      </c>
+      <c r="F87" s="2">
+        <v>8.093636708988084</v>
+      </c>
+      <c r="G87" s="2">
+        <v>5.763500042955081</v>
+      </c>
+      <c r="H87" s="3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8">
+      <c r="A88" s="1">
+        <v>46231</v>
+      </c>
+      <c r="B88" s="2">
+        <v>509.7563989235802</v>
+      </c>
+      <c r="C88" s="2">
+        <v>80.45194568102917</v>
+      </c>
+      <c r="D88" s="2">
+        <v>368.3934339935183</v>
+      </c>
+      <c r="E88" s="2">
+        <v>51.41017859317155</v>
+      </c>
+      <c r="F88" s="2">
+        <v>5.600065685144315</v>
+      </c>
+      <c r="G88" s="2">
+        <v>3.9007749707169</v>
+      </c>
+      <c r="H88" s="3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8">
+      <c r="A89" s="1">
+        <v>46232</v>
+      </c>
+      <c r="B89" s="2">
+        <v>491.1225223996401</v>
+      </c>
+      <c r="C89" s="2">
+        <v>73.65371922912865</v>
+      </c>
+      <c r="D89" s="2">
+        <v>290.2961258924776</v>
+      </c>
+      <c r="E89" s="2">
+        <v>121.0986867113101</v>
+      </c>
+      <c r="F89" s="2">
+        <v>3.504318906085359</v>
+      </c>
+      <c r="G89" s="2">
+        <v>2.569671660638414</v>
+      </c>
+      <c r="H89" s="3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8">
+      <c r="A90" s="1">
+        <v>46233</v>
+      </c>
+      <c r="B90" s="2">
+        <v>96.28983412090869</v>
+      </c>
+      <c r="C90" s="2">
+        <v>6.918168612288104</v>
+      </c>
+      <c r="D90" s="2">
+        <v>69.3839119083825</v>
+      </c>
+      <c r="E90" s="2">
+        <v>19.77956916064024</v>
+      </c>
+      <c r="F90" s="2">
+        <v>0</v>
+      </c>
+      <c r="G90" s="2">
+        <v>0.2081844395978583</v>
+      </c>
+      <c r="H90" s="3">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -2906,13 +3010,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAC32DB2-8148-4A6C-8DBC-8B647A3D2A83}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30C50570-67FD-49EB-9346-B558DB3BE4FE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5D9655F-000B-4DD0-AFB3-9627B98E55A3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{90EDEC7E-A307-4FE3-BBB8-8376C423435E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27D8329F-3C75-4895-9DDC-6006FDBB1047}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{875B11BF-FD07-44FA-A4A8-27CE5960F4E3}"/>
 </file>
--- a/sea_productive.xlsx
+++ b/sea_productive.xlsx
@@ -109,8 +109,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:H90" totalsRowShown="0">
-  <autoFilter ref="A1:H90"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:H92" totalsRowShown="0">
+  <autoFilter ref="A1:H92"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Date_Converted" dataDxfId="0"/>
     <tableColumn id="2" name="Staff Hour (In Hours)" dataDxfId="1"/>
@@ -410,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H90"/>
+  <dimension ref="A1:H92"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1276,7 +1276,7 @@
         <v>46177</v>
       </c>
       <c r="B34" s="2">
-        <v>468.3333093030267</v>
+        <v>468.3330873585754</v>
       </c>
       <c r="C34" s="2">
         <v>71.60701902108887</v>
@@ -1291,7 +1291,7 @@
         <v>2.529644486755133</v>
       </c>
       <c r="G34" s="2">
-        <v>1.829796105726467</v>
+        <v>1.829574161275135</v>
       </c>
       <c r="H34" s="3">
         <v>53</v>
@@ -1302,7 +1302,7 @@
         <v>46178</v>
       </c>
       <c r="B35" s="2">
-        <v>455.0870836276013</v>
+        <v>455.0873055720526</v>
       </c>
       <c r="C35" s="2">
         <v>66.41595884060021</v>
@@ -1317,7 +1317,7 @@
         <v>3.752658105542262</v>
       </c>
       <c r="G35" s="2">
-        <v>3.75564940908277</v>
+        <v>3.755871353534102</v>
       </c>
       <c r="H35" s="3">
         <v>53</v>
@@ -1926,7 +1926,7 @@
         <v>46202</v>
       </c>
       <c r="B59" s="2">
-        <v>713.5880962315314</v>
+        <v>713.5883717870825</v>
       </c>
       <c r="C59" s="2">
         <v>108.2246905485604</v>
@@ -1941,7 +1941,7 @@
         <v>8.800082812102305</v>
       </c>
       <c r="G59" s="2">
-        <v>5.270463070339627</v>
+        <v>5.270738625890679</v>
       </c>
       <c r="H59" s="3">
         <v>80</v>
@@ -1952,7 +1952,7 @@
         <v>46203</v>
       </c>
       <c r="B60" s="2">
-        <v>552.0862636072785</v>
+        <v>552.0859880517276</v>
       </c>
       <c r="C60" s="2">
         <v>83.59095062429596</v>
@@ -1967,7 +1967,7 @@
         <v>2.209647253139151</v>
       </c>
       <c r="G60" s="2">
-        <v>4.32150056367947</v>
+        <v>4.321225008128418</v>
       </c>
       <c r="H60" s="3">
         <v>63</v>
@@ -2108,7 +2108,7 @@
         <v>46209</v>
       </c>
       <c r="B66" s="2">
-        <v>604.7907679085206</v>
+        <v>604.7909920751821</v>
       </c>
       <c r="C66" s="2">
         <v>90.05370179180883</v>
@@ -2123,7 +2123,7 @@
         <v>0.509589439249701</v>
       </c>
       <c r="G66" s="2">
-        <v>8.136803082848589</v>
+        <v>8.137027249510089</v>
       </c>
       <c r="H66" s="3">
         <v>68</v>
@@ -2134,7 +2134,7 @@
         <v>46210</v>
       </c>
       <c r="B67" s="2">
-        <v>573.6395372241474</v>
+        <v>573.6393130574859</v>
       </c>
       <c r="C67" s="2">
         <v>86.22402850218477</v>
@@ -2149,7 +2149,7 @@
         <v>1.783218398872349</v>
       </c>
       <c r="G67" s="2">
-        <v>3.942590572759509</v>
+        <v>3.942366406098008</v>
       </c>
       <c r="H67" s="3">
         <v>65</v>
@@ -2706,7 +2706,7 @@
         <v>46232</v>
       </c>
       <c r="B89" s="2">
-        <v>491.1225223996401</v>
+        <v>491.1687032349401</v>
       </c>
       <c r="C89" s="2">
         <v>73.65371922912865</v>
@@ -2715,7 +2715,7 @@
         <v>290.2961258924776</v>
       </c>
       <c r="E89" s="2">
-        <v>121.0986867113101</v>
+        <v>121.1448675466101</v>
       </c>
       <c r="F89" s="2">
         <v>3.504318906085359</v>
@@ -2732,25 +2732,77 @@
         <v>46233</v>
       </c>
       <c r="B90" s="2">
-        <v>96.28983412090869</v>
+        <v>561.0363250034864</v>
       </c>
       <c r="C90" s="2">
-        <v>6.918168612288104</v>
+        <v>85.09984127986762</v>
       </c>
       <c r="D90" s="2">
-        <v>69.3839119083825</v>
+        <v>321.7743402478495</v>
       </c>
       <c r="E90" s="2">
-        <v>19.77956916064024</v>
+        <v>144.8330565315568</v>
       </c>
       <c r="F90" s="2">
-        <v>0</v>
+        <v>6.689186406963401</v>
       </c>
       <c r="G90" s="2">
-        <v>0.2081844395978583</v>
+        <v>2.639900537249115</v>
       </c>
       <c r="H90" s="3">
-        <v>24</v>
+        <v>63</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8">
+      <c r="A91" s="1">
+        <v>46234</v>
+      </c>
+      <c r="B91" s="2">
+        <v>605.7447988411624</v>
+      </c>
+      <c r="C91" s="2">
+        <v>94.11890951497894</v>
+      </c>
+      <c r="D91" s="2">
+        <v>353.3535579468956</v>
+      </c>
+      <c r="E91" s="2">
+        <v>146.2372897889631</v>
+      </c>
+      <c r="F91" s="2">
+        <v>9.715374089032412</v>
+      </c>
+      <c r="G91" s="2">
+        <v>2.319667501292295</v>
+      </c>
+      <c r="H91" s="3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8">
+      <c r="A92" s="1">
+        <v>46235</v>
+      </c>
+      <c r="B92" s="2">
+        <v>157.9557290897536</v>
+      </c>
+      <c r="C92" s="2">
+        <v>15.99790638929799</v>
+      </c>
+      <c r="D92" s="2">
+        <v>117.4402441353622</v>
+      </c>
+      <c r="E92" s="2">
+        <v>23.68901330382046</v>
+      </c>
+      <c r="F92" s="2">
+        <v>0.09955222391419941</v>
+      </c>
+      <c r="G92" s="2">
+        <v>0.7290130373587211</v>
+      </c>
+      <c r="H92" s="3">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -3010,13 +3062,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30C50570-67FD-49EB-9346-B558DB3BE4FE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F496CF72-CB06-4A6A-AA4D-38B1DA9FA323}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{90EDEC7E-A307-4FE3-BBB8-8376C423435E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{370436FC-5FAC-4978-895B-499EF0D41ADA}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{875B11BF-FD07-44FA-A4A8-27CE5960F4E3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7436AA8C-161A-4BF5-8C0F-612D0C385232}"/>
 </file>
--- a/sea_productive.xlsx
+++ b/sea_productive.xlsx
@@ -109,8 +109,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:H92" totalsRowShown="0">
-  <autoFilter ref="A1:H92"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:H93" totalsRowShown="0">
+  <autoFilter ref="A1:H93"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Date_Converted" dataDxfId="0"/>
     <tableColumn id="2" name="Staff Hour (In Hours)" dataDxfId="1"/>
@@ -410,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H92"/>
+  <dimension ref="A1:H93"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -782,7 +782,7 @@
         <v>46158</v>
       </c>
       <c r="B15" s="2">
-        <v>437.8700297472708</v>
+        <v>437.8702025250428</v>
       </c>
       <c r="C15" s="2">
         <v>61.91067844582928</v>
@@ -791,7 +791,7 @@
         <v>236.6874654512273</v>
       </c>
       <c r="E15" s="2">
-        <v>124.667381695095</v>
+        <v>124.667554472867</v>
       </c>
       <c r="F15" s="2">
         <v>10.49331111394697</v>
@@ -808,7 +808,7 @@
         <v>46159</v>
       </c>
       <c r="B16" s="2">
-        <v>421.9364205232325</v>
+        <v>421.9362477454605</v>
       </c>
       <c r="C16" s="2">
         <v>61.63815071587761</v>
@@ -817,7 +817,7 @@
         <v>226.5145835634218</v>
       </c>
       <c r="E16" s="2">
-        <v>109.0880901545949</v>
+        <v>109.0879173768229</v>
       </c>
       <c r="F16" s="2">
         <v>19.19578698227803</v>
@@ -1276,7 +1276,7 @@
         <v>46177</v>
       </c>
       <c r="B34" s="2">
-        <v>468.3330873585754</v>
+        <v>468.3333093030267</v>
       </c>
       <c r="C34" s="2">
         <v>71.60701902108887</v>
@@ -1291,7 +1291,7 @@
         <v>2.529644486755133</v>
       </c>
       <c r="G34" s="2">
-        <v>1.829574161275135</v>
+        <v>1.829796105726467</v>
       </c>
       <c r="H34" s="3">
         <v>53</v>
@@ -1302,7 +1302,7 @@
         <v>46178</v>
       </c>
       <c r="B35" s="2">
-        <v>455.0873055720526</v>
+        <v>455.0870836276013</v>
       </c>
       <c r="C35" s="2">
         <v>66.41595884060021</v>
@@ -1317,7 +1317,7 @@
         <v>3.752658105542262</v>
       </c>
       <c r="G35" s="2">
-        <v>3.755871353534102</v>
+        <v>3.75564940908277</v>
       </c>
       <c r="H35" s="3">
         <v>53</v>
@@ -1926,7 +1926,7 @@
         <v>46202</v>
       </c>
       <c r="B59" s="2">
-        <v>713.5883717870825</v>
+        <v>713.5880962315314</v>
       </c>
       <c r="C59" s="2">
         <v>108.2246905485604</v>
@@ -1941,7 +1941,7 @@
         <v>8.800082812102305</v>
       </c>
       <c r="G59" s="2">
-        <v>5.270738625890679</v>
+        <v>5.270463070339627</v>
       </c>
       <c r="H59" s="3">
         <v>80</v>
@@ -1952,7 +1952,7 @@
         <v>46203</v>
       </c>
       <c r="B60" s="2">
-        <v>552.0859880517276</v>
+        <v>552.0862636072785</v>
       </c>
       <c r="C60" s="2">
         <v>83.59095062429596</v>
@@ -1967,7 +1967,7 @@
         <v>2.209647253139151</v>
       </c>
       <c r="G60" s="2">
-        <v>4.321225008128418</v>
+        <v>4.32150056367947</v>
       </c>
       <c r="H60" s="3">
         <v>63</v>
@@ -2108,7 +2108,7 @@
         <v>46209</v>
       </c>
       <c r="B66" s="2">
-        <v>604.7909920751821</v>
+        <v>604.7907679085206</v>
       </c>
       <c r="C66" s="2">
         <v>90.05370179180883</v>
@@ -2123,7 +2123,7 @@
         <v>0.509589439249701</v>
       </c>
       <c r="G66" s="2">
-        <v>8.137027249510089</v>
+        <v>8.136803082848589</v>
       </c>
       <c r="H66" s="3">
         <v>68</v>
@@ -2134,7 +2134,7 @@
         <v>46210</v>
       </c>
       <c r="B67" s="2">
-        <v>573.6393130574859</v>
+        <v>573.6395372241474</v>
       </c>
       <c r="C67" s="2">
         <v>86.22402850218477</v>
@@ -2149,7 +2149,7 @@
         <v>1.783218398872349</v>
       </c>
       <c r="G67" s="2">
-        <v>3.942366406098008</v>
+        <v>3.942590572759509</v>
       </c>
       <c r="H67" s="3">
         <v>65</v>
@@ -2758,7 +2758,7 @@
         <v>46234</v>
       </c>
       <c r="B91" s="2">
-        <v>605.7447988411624</v>
+        <v>605.7840235632829</v>
       </c>
       <c r="C91" s="2">
         <v>94.11890951497894</v>
@@ -2767,7 +2767,7 @@
         <v>353.3535579468956</v>
       </c>
       <c r="E91" s="2">
-        <v>146.2372897889631</v>
+        <v>146.2765145110836</v>
       </c>
       <c r="F91" s="2">
         <v>9.715374089032412</v>
@@ -2784,25 +2784,51 @@
         <v>46235</v>
       </c>
       <c r="B92" s="2">
-        <v>157.9557290897536</v>
+        <v>564.8291119537331</v>
       </c>
       <c r="C92" s="2">
-        <v>15.99790638929799</v>
+        <v>86.45828823079196</v>
       </c>
       <c r="D92" s="2">
-        <v>117.4402441353622</v>
+        <v>386.8637654302993</v>
       </c>
       <c r="E92" s="2">
-        <v>23.68901330382046</v>
+        <v>86.54819909832324</v>
       </c>
       <c r="F92" s="2">
-        <v>0.09955222391419941</v>
+        <v>1.145287795017163</v>
       </c>
       <c r="G92" s="2">
-        <v>0.7290130373587211</v>
+        <v>3.81357139930129</v>
       </c>
       <c r="H92" s="3">
-        <v>33</v>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8">
+      <c r="A93" s="1">
+        <v>46236</v>
+      </c>
+      <c r="B93" s="2">
+        <v>104.1535184321286</v>
+      </c>
+      <c r="C93" s="2">
+        <v>5.299454991602236</v>
+      </c>
+      <c r="D93" s="2">
+        <v>85.26513015154568</v>
+      </c>
+      <c r="E93" s="2">
+        <v>13.44374745751835</v>
+      </c>
+      <c r="F93" s="2">
+        <v>0</v>
+      </c>
+      <c r="G93" s="2">
+        <v>0.1451858314623435</v>
+      </c>
+      <c r="H93" s="3">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -3062,13 +3088,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F496CF72-CB06-4A6A-AA4D-38B1DA9FA323}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4AA317F-F6C0-43C7-9ECF-5BF338869FA6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{370436FC-5FAC-4978-895B-499EF0D41ADA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF7AF33E-AC1F-4DAE-BCC4-7BA7694C7924}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7436AA8C-161A-4BF5-8C0F-612D0C385232}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2023B6EB-65F5-42F3-A21C-12BB0A2DCC98}"/>
 </file>
--- a/sea_productive.xlsx
+++ b/sea_productive.xlsx
@@ -109,8 +109,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:H93" totalsRowShown="0">
-  <autoFilter ref="A1:H93"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:H97" totalsRowShown="0">
+  <autoFilter ref="A1:H97"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Date_Converted" dataDxfId="0"/>
     <tableColumn id="2" name="Staff Hour (In Hours)" dataDxfId="1"/>
@@ -410,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H93"/>
+  <dimension ref="A1:H97"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1926,7 +1926,7 @@
         <v>46202</v>
       </c>
       <c r="B59" s="2">
-        <v>713.5880962315314</v>
+        <v>713.5883717870825</v>
       </c>
       <c r="C59" s="2">
         <v>108.2246905485604</v>
@@ -1941,7 +1941,7 @@
         <v>8.800082812102305</v>
       </c>
       <c r="G59" s="2">
-        <v>5.270463070339627</v>
+        <v>5.270738625890679</v>
       </c>
       <c r="H59" s="3">
         <v>80</v>
@@ -1952,7 +1952,7 @@
         <v>46203</v>
       </c>
       <c r="B60" s="2">
-        <v>552.0862636072785</v>
+        <v>552.0859880517276</v>
       </c>
       <c r="C60" s="2">
         <v>83.59095062429596</v>
@@ -1967,7 +1967,7 @@
         <v>2.209647253139151</v>
       </c>
       <c r="G60" s="2">
-        <v>4.32150056367947</v>
+        <v>4.321225008128418</v>
       </c>
       <c r="H60" s="3">
         <v>63</v>
@@ -2108,7 +2108,7 @@
         <v>46209</v>
       </c>
       <c r="B66" s="2">
-        <v>604.7907679085206</v>
+        <v>604.7909920751821</v>
       </c>
       <c r="C66" s="2">
         <v>90.05370179180883</v>
@@ -2123,7 +2123,7 @@
         <v>0.509589439249701</v>
       </c>
       <c r="G66" s="2">
-        <v>8.136803082848589</v>
+        <v>8.137027249510089</v>
       </c>
       <c r="H66" s="3">
         <v>68</v>
@@ -2134,7 +2134,7 @@
         <v>46210</v>
       </c>
       <c r="B67" s="2">
-        <v>573.6395372241474</v>
+        <v>573.6393130574859</v>
       </c>
       <c r="C67" s="2">
         <v>86.22402850218477</v>
@@ -2149,7 +2149,7 @@
         <v>1.783218398872349</v>
       </c>
       <c r="G67" s="2">
-        <v>3.942590572759509</v>
+        <v>3.942366406098008</v>
       </c>
       <c r="H67" s="3">
         <v>65</v>
@@ -2654,25 +2654,25 @@
         <v>46230</v>
       </c>
       <c r="B87" s="2">
-        <v>597.3494747869665</v>
+        <v>615.2571711930358</v>
       </c>
       <c r="C87" s="2">
-        <v>91.60031418796214</v>
+        <v>94.45675751003127</v>
       </c>
       <c r="D87" s="2">
-        <v>434.9187237028897</v>
+        <v>447.310195674517</v>
       </c>
       <c r="E87" s="2">
-        <v>56.97330014417155</v>
+        <v>59.31069764828931</v>
       </c>
       <c r="F87" s="2">
         <v>8.093636708988084</v>
       </c>
       <c r="G87" s="2">
-        <v>5.763500042955081</v>
+        <v>6.085883651210202</v>
       </c>
       <c r="H87" s="3">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -2680,25 +2680,25 @@
         <v>46231</v>
       </c>
       <c r="B88" s="2">
-        <v>509.7563989235802</v>
+        <v>527.9680008692154</v>
       </c>
       <c r="C88" s="2">
-        <v>80.45194568102917</v>
+        <v>83.43221763606232</v>
       </c>
       <c r="D88" s="2">
-        <v>368.3934339935183</v>
+        <v>381.318357047065</v>
       </c>
       <c r="E88" s="2">
-        <v>51.41017859317155</v>
+        <v>53.2600210875459</v>
       </c>
       <c r="F88" s="2">
         <v>5.600065685144315</v>
       </c>
       <c r="G88" s="2">
-        <v>3.9007749707169</v>
+        <v>4.357339413397842</v>
       </c>
       <c r="H88" s="3">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="89" spans="1:8">
@@ -2706,25 +2706,25 @@
         <v>46232</v>
       </c>
       <c r="B89" s="2">
-        <v>491.1687032349401</v>
+        <v>509.3956852139488</v>
       </c>
       <c r="C89" s="2">
-        <v>73.65371922912865</v>
+        <v>76.62676231575676</v>
       </c>
       <c r="D89" s="2">
-        <v>290.2961258924776</v>
+        <v>304.0351681293862</v>
       </c>
       <c r="E89" s="2">
-        <v>121.1448675466101</v>
+        <v>122.4877939276666</v>
       </c>
       <c r="F89" s="2">
         <v>3.504318906085359</v>
       </c>
       <c r="G89" s="2">
-        <v>2.569671660638414</v>
+        <v>2.741641935053695</v>
       </c>
       <c r="H89" s="3">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -2732,25 +2732,25 @@
         <v>46233</v>
       </c>
       <c r="B90" s="2">
-        <v>561.0363250034864</v>
+        <v>579.2313585470573</v>
       </c>
       <c r="C90" s="2">
-        <v>85.09984127986762</v>
+        <v>88.06546714847286</v>
       </c>
       <c r="D90" s="2">
-        <v>321.7743402478495</v>
+        <v>334.2999982277508</v>
       </c>
       <c r="E90" s="2">
-        <v>144.8330565315568</v>
+        <v>147.1572662327521</v>
       </c>
       <c r="F90" s="2">
         <v>6.689186406963401</v>
       </c>
       <c r="G90" s="2">
-        <v>2.639900537249115</v>
+        <v>3.019440531118049</v>
       </c>
       <c r="H90" s="3">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="91" spans="1:8">
@@ -2758,25 +2758,25 @@
         <v>46234</v>
       </c>
       <c r="B91" s="2">
-        <v>605.7840235632829</v>
+        <v>623.8103840832575</v>
       </c>
       <c r="C91" s="2">
-        <v>94.11890951497894</v>
+        <v>97.08479813368163</v>
       </c>
       <c r="D91" s="2">
-        <v>353.3535579468956</v>
+        <v>366.574242913315</v>
       </c>
       <c r="E91" s="2">
-        <v>146.2765145110836</v>
+        <v>147.7331233890603</v>
       </c>
       <c r="F91" s="2">
         <v>9.715374089032412</v>
       </c>
       <c r="G91" s="2">
-        <v>2.319667501292295</v>
+        <v>2.70284555816816</v>
       </c>
       <c r="H91" s="3">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -2784,22 +2784,22 @@
         <v>46235</v>
       </c>
       <c r="B92" s="2">
-        <v>564.8291119537331</v>
+        <v>565.2931019488716</v>
       </c>
       <c r="C92" s="2">
         <v>86.45828823079196</v>
       </c>
       <c r="D92" s="2">
-        <v>386.8637654302993</v>
+        <v>387.2233843128031</v>
       </c>
       <c r="E92" s="2">
-        <v>86.54819909832324</v>
+        <v>86.60338854405396</v>
       </c>
       <c r="F92" s="2">
         <v>1.145287795017163</v>
       </c>
       <c r="G92" s="2">
-        <v>3.81357139930129</v>
+        <v>3.862753066205316</v>
       </c>
       <c r="H92" s="3">
         <v>64</v>
@@ -2810,25 +2810,129 @@
         <v>46236</v>
       </c>
       <c r="B93" s="2">
-        <v>104.1535184321286</v>
+        <v>498.7147375152669</v>
       </c>
       <c r="C93" s="2">
-        <v>5.299454991602236</v>
+        <v>72.89679199720422</v>
       </c>
       <c r="D93" s="2">
-        <v>85.26513015154568</v>
+        <v>373.4627755125765</v>
       </c>
       <c r="E93" s="2">
-        <v>13.44374745751835</v>
+        <v>47.66907389866059</v>
       </c>
       <c r="F93" s="2">
-        <v>0</v>
+        <v>1.584615003383822</v>
       </c>
       <c r="G93" s="2">
-        <v>0.1451858314623435</v>
+        <v>3.101481103441782</v>
       </c>
       <c r="H93" s="3">
-        <v>25</v>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8">
+      <c r="A94" s="1">
+        <v>46237</v>
+      </c>
+      <c r="B94" s="2">
+        <v>383.0603397886753</v>
+      </c>
+      <c r="C94" s="2">
+        <v>59.61875633161929</v>
+      </c>
+      <c r="D94" s="2">
+        <v>277.7001900241358</v>
+      </c>
+      <c r="E94" s="2">
+        <v>37.45547256339859</v>
+      </c>
+      <c r="F94" s="2">
+        <v>5.411665603762441</v>
+      </c>
+      <c r="G94" s="2">
+        <v>2.874255265759097</v>
+      </c>
+      <c r="H94" s="3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8">
+      <c r="A95" s="1">
+        <v>46238</v>
+      </c>
+      <c r="B95" s="2">
+        <v>495.3746127439921</v>
+      </c>
+      <c r="C95" s="2">
+        <v>77.56146169803209</v>
+      </c>
+      <c r="D95" s="2">
+        <v>364.6090605331254</v>
+      </c>
+      <c r="E95" s="2">
+        <v>39.69961220235564</v>
+      </c>
+      <c r="F95" s="2">
+        <v>8.736412738975551</v>
+      </c>
+      <c r="G95" s="2">
+        <v>4.768065571503507</v>
+      </c>
+      <c r="H95" s="3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8">
+      <c r="A96" s="1">
+        <v>46239</v>
+      </c>
+      <c r="B96" s="2">
+        <v>559.7692488641077</v>
+      </c>
+      <c r="C96" s="2">
+        <v>86.84341292021175</v>
+      </c>
+      <c r="D96" s="2">
+        <v>423.5485508325403</v>
+      </c>
+      <c r="E96" s="2">
+        <v>43.35442723495213</v>
+      </c>
+      <c r="F96" s="2">
+        <v>3.173914805766609</v>
+      </c>
+      <c r="G96" s="2">
+        <v>2.848943070636855</v>
+      </c>
+      <c r="H96" s="3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8">
+      <c r="A97" s="1">
+        <v>46240</v>
+      </c>
+      <c r="B97" s="2">
+        <v>62.84831132017917</v>
+      </c>
+      <c r="C97" s="2">
+        <v>3.420604449750649</v>
+      </c>
+      <c r="D97" s="2">
+        <v>58.1825513102488</v>
+      </c>
+      <c r="E97" s="2">
+        <v>0.7301638878592186</v>
+      </c>
+      <c r="F97" s="2">
+        <v>0.1477900012665325</v>
+      </c>
+      <c r="G97" s="2">
+        <v>0.3672016710539659</v>
+      </c>
+      <c r="H97" s="3">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -3088,13 +3192,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4AA317F-F6C0-43C7-9ECF-5BF338869FA6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F4A0BAF-494A-43EB-9145-29B999E43E48}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF7AF33E-AC1F-4DAE-BCC4-7BA7694C7924}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{891C6A44-DB3C-4830-8406-AB4E5B150A5B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2023B6EB-65F5-42F3-A21C-12BB0A2DCC98}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF172E7E-ABED-4A92-8056-9086D39D65BE}"/>
 </file>
--- a/sea_productive.xlsx
+++ b/sea_productive.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cnxmail.sharepoint.com/sites/WFM-Expedia-HCM/Branding files/BI_Task/CODE/Python_Code/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_22D9AC88D21170F70BB535D05C809441BBDEBD6B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48A04D72-7793-47F4-9CDB-667EAFB30DD7}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -43,13 +49,13 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd;@"/>
-    <numFmt numFmtId="165" formatCode="#,##0.000;[Red]-#,##0.000"/>
-    <numFmt numFmtId="166" formatCode="#,##0;[Red]-#,##0"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000;[Red]\-#,##0.000"/>
+    <numFmt numFmtId="166" formatCode="#,##0;[Red]\-#,##0"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -93,42 +99,65 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="8">
     <dxf>
-      <numFmt numFmtId="164" formatCode="yyyy-mm-dd;@"/>
+      <numFmt numFmtId="166" formatCode="#,##0;[Red]\-#,##0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.000;[Red]-#,##0.000"/>
+      <numFmt numFmtId="165" formatCode="#,##0.000;[Red]\-#,##0.000"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0;[Red]-#,##0"/>
+      <numFmt numFmtId="165" formatCode="#,##0.000;[Red]\-#,##0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="#,##0.000;[Red]\-#,##0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="#,##0.000;[Red]\-#,##0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="#,##0.000;[Red]\-#,##0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="#,##0.000;[Red]\-#,##0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:H33" totalsRowShown="0">
-  <autoFilter ref="A1:H33"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Frame0" displayName="Frame0" ref="A1:H39" totalsRowShown="0">
+  <autoFilter ref="A1:H39" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="8">
-    <tableColumn id="1" name="Date_Converted" dataDxfId="0"/>
-    <tableColumn id="2" name="Staff Hour (In Hours)" dataDxfId="1"/>
-    <tableColumn id="3" name="Total Break (In Hours)" dataDxfId="1"/>
-    <tableColumn id="4" name="THT(In Hours)" dataDxfId="1"/>
-    <tableColumn id="5" name="Avail Time(In Hours)" dataDxfId="1"/>
-    <tableColumn id="6" name="Other Productive Aux(In Hours)" dataDxfId="1"/>
-    <tableColumn id="7" name="Non Productive Aux (In Hours)" dataDxfId="1"/>
-    <tableColumn id="8" name="Present for Calculation" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Date_Converted" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Staff Hour (In Hours)" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Total Break (In Hours)" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="THT(In Hours)" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Avail Time(In Hours)" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Other Productive Aux(In Hours)" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Non Productive Aux (In Hours)" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Present for Calculation" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -166,7 +195,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -200,6 +229,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -234,9 +264,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -409,11 +440,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H33"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -439,15 +480,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46222</v>
       </c>
       <c r="B2" s="2">
-        <v>128.809967017707</v>
+        <v>128.80996701770701</v>
       </c>
       <c r="C2" s="2">
-        <v>24.49508837261134</v>
+        <v>24.495088372611342</v>
       </c>
       <c r="D2" s="2">
         <v>100.6516602932964</v>
@@ -456,7 +497,7 @@
         <v>1.134721109335207</v>
       </c>
       <c r="F2" s="2">
-        <v>0.7353822017378278</v>
+        <v>0.73538220173782776</v>
       </c>
       <c r="G2" s="2">
         <v>1.793115040726132</v>
@@ -465,33 +506,33 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>46223</v>
       </c>
       <c r="B3" s="2">
-        <v>547.39860413207</v>
+        <v>547.39860413206998</v>
       </c>
       <c r="C3" s="2">
-        <v>81.47549627913757</v>
+        <v>81.475496279137573</v>
       </c>
       <c r="D3" s="2">
         <v>416.6683187794755</v>
       </c>
       <c r="E3" s="2">
-        <v>34.53752444881532</v>
+        <v>34.537524448815319</v>
       </c>
       <c r="F3" s="2">
-        <v>6.957641750830743</v>
+        <v>6.9576417508307431</v>
       </c>
       <c r="G3" s="2">
-        <v>7.759622873810844</v>
+        <v>7.7596228738108444</v>
       </c>
       <c r="H3" s="3">
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>46224</v>
       </c>
@@ -499,77 +540,77 @@
         <v>504.4733979579139</v>
       </c>
       <c r="C4" s="2">
-        <v>75.50612567741838</v>
+        <v>75.506125677418382</v>
       </c>
       <c r="D4" s="2">
-        <v>375.3173412815657</v>
+        <v>375.31734128156569</v>
       </c>
       <c r="E4" s="2">
-        <v>48.9593456641983</v>
+        <v>48.959345664198302</v>
       </c>
       <c r="F4" s="2">
         <v>1.25775667178962</v>
       </c>
       <c r="G4" s="2">
-        <v>3.432828662941853</v>
+        <v>3.4328286629418532</v>
       </c>
       <c r="H4" s="3">
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>46225</v>
       </c>
       <c r="B5" s="2">
-        <v>450.5082771122056</v>
+        <v>450.50827711220558</v>
       </c>
       <c r="C5" s="2">
-        <v>68.10940885631261</v>
+        <v>68.109408856312612</v>
       </c>
       <c r="D5" s="2">
-        <v>333.0898195902573</v>
+        <v>333.08981959025732</v>
       </c>
       <c r="E5" s="2">
-        <v>44.25153703402314</v>
+        <v>44.251537034023137</v>
       </c>
       <c r="F5" s="2">
-        <v>1.733442459255457</v>
+        <v>1.7334424592554569</v>
       </c>
       <c r="G5" s="2">
-        <v>3.324069172357106</v>
+        <v>3.3240691723571061</v>
       </c>
       <c r="H5" s="3">
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>46226</v>
       </c>
       <c r="B6" s="2">
-        <v>535.0621526777708</v>
+        <v>535.06215267777077</v>
       </c>
       <c r="C6" s="2">
-        <v>79.53510711406668</v>
+        <v>79.535107114066676</v>
       </c>
       <c r="D6" s="2">
-        <v>405.0616924142274</v>
+        <v>405.06169241422742</v>
       </c>
       <c r="E6" s="2">
-        <v>37.75679362351593</v>
+        <v>37.756793623515932</v>
       </c>
       <c r="F6" s="2">
-        <v>7.109032284869916</v>
+        <v>7.1090322848699161</v>
       </c>
       <c r="G6" s="2">
-        <v>5.599527241090933</v>
+        <v>5.5995272410909331</v>
       </c>
       <c r="H6" s="3">
         <v>59</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>46227</v>
       </c>
@@ -577,25 +618,25 @@
         <v>601.2953243564607</v>
       </c>
       <c r="C7" s="2">
-        <v>92.07236300205192</v>
+        <v>92.072363002051915</v>
       </c>
       <c r="D7" s="2">
-        <v>454.0617388668713</v>
+        <v>454.06173886687128</v>
       </c>
       <c r="E7" s="2">
-        <v>47.5690755702043</v>
+        <v>47.569075570204298</v>
       </c>
       <c r="F7" s="2">
         <v>2.812200804866023</v>
       </c>
       <c r="G7" s="2">
-        <v>4.779287223584122</v>
+        <v>4.7792872235841219</v>
       </c>
       <c r="H7" s="3">
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>46228</v>
       </c>
@@ -606,143 +647,143 @@
         <v>100.3969372175717</v>
       </c>
       <c r="D8" s="2">
-        <v>518.3581134789611</v>
+        <v>518.35811347896106</v>
       </c>
       <c r="E8" s="2">
         <v>49.65858524487949</v>
       </c>
       <c r="F8" s="2">
-        <v>1.96357804313302</v>
+        <v>1.9635780431330201</v>
       </c>
       <c r="G8" s="2">
-        <v>5.536271124275194</v>
+        <v>5.5362711242751939</v>
       </c>
       <c r="H8" s="3">
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>46229</v>
       </c>
       <c r="B9" s="2">
-        <v>695.8043334684645</v>
+        <v>695.80433346846451</v>
       </c>
       <c r="C9" s="2">
-        <v>102.0543588986662</v>
+        <v>102.05435889866619</v>
       </c>
       <c r="D9" s="2">
-        <v>529.0926234221748</v>
+        <v>529.09262342217482</v>
       </c>
       <c r="E9" s="2">
-        <v>59.76118891191151</v>
+        <v>59.761188911911511</v>
       </c>
       <c r="F9" s="2">
         <v>0.1376133308145735</v>
       </c>
       <c r="G9" s="2">
-        <v>4.758548904897438</v>
+        <v>4.7585489048974381</v>
       </c>
       <c r="H9" s="3">
         <v>78</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>46230</v>
       </c>
       <c r="B10" s="2">
-        <v>615.2571711930358</v>
+        <v>615.25717119303579</v>
       </c>
       <c r="C10" s="2">
-        <v>94.45675751003127</v>
+        <v>94.456757510031267</v>
       </c>
       <c r="D10" s="2">
-        <v>447.310195674517</v>
+        <v>447.31019567451699</v>
       </c>
       <c r="E10" s="2">
-        <v>59.31069764828931</v>
+        <v>59.310697648289313</v>
       </c>
       <c r="F10" s="2">
-        <v>8.093636708988084</v>
+        <v>8.0936367089880843</v>
       </c>
       <c r="G10" s="2">
-        <v>6.085883651210202</v>
+        <v>6.0858836512102021</v>
       </c>
       <c r="H10" s="3">
         <v>70</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>46231</v>
       </c>
       <c r="B11" s="2">
-        <v>527.9680008692154</v>
+        <v>527.96800086921542</v>
       </c>
       <c r="C11" s="2">
-        <v>83.43221763606232</v>
+        <v>83.432217636062319</v>
       </c>
       <c r="D11" s="2">
-        <v>381.318357047065</v>
+        <v>381.31835704706498</v>
       </c>
       <c r="E11" s="2">
-        <v>53.2600210875459</v>
+        <v>53.260021087545901</v>
       </c>
       <c r="F11" s="2">
-        <v>5.600065685144315</v>
+        <v>5.6000656851443154</v>
       </c>
       <c r="G11" s="2">
-        <v>4.357339413397842</v>
+        <v>4.3573394133978418</v>
       </c>
       <c r="H11" s="3">
         <v>59</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>46232</v>
       </c>
       <c r="B12" s="2">
-        <v>509.3956852139488</v>
+        <v>509.39568521394881</v>
       </c>
       <c r="C12" s="2">
-        <v>76.62676231575676</v>
+        <v>76.626762315756764</v>
       </c>
       <c r="D12" s="2">
-        <v>304.0351681293862</v>
+        <v>304.03516812938619</v>
       </c>
       <c r="E12" s="2">
         <v>122.4877939276666</v>
       </c>
       <c r="F12" s="2">
-        <v>3.504318906085359</v>
+        <v>3.5043189060853588</v>
       </c>
       <c r="G12" s="2">
-        <v>2.741641935053695</v>
+        <v>2.7416419350536949</v>
       </c>
       <c r="H12" s="3">
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>46233</v>
       </c>
       <c r="B13" s="2">
-        <v>579.2313585470573</v>
+        <v>579.23135854705731</v>
       </c>
       <c r="C13" s="2">
-        <v>88.06546714847286</v>
+        <v>88.065467148472862</v>
       </c>
       <c r="D13" s="2">
-        <v>334.2999982277508</v>
+        <v>334.29999822775079</v>
       </c>
       <c r="E13" s="2">
-        <v>147.1572662327521</v>
+        <v>147.15726623275211</v>
       </c>
       <c r="F13" s="2">
-        <v>6.689186406963401</v>
+        <v>6.6891864069634011</v>
       </c>
       <c r="G13" s="2">
         <v>3.019440531118049</v>
@@ -751,12 +792,12 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>46234</v>
       </c>
       <c r="B14" s="2">
-        <v>623.8103840832575</v>
+        <v>623.81038408325753</v>
       </c>
       <c r="C14" s="2">
         <v>97.08479813368163</v>
@@ -768,33 +809,33 @@
         <v>147.7331233890603</v>
       </c>
       <c r="F14" s="2">
-        <v>9.715374089032412</v>
+        <v>9.7153740890324123</v>
       </c>
       <c r="G14" s="2">
-        <v>2.70284555816816</v>
+        <v>2.7028455581681601</v>
       </c>
       <c r="H14" s="3">
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>46235</v>
       </c>
       <c r="B15" s="2">
-        <v>565.2931019488716</v>
+        <v>565.29310194887159</v>
       </c>
       <c r="C15" s="2">
-        <v>86.45828823079196</v>
+        <v>86.458288230791965</v>
       </c>
       <c r="D15" s="2">
-        <v>387.2233843128031</v>
+        <v>387.22338431280309</v>
       </c>
       <c r="E15" s="2">
-        <v>86.60338854405396</v>
+        <v>86.603388544053956</v>
       </c>
       <c r="F15" s="2">
-        <v>1.145287795017163</v>
+        <v>1.1452877950171629</v>
       </c>
       <c r="G15" s="2">
         <v>3.862753066205316</v>
@@ -803,7 +844,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>46236</v>
       </c>
@@ -811,13 +852,13 @@
         <v>498.7147375152669</v>
       </c>
       <c r="C16" s="2">
-        <v>72.89679199720422</v>
+        <v>72.896791997204218</v>
       </c>
       <c r="D16" s="2">
-        <v>373.4627755125765</v>
+        <v>373.46277551257651</v>
       </c>
       <c r="E16" s="2">
-        <v>47.66907389866059</v>
+        <v>47.669073898660592</v>
       </c>
       <c r="F16" s="2">
         <v>1.584615003383822</v>
@@ -829,90 +870,90 @@
         <v>58</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>46237</v>
       </c>
       <c r="B17" s="2">
-        <v>383.0603397886753</v>
+        <v>383.06033978867532</v>
       </c>
       <c r="C17" s="2">
-        <v>59.61875633161929</v>
+        <v>59.618756331619288</v>
       </c>
       <c r="D17" s="2">
-        <v>277.7001900241358</v>
+        <v>277.70019002413579</v>
       </c>
       <c r="E17" s="2">
-        <v>37.45547256339859</v>
+        <v>37.455472563398587</v>
       </c>
       <c r="F17" s="2">
-        <v>5.411665603762441</v>
+        <v>5.4116656037624411</v>
       </c>
       <c r="G17" s="2">
-        <v>2.874255265759097</v>
+        <v>2.8742552657590972</v>
       </c>
       <c r="H17" s="3">
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>46238</v>
       </c>
       <c r="B18" s="2">
-        <v>495.3746127439921</v>
+        <v>495.37461274399209</v>
       </c>
       <c r="C18" s="2">
         <v>77.56146169803209</v>
       </c>
       <c r="D18" s="2">
-        <v>364.6090605331254</v>
+        <v>364.60906053312539</v>
       </c>
       <c r="E18" s="2">
-        <v>39.69961220235564</v>
+        <v>39.699612202355638</v>
       </c>
       <c r="F18" s="2">
-        <v>8.736412738975551</v>
+        <v>8.7364127389755506</v>
       </c>
       <c r="G18" s="2">
-        <v>4.768065571503507</v>
+        <v>4.7680655715035067</v>
       </c>
       <c r="H18" s="3">
         <v>55</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>46239</v>
       </c>
       <c r="B19" s="2">
-        <v>559.786069975151</v>
+        <v>559.78606997515101</v>
       </c>
       <c r="C19" s="2">
-        <v>86.84341292021175</v>
+        <v>86.843412920211748</v>
       </c>
       <c r="D19" s="2">
-        <v>423.5485508325403</v>
+        <v>423.54855083254029</v>
       </c>
       <c r="E19" s="2">
-        <v>43.37124834599543</v>
+        <v>43.371248345995433</v>
       </c>
       <c r="F19" s="2">
-        <v>3.173914805766609</v>
+        <v>3.1739148057666089</v>
       </c>
       <c r="G19" s="2">
-        <v>2.848943070636855</v>
+        <v>2.8489430706368548</v>
       </c>
       <c r="H19" s="3">
         <v>62</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>46240</v>
       </c>
       <c r="B20" s="2">
-        <v>563.2563497274679</v>
+        <v>563.25634972746786</v>
       </c>
       <c r="C20" s="2">
         <v>86.29151588264439</v>
@@ -921,149 +962,149 @@
         <v>428.9647479771524</v>
       </c>
       <c r="E20" s="2">
-        <v>33.87085392028378</v>
+        <v>33.870853920283778</v>
       </c>
       <c r="F20" s="2">
-        <v>9.909736172200905</v>
+        <v>9.9097361722009047</v>
       </c>
       <c r="G20" s="2">
-        <v>4.219495775186354</v>
+        <v>4.2194957751863544</v>
       </c>
       <c r="H20" s="3">
         <v>64</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>46241</v>
       </c>
       <c r="B21" s="2">
-        <v>661.6727528864249</v>
+        <v>661.67275288642486</v>
       </c>
       <c r="C21" s="2">
         <v>101.1119900993294</v>
       </c>
       <c r="D21" s="2">
-        <v>470.1765665270905</v>
+        <v>470.17656652709047</v>
       </c>
       <c r="E21" s="2">
         <v>69.24319958841221</v>
       </c>
       <c r="F21" s="2">
-        <v>12.57363942900517</v>
+        <v>12.573639429005169</v>
       </c>
       <c r="G21" s="2">
-        <v>8.567357242587541</v>
+        <v>8.5673572425875406</v>
       </c>
       <c r="H21" s="3">
         <v>74</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>46242</v>
       </c>
       <c r="B22" s="2">
-        <v>630.7066306034503</v>
+        <v>630.70663060345032</v>
       </c>
       <c r="C22" s="2">
-        <v>96.99364224351115</v>
+        <v>96.993642243511147</v>
       </c>
       <c r="D22" s="2">
-        <v>513.6310459325841</v>
+        <v>513.63104593258413</v>
       </c>
       <c r="E22" s="2">
-        <v>10.08298638438806</v>
+        <v>10.082986384388059</v>
       </c>
       <c r="F22" s="2">
-        <v>4.709660226263933</v>
+        <v>4.7096602262639333</v>
       </c>
       <c r="G22" s="2">
-        <v>5.289295816702976</v>
+        <v>5.2892958167029764</v>
       </c>
       <c r="H22" s="3">
         <v>71</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>46243</v>
       </c>
       <c r="B23" s="2">
-        <v>544.6174559308317</v>
+        <v>544.61745593083174</v>
       </c>
       <c r="C23" s="2">
-        <v>85.17719129576969</v>
+        <v>85.177191295769688</v>
       </c>
       <c r="D23" s="2">
-        <v>441.0882322196629</v>
+        <v>441.08823221966293</v>
       </c>
       <c r="E23" s="2">
-        <v>8.359348911522991</v>
+        <v>8.3593489115229911</v>
       </c>
       <c r="F23" s="2">
-        <v>4.07531942423847</v>
+        <v>4.0753194242384696</v>
       </c>
       <c r="G23" s="2">
-        <v>5.91736407963766</v>
+        <v>5.9173640796376601</v>
       </c>
       <c r="H23" s="3">
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>46244</v>
       </c>
       <c r="B24" s="2">
-        <v>521.2948620928651</v>
+        <v>521.29486209286506</v>
       </c>
       <c r="C24" s="2">
-        <v>72.00276426413821</v>
+        <v>72.002764264138207</v>
       </c>
       <c r="D24" s="2">
-        <v>370.5284384858344</v>
+        <v>370.52843848583439</v>
       </c>
       <c r="E24" s="2">
         <v>15.57776726235636</v>
       </c>
       <c r="F24" s="2">
-        <v>57.10188593574696</v>
+        <v>57.101885935746957</v>
       </c>
       <c r="G24" s="2">
-        <v>6.083246422596017</v>
+        <v>6.0832464225960168</v>
       </c>
       <c r="H24" s="3">
         <v>68</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>46245</v>
       </c>
       <c r="B25" s="2">
-        <v>453.4820830961413</v>
+        <v>453.48208309614131</v>
       </c>
       <c r="C25" s="2">
-        <v>62.20752357936153</v>
+        <v>62.207523579361528</v>
       </c>
       <c r="D25" s="2">
-        <v>331.7485437463775</v>
+        <v>331.74854374637749</v>
       </c>
       <c r="E25" s="2">
-        <v>21.63390863743093</v>
+        <v>21.633908637430931</v>
       </c>
       <c r="F25" s="2">
-        <v>35.14755184718305</v>
+        <v>35.147551847183053</v>
       </c>
       <c r="G25" s="2">
-        <v>2.744555285788245</v>
+        <v>2.7445552857882451</v>
       </c>
       <c r="H25" s="3">
         <v>54</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>46246</v>
       </c>
@@ -1074,33 +1115,33 @@
         <v>64.06988657807311</v>
       </c>
       <c r="D26" s="2">
-        <v>341.3200201503125</v>
+        <v>341.32002015031247</v>
       </c>
       <c r="E26" s="2">
-        <v>25.71865660493159</v>
+        <v>25.718656604931589</v>
       </c>
       <c r="F26" s="2">
-        <v>94.79686236748265</v>
+        <v>94.796862367482646</v>
       </c>
       <c r="G26" s="2">
-        <v>2.31879750325448</v>
+        <v>2.3187975032544799</v>
       </c>
       <c r="H26" s="3">
         <v>64</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>46247</v>
       </c>
       <c r="B27" s="2">
-        <v>430.6436248829863</v>
+        <v>430.64362488298627</v>
       </c>
       <c r="C27" s="2">
-        <v>62.82694961813589</v>
+        <v>62.826949618135892</v>
       </c>
       <c r="D27" s="2">
-        <v>332.1147064085837</v>
+        <v>332.11470640858369</v>
       </c>
       <c r="E27" s="2">
         <v>21.42559106844374</v>
@@ -1109,30 +1150,30 @@
         <v>10.92816330679589</v>
       </c>
       <c r="G27" s="2">
-        <v>3.348214481026969</v>
+        <v>3.3482144810269689</v>
       </c>
       <c r="H27" s="3">
         <v>47</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>46248</v>
       </c>
       <c r="B28" s="2">
-        <v>493.5921287655228</v>
+        <v>493.59212876552277</v>
       </c>
       <c r="C28" s="2">
-        <v>73.37003969308402</v>
+        <v>73.370039693084024</v>
       </c>
       <c r="D28" s="2">
         <v>390.0046407809499</v>
       </c>
       <c r="E28" s="2">
-        <v>22.33588750680702</v>
+        <v>22.335887506807019</v>
       </c>
       <c r="F28" s="2">
-        <v>4.353428290817472</v>
+        <v>4.3534282908174724</v>
       </c>
       <c r="G28" s="2">
         <v>3.528132493864331</v>
@@ -1141,24 +1182,24 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>46249</v>
       </c>
       <c r="B29" s="2">
-        <v>630.7907854192832</v>
+        <v>630.79078541928322</v>
       </c>
       <c r="C29" s="2">
-        <v>94.19717707108707</v>
+        <v>94.197177071087069</v>
       </c>
       <c r="D29" s="2">
-        <v>391.5434194185816</v>
+        <v>391.54341941858161</v>
       </c>
       <c r="E29" s="2">
-        <v>13.42661195987836</v>
+        <v>13.426611959878359</v>
       </c>
       <c r="F29" s="2">
-        <v>128.3339636232124</v>
+        <v>128.33396362321241</v>
       </c>
       <c r="G29" s="2">
         <v>3.289613346523709</v>
@@ -1167,18 +1208,18 @@
         <v>73</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>46250</v>
       </c>
       <c r="B30" s="2">
-        <v>451.855331223694</v>
+        <v>451.85533122369401</v>
       </c>
       <c r="C30" s="2">
-        <v>67.59346960393918</v>
+        <v>67.593469603939184</v>
       </c>
       <c r="D30" s="2">
-        <v>253.3830774407733</v>
+        <v>253.38307744077329</v>
       </c>
       <c r="E30" s="2">
         <v>18.29030030822355</v>
@@ -1193,24 +1234,24 @@
         <v>57</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>46251</v>
       </c>
       <c r="B31" s="2">
-        <v>444.199633403977</v>
+        <v>444.19963340397697</v>
       </c>
       <c r="C31" s="2">
-        <v>69.22938482354188</v>
+        <v>69.229384823541878</v>
       </c>
       <c r="D31" s="2">
         <v>339.3426651748473</v>
       </c>
       <c r="E31" s="2">
-        <v>28.79228700278249</v>
+        <v>28.792287002782491</v>
       </c>
       <c r="F31" s="2">
-        <v>4.241608050283459</v>
+        <v>4.2416080502834594</v>
       </c>
       <c r="G31" s="2">
         <v>2.593688352521923</v>
@@ -1219,24 +1260,24 @@
         <v>49</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>46252</v>
       </c>
       <c r="B32" s="2">
-        <v>660.0068933520937</v>
+        <v>663.99991174402078</v>
       </c>
       <c r="C32" s="2">
-        <v>98.82585904525904</v>
+        <v>98.825859045259037</v>
       </c>
       <c r="D32" s="2">
-        <v>351.6171757395012</v>
+        <v>351.61717573950119</v>
       </c>
       <c r="E32" s="2">
-        <v>47.28481394486088</v>
+        <v>47.284813944860879</v>
       </c>
       <c r="F32" s="2">
-        <v>159.0047434975041</v>
+        <v>162.99776188943119</v>
       </c>
       <c r="G32" s="2">
         <v>3.274301124968463</v>
@@ -1245,30 +1286,186 @@
         <v>76</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>46253</v>
       </c>
       <c r="B33" s="2">
-        <v>334.3851231003724</v>
+        <v>694.63439370326262</v>
       </c>
       <c r="C33" s="2">
-        <v>52.6768523040745</v>
+        <v>105.4410611541889</v>
       </c>
       <c r="D33" s="2">
-        <v>217.582416688246</v>
+        <v>375.30410813305423</v>
       </c>
       <c r="E33" s="2">
-        <v>45.37606633709097</v>
+        <v>51.185770811071983</v>
       </c>
       <c r="F33" s="2">
-        <v>16.2140288545895</v>
+        <v>159.73487969220099</v>
       </c>
       <c r="G33" s="2">
-        <v>2.535758916371399</v>
+        <v>2.9685739127463759</v>
       </c>
       <c r="H33" s="3">
-        <v>45</v>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B34" s="2">
+        <v>699.10081959158458</v>
+      </c>
+      <c r="C34" s="2">
+        <v>104.7918750341363</v>
+      </c>
+      <c r="D34" s="2">
+        <v>342.15253555600049</v>
+      </c>
+      <c r="E34" s="2">
+        <v>86.095480821252693</v>
+      </c>
+      <c r="F34" s="2">
+        <v>162.5039526316296</v>
+      </c>
+      <c r="G34" s="2">
+        <v>3.5569755485653878</v>
+      </c>
+      <c r="H34" s="3">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>46255</v>
+      </c>
+      <c r="B35" s="2">
+        <v>753.62975155918832</v>
+      </c>
+      <c r="C35" s="2">
+        <v>108.19687197884279</v>
+      </c>
+      <c r="D35" s="2">
+        <v>357.88138375552472</v>
+      </c>
+      <c r="E35" s="2">
+        <v>106.1723560326712</v>
+      </c>
+      <c r="F35" s="2">
+        <v>178.1908817241675</v>
+      </c>
+      <c r="G35" s="2">
+        <v>3.1882580679820638</v>
+      </c>
+      <c r="H35" s="3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>46256</v>
+      </c>
+      <c r="B36" s="2">
+        <v>806.8052939721432</v>
+      </c>
+      <c r="C36" s="2">
+        <v>119.715860667386</v>
+      </c>
+      <c r="D36" s="2">
+        <v>354.39638628257927</v>
+      </c>
+      <c r="E36" s="2">
+        <v>155.07115230291049</v>
+      </c>
+      <c r="F36" s="2">
+        <v>173.78248750738331</v>
+      </c>
+      <c r="G36" s="2">
+        <v>3.839407211884132</v>
+      </c>
+      <c r="H36" s="3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <v>46257</v>
+      </c>
+      <c r="B37" s="2">
+        <v>509.71101574216169</v>
+      </c>
+      <c r="C37" s="2">
+        <v>80.476073851717842</v>
+      </c>
+      <c r="D37" s="2">
+        <v>276.7035884362291</v>
+      </c>
+      <c r="E37" s="2">
+        <v>148.7255431878624</v>
+      </c>
+      <c r="F37" s="2">
+        <v>1.531809989429183</v>
+      </c>
+      <c r="G37" s="2">
+        <v>2.27400027692318</v>
+      </c>
+      <c r="H37" s="3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>46258</v>
+      </c>
+      <c r="B38" s="2">
+        <v>549.37150319815999</v>
+      </c>
+      <c r="C38" s="2">
+        <v>88.838087343821925</v>
+      </c>
+      <c r="D38" s="2">
+        <v>328.92196055745887</v>
+      </c>
+      <c r="E38" s="2">
+        <v>110.2758588733835</v>
+      </c>
+      <c r="F38" s="2">
+        <v>17.277070292250979</v>
+      </c>
+      <c r="G38" s="2">
+        <v>4.0585261312447898</v>
+      </c>
+      <c r="H38" s="3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
+        <v>46259</v>
+      </c>
+      <c r="B39" s="2">
+        <v>291.51065943485639</v>
+      </c>
+      <c r="C39" s="2">
+        <v>45.212950681770842</v>
+      </c>
+      <c r="D39" s="2">
+        <v>141.9303877499006</v>
+      </c>
+      <c r="E39" s="2">
+        <v>99.898335480472696</v>
+      </c>
+      <c r="F39" s="2">
+        <v>3.2041005372173261</v>
+      </c>
+      <c r="G39" s="2">
+        <v>1.2648849854949451</v>
+      </c>
+      <c r="H39" s="3">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1280,6 +1477,33 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="98e5d340-1856-43f4-9776-f0c5fe464598">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="0b1f5c80-8d6b-48f0-84f6-ea4845a21fc7" xsi:nil="true"/>
+    <Owner xmlns="98e5d340-1856-43f4-9776-f0c5fe464598">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Owner>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ED34050369F83D419D9CDC413B23CD9E" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="34f0fc59c9e9af6707b4260e15f92132">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="98e5d340-1856-43f4-9776-f0c5fe464598" xmlns:ns3="0b1f5c80-8d6b-48f0-84f6-ea4845a21fc7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="07a1a8fd5e9c2307366362e961f0f77e" ns2:_="" ns3:_="">
     <xsd:import namespace="98e5d340-1856-43f4-9776-f0c5fe464598"/>
@@ -1500,41 +1724,40 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="98e5d340-1856-43f4-9776-f0c5fe464598">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="0b1f5c80-8d6b-48f0-84f6-ea4845a21fc7" xsi:nil="true"/>
-    <Owner xmlns="98e5d340-1856-43f4-9776-f0c5fe464598">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Owner>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93A96EB0-B321-4888-95CC-D3FE0BFA6CB6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A9C776B-A62A-45AB-BC1C-78ED891AB8D5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="98e5d340-1856-43f4-9776-f0c5fe464598"/>
+    <ds:schemaRef ds:uri="0b1f5c80-8d6b-48f0-84f6-ea4845a21fc7"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{719A2E94-A706-4728-8C42-8ABEE05F9164}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF6E3674-AF72-4E1D-8B3E-07BDE01452F1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7378001-63C1-4611-A211-1EA93E5B006D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B7E3D98-EF0E-434F-A003-6047277231B3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="98e5d340-1856-43f4-9776-f0c5fe464598"/>
+    <ds:schemaRef ds:uri="0b1f5c80-8d6b-48f0-84f6-ea4845a21fc7"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/sea_productive.xlsx
+++ b/sea_productive.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cnxmail.sharepoint.com/sites/WFM-Expedia-HCM/Branding files/BI_Task/CODE/Python_Code/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_22D9AC88D21170F70BB535D05C809441BBDEBD6B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48A04D72-7793-47F4-9CDB-667EAFB30DD7}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -49,13 +43,13 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="165" formatCode="#,##0.000;[Red]\-#,##0.000"/>
-    <numFmt numFmtId="166" formatCode="#,##0;[Red]\-#,##0"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd;@"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000;[Red]-#,##0.000"/>
+    <numFmt numFmtId="166" formatCode="#,##0;[Red]-#,##0"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -99,65 +93,42 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="3">
     <dxf>
-      <numFmt numFmtId="166" formatCode="#,##0;[Red]\-#,##0"/>
+      <numFmt numFmtId="164" formatCode="yyyy-mm-dd;@"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.000;[Red]\-#,##0.000"/>
+      <numFmt numFmtId="165" formatCode="#,##0.000;[Red]-#,##0.000"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.000;[Red]\-#,##0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.000;[Red]\-#,##0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.000;[Red]\-#,##0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.000;[Red]\-#,##0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.000;[Red]\-#,##0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+      <numFmt numFmtId="166" formatCode="#,##0;[Red]-#,##0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Frame0" displayName="Frame0" ref="A1:H39" totalsRowShown="0">
-  <autoFilter ref="A1:H39" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:H40" totalsRowShown="0">
+  <autoFilter ref="A1:H40"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Date_Converted" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Staff Hour (In Hours)" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Total Break (In Hours)" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="THT(In Hours)" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Avail Time(In Hours)" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Other Productive Aux(In Hours)" dataDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Non Productive Aux (In Hours)" dataDxfId="1"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Present for Calculation" dataDxfId="0"/>
+    <tableColumn id="1" name="Date_Converted" dataDxfId="0"/>
+    <tableColumn id="2" name="Staff Hour (In Hours)" dataDxfId="1"/>
+    <tableColumn id="3" name="Total Break (In Hours)" dataDxfId="1"/>
+    <tableColumn id="4" name="THT(In Hours)" dataDxfId="1"/>
+    <tableColumn id="5" name="Avail Time(In Hours)" dataDxfId="1"/>
+    <tableColumn id="6" name="Other Productive Aux(In Hours)" dataDxfId="1"/>
+    <tableColumn id="7" name="Non Productive Aux (In Hours)" dataDxfId="1"/>
+    <tableColumn id="8" name="Present for Calculation" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -195,7 +166,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -229,7 +200,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -264,10 +234,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -440,21 +409,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H39"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="31.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.85546875" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H40"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -480,15 +439,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" s="1">
         <v>46222</v>
       </c>
       <c r="B2" s="2">
-        <v>128.80996701770701</v>
+        <v>128.809967017707</v>
       </c>
       <c r="C2" s="2">
-        <v>24.495088372611342</v>
+        <v>24.49508837261134</v>
       </c>
       <c r="D2" s="2">
         <v>100.6516602932964</v>
@@ -497,7 +456,7 @@
         <v>1.134721109335207</v>
       </c>
       <c r="F2" s="2">
-        <v>0.73538220173782776</v>
+        <v>0.7353822017378278</v>
       </c>
       <c r="G2" s="2">
         <v>1.793115040726132</v>
@@ -506,33 +465,33 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>46223</v>
       </c>
       <c r="B3" s="2">
-        <v>547.39860413206998</v>
+        <v>547.39860413207</v>
       </c>
       <c r="C3" s="2">
-        <v>81.475496279137573</v>
+        <v>81.47549627913757</v>
       </c>
       <c r="D3" s="2">
         <v>416.6683187794755</v>
       </c>
       <c r="E3" s="2">
-        <v>34.537524448815319</v>
+        <v>34.53752444881532</v>
       </c>
       <c r="F3" s="2">
-        <v>6.9576417508307431</v>
+        <v>6.957641750830743</v>
       </c>
       <c r="G3" s="2">
-        <v>7.7596228738108444</v>
+        <v>7.759622873810844</v>
       </c>
       <c r="H3" s="3">
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>46224</v>
       </c>
@@ -540,77 +499,77 @@
         <v>504.4733979579139</v>
       </c>
       <c r="C4" s="2">
-        <v>75.506125677418382</v>
+        <v>75.50612567741838</v>
       </c>
       <c r="D4" s="2">
-        <v>375.31734128156569</v>
+        <v>375.3173412815657</v>
       </c>
       <c r="E4" s="2">
-        <v>48.959345664198302</v>
+        <v>48.9593456641983</v>
       </c>
       <c r="F4" s="2">
         <v>1.25775667178962</v>
       </c>
       <c r="G4" s="2">
-        <v>3.4328286629418532</v>
+        <v>3.432828662941853</v>
       </c>
       <c r="H4" s="3">
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>46225</v>
       </c>
       <c r="B5" s="2">
-        <v>450.50827711220558</v>
+        <v>450.5082771122056</v>
       </c>
       <c r="C5" s="2">
-        <v>68.109408856312612</v>
+        <v>68.10940885631261</v>
       </c>
       <c r="D5" s="2">
-        <v>333.08981959025732</v>
+        <v>333.0898195902573</v>
       </c>
       <c r="E5" s="2">
-        <v>44.251537034023137</v>
+        <v>44.25153703402314</v>
       </c>
       <c r="F5" s="2">
-        <v>1.7334424592554569</v>
+        <v>1.733442459255457</v>
       </c>
       <c r="G5" s="2">
-        <v>3.3240691723571061</v>
+        <v>3.324069172357106</v>
       </c>
       <c r="H5" s="3">
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
         <v>46226</v>
       </c>
       <c r="B6" s="2">
-        <v>535.06215267777077</v>
+        <v>535.0621526777708</v>
       </c>
       <c r="C6" s="2">
-        <v>79.535107114066676</v>
+        <v>79.53510711406668</v>
       </c>
       <c r="D6" s="2">
-        <v>405.06169241422742</v>
+        <v>405.0616924142274</v>
       </c>
       <c r="E6" s="2">
-        <v>37.756793623515932</v>
+        <v>37.75679362351593</v>
       </c>
       <c r="F6" s="2">
-        <v>7.1090322848699161</v>
+        <v>7.109032284869916</v>
       </c>
       <c r="G6" s="2">
-        <v>5.5995272410909331</v>
+        <v>5.599527241090933</v>
       </c>
       <c r="H6" s="3">
         <v>59</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8">
       <c r="A7" s="1">
         <v>46227</v>
       </c>
@@ -618,25 +577,25 @@
         <v>601.2953243564607</v>
       </c>
       <c r="C7" s="2">
-        <v>92.072363002051915</v>
+        <v>92.07236300205192</v>
       </c>
       <c r="D7" s="2">
-        <v>454.06173886687128</v>
+        <v>454.0617388668713</v>
       </c>
       <c r="E7" s="2">
-        <v>47.569075570204298</v>
+        <v>47.5690755702043</v>
       </c>
       <c r="F7" s="2">
         <v>2.812200804866023</v>
       </c>
       <c r="G7" s="2">
-        <v>4.7792872235841219</v>
+        <v>4.779287223584122</v>
       </c>
       <c r="H7" s="3">
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8">
       <c r="A8" s="1">
         <v>46228</v>
       </c>
@@ -647,143 +606,143 @@
         <v>100.3969372175717</v>
       </c>
       <c r="D8" s="2">
-        <v>518.35811347896106</v>
+        <v>518.3581134789611</v>
       </c>
       <c r="E8" s="2">
         <v>49.65858524487949</v>
       </c>
       <c r="F8" s="2">
-        <v>1.9635780431330201</v>
+        <v>1.96357804313302</v>
       </c>
       <c r="G8" s="2">
-        <v>5.5362711242751939</v>
+        <v>5.536271124275194</v>
       </c>
       <c r="H8" s="3">
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8">
       <c r="A9" s="1">
         <v>46229</v>
       </c>
       <c r="B9" s="2">
-        <v>695.80433346846451</v>
+        <v>695.8043334684645</v>
       </c>
       <c r="C9" s="2">
-        <v>102.05435889866619</v>
+        <v>102.0543588986662</v>
       </c>
       <c r="D9" s="2">
-        <v>529.09262342217482</v>
+        <v>529.0926234221748</v>
       </c>
       <c r="E9" s="2">
-        <v>59.761188911911511</v>
+        <v>59.76118891191151</v>
       </c>
       <c r="F9" s="2">
         <v>0.1376133308145735</v>
       </c>
       <c r="G9" s="2">
-        <v>4.7585489048974381</v>
+        <v>4.758548904897438</v>
       </c>
       <c r="H9" s="3">
         <v>78</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8">
       <c r="A10" s="1">
         <v>46230</v>
       </c>
       <c r="B10" s="2">
-        <v>615.25717119303579</v>
+        <v>615.2571711930358</v>
       </c>
       <c r="C10" s="2">
-        <v>94.456757510031267</v>
+        <v>94.45675751003127</v>
       </c>
       <c r="D10" s="2">
-        <v>447.31019567451699</v>
+        <v>447.310195674517</v>
       </c>
       <c r="E10" s="2">
-        <v>59.310697648289313</v>
+        <v>59.31069764828931</v>
       </c>
       <c r="F10" s="2">
-        <v>8.0936367089880843</v>
+        <v>8.093636708988084</v>
       </c>
       <c r="G10" s="2">
-        <v>6.0858836512102021</v>
+        <v>6.085883651210202</v>
       </c>
       <c r="H10" s="3">
         <v>70</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8">
       <c r="A11" s="1">
         <v>46231</v>
       </c>
       <c r="B11" s="2">
-        <v>527.96800086921542</v>
+        <v>527.9680008692154</v>
       </c>
       <c r="C11" s="2">
-        <v>83.432217636062319</v>
+        <v>83.43221763606232</v>
       </c>
       <c r="D11" s="2">
-        <v>381.31835704706498</v>
+        <v>381.318357047065</v>
       </c>
       <c r="E11" s="2">
-        <v>53.260021087545901</v>
+        <v>53.2600210875459</v>
       </c>
       <c r="F11" s="2">
-        <v>5.6000656851443154</v>
+        <v>5.600065685144315</v>
       </c>
       <c r="G11" s="2">
-        <v>4.3573394133978418</v>
+        <v>4.357339413397842</v>
       </c>
       <c r="H11" s="3">
         <v>59</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8">
       <c r="A12" s="1">
         <v>46232</v>
       </c>
       <c r="B12" s="2">
-        <v>509.39568521394881</v>
+        <v>509.3956852139488</v>
       </c>
       <c r="C12" s="2">
-        <v>76.626762315756764</v>
+        <v>76.62676231575676</v>
       </c>
       <c r="D12" s="2">
-        <v>304.03516812938619</v>
+        <v>304.0351681293862</v>
       </c>
       <c r="E12" s="2">
         <v>122.4877939276666</v>
       </c>
       <c r="F12" s="2">
-        <v>3.5043189060853588</v>
+        <v>3.504318906085359</v>
       </c>
       <c r="G12" s="2">
-        <v>2.7416419350536949</v>
+        <v>2.741641935053695</v>
       </c>
       <c r="H12" s="3">
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8">
       <c r="A13" s="1">
         <v>46233</v>
       </c>
       <c r="B13" s="2">
-        <v>579.23135854705731</v>
+        <v>579.2313585470573</v>
       </c>
       <c r="C13" s="2">
-        <v>88.065467148472862</v>
+        <v>88.06546714847286</v>
       </c>
       <c r="D13" s="2">
-        <v>334.29999822775079</v>
+        <v>334.2999982277508</v>
       </c>
       <c r="E13" s="2">
-        <v>147.15726623275211</v>
+        <v>147.1572662327521</v>
       </c>
       <c r="F13" s="2">
-        <v>6.6891864069634011</v>
+        <v>6.689186406963401</v>
       </c>
       <c r="G13" s="2">
         <v>3.019440531118049</v>
@@ -792,12 +751,12 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8">
       <c r="A14" s="1">
         <v>46234</v>
       </c>
       <c r="B14" s="2">
-        <v>623.81038408325753</v>
+        <v>623.8103840832575</v>
       </c>
       <c r="C14" s="2">
         <v>97.08479813368163</v>
@@ -809,33 +768,33 @@
         <v>147.7331233890603</v>
       </c>
       <c r="F14" s="2">
-        <v>9.7153740890324123</v>
+        <v>9.715374089032412</v>
       </c>
       <c r="G14" s="2">
-        <v>2.7028455581681601</v>
+        <v>2.70284555816816</v>
       </c>
       <c r="H14" s="3">
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8">
       <c r="A15" s="1">
         <v>46235</v>
       </c>
       <c r="B15" s="2">
-        <v>565.29310194887159</v>
+        <v>565.2931019488716</v>
       </c>
       <c r="C15" s="2">
-        <v>86.458288230791965</v>
+        <v>86.45828823079196</v>
       </c>
       <c r="D15" s="2">
-        <v>387.22338431280309</v>
+        <v>387.2233843128031</v>
       </c>
       <c r="E15" s="2">
-        <v>86.603388544053956</v>
+        <v>86.60338854405396</v>
       </c>
       <c r="F15" s="2">
-        <v>1.1452877950171629</v>
+        <v>1.145287795017163</v>
       </c>
       <c r="G15" s="2">
         <v>3.862753066205316</v>
@@ -844,7 +803,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8">
       <c r="A16" s="1">
         <v>46236</v>
       </c>
@@ -852,13 +811,13 @@
         <v>498.7147375152669</v>
       </c>
       <c r="C16" s="2">
-        <v>72.896791997204218</v>
+        <v>72.89679199720422</v>
       </c>
       <c r="D16" s="2">
-        <v>373.46277551257651</v>
+        <v>373.4627755125765</v>
       </c>
       <c r="E16" s="2">
-        <v>47.669073898660592</v>
+        <v>47.66907389866059</v>
       </c>
       <c r="F16" s="2">
         <v>1.584615003383822</v>
@@ -870,90 +829,90 @@
         <v>58</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8">
       <c r="A17" s="1">
         <v>46237</v>
       </c>
       <c r="B17" s="2">
-        <v>383.06033978867532</v>
+        <v>383.0603397886753</v>
       </c>
       <c r="C17" s="2">
-        <v>59.618756331619288</v>
+        <v>59.61875633161929</v>
       </c>
       <c r="D17" s="2">
-        <v>277.70019002413579</v>
+        <v>277.7001900241358</v>
       </c>
       <c r="E17" s="2">
-        <v>37.455472563398587</v>
+        <v>37.45547256339859</v>
       </c>
       <c r="F17" s="2">
-        <v>5.4116656037624411</v>
+        <v>5.411665603762441</v>
       </c>
       <c r="G17" s="2">
-        <v>2.8742552657590972</v>
+        <v>2.874255265759097</v>
       </c>
       <c r="H17" s="3">
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8">
       <c r="A18" s="1">
         <v>46238</v>
       </c>
       <c r="B18" s="2">
-        <v>495.37461274399209</v>
+        <v>495.3746127439921</v>
       </c>
       <c r="C18" s="2">
         <v>77.56146169803209</v>
       </c>
       <c r="D18" s="2">
-        <v>364.60906053312539</v>
+        <v>364.6090605331254</v>
       </c>
       <c r="E18" s="2">
-        <v>39.699612202355638</v>
+        <v>39.69961220235564</v>
       </c>
       <c r="F18" s="2">
-        <v>8.7364127389755506</v>
+        <v>8.736412738975551</v>
       </c>
       <c r="G18" s="2">
-        <v>4.7680655715035067</v>
+        <v>4.768065571503507</v>
       </c>
       <c r="H18" s="3">
         <v>55</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8">
       <c r="A19" s="1">
         <v>46239</v>
       </c>
       <c r="B19" s="2">
-        <v>559.78606997515101</v>
+        <v>559.786069975151</v>
       </c>
       <c r="C19" s="2">
-        <v>86.843412920211748</v>
+        <v>86.84341292021175</v>
       </c>
       <c r="D19" s="2">
-        <v>423.54855083254029</v>
+        <v>423.5485508325403</v>
       </c>
       <c r="E19" s="2">
-        <v>43.371248345995433</v>
+        <v>43.37124834599543</v>
       </c>
       <c r="F19" s="2">
-        <v>3.1739148057666089</v>
+        <v>3.173914805766609</v>
       </c>
       <c r="G19" s="2">
-        <v>2.8489430706368548</v>
+        <v>2.848943070636855</v>
       </c>
       <c r="H19" s="3">
         <v>62</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8">
       <c r="A20" s="1">
         <v>46240</v>
       </c>
       <c r="B20" s="2">
-        <v>563.25634972746786</v>
+        <v>563.2563497274679</v>
       </c>
       <c r="C20" s="2">
         <v>86.29151588264439</v>
@@ -962,186 +921,186 @@
         <v>428.9647479771524</v>
       </c>
       <c r="E20" s="2">
-        <v>33.870853920283778</v>
+        <v>33.87085392028378</v>
       </c>
       <c r="F20" s="2">
-        <v>9.9097361722009047</v>
+        <v>9.909736172200905</v>
       </c>
       <c r="G20" s="2">
-        <v>4.2194957751863544</v>
+        <v>4.219495775186354</v>
       </c>
       <c r="H20" s="3">
         <v>64</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8">
       <c r="A21" s="1">
         <v>46241</v>
       </c>
       <c r="B21" s="2">
-        <v>661.67275288642486</v>
+        <v>661.6727528864249</v>
       </c>
       <c r="C21" s="2">
         <v>101.1119900993294</v>
       </c>
       <c r="D21" s="2">
-        <v>470.17656652709047</v>
+        <v>470.1765665270905</v>
       </c>
       <c r="E21" s="2">
         <v>69.24319958841221</v>
       </c>
       <c r="F21" s="2">
-        <v>12.573639429005169</v>
+        <v>12.57363942900517</v>
       </c>
       <c r="G21" s="2">
-        <v>8.5673572425875406</v>
+        <v>8.567357242587541</v>
       </c>
       <c r="H21" s="3">
         <v>74</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8">
       <c r="A22" s="1">
         <v>46242</v>
       </c>
       <c r="B22" s="2">
-        <v>630.70663060345032</v>
+        <v>630.7066306034503</v>
       </c>
       <c r="C22" s="2">
-        <v>96.993642243511147</v>
+        <v>96.99364224351115</v>
       </c>
       <c r="D22" s="2">
-        <v>513.63104593258413</v>
+        <v>513.6310459325841</v>
       </c>
       <c r="E22" s="2">
-        <v>10.082986384388059</v>
+        <v>10.08298638438806</v>
       </c>
       <c r="F22" s="2">
-        <v>4.7096602262639333</v>
+        <v>4.709660226263933</v>
       </c>
       <c r="G22" s="2">
-        <v>5.2892958167029764</v>
+        <v>5.289295816702976</v>
       </c>
       <c r="H22" s="3">
         <v>71</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8">
       <c r="A23" s="1">
         <v>46243</v>
       </c>
       <c r="B23" s="2">
-        <v>544.61745593083174</v>
+        <v>544.6174559308317</v>
       </c>
       <c r="C23" s="2">
-        <v>85.177191295769688</v>
+        <v>85.17719129576969</v>
       </c>
       <c r="D23" s="2">
-        <v>441.08823221966293</v>
+        <v>441.0882322196629</v>
       </c>
       <c r="E23" s="2">
-        <v>8.3593489115229911</v>
+        <v>8.359348911522991</v>
       </c>
       <c r="F23" s="2">
-        <v>4.0753194242384696</v>
+        <v>4.07531942423847</v>
       </c>
       <c r="G23" s="2">
-        <v>5.9173640796376601</v>
+        <v>5.91736407963766</v>
       </c>
       <c r="H23" s="3">
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8">
       <c r="A24" s="1">
         <v>46244</v>
       </c>
       <c r="B24" s="2">
-        <v>521.29486209286506</v>
+        <v>462.4270792535519</v>
       </c>
       <c r="C24" s="2">
-        <v>72.002764264138207</v>
+        <v>67.82130650916861</v>
       </c>
       <c r="D24" s="2">
-        <v>370.52843848583439</v>
+        <v>368.1042746230531</v>
       </c>
       <c r="E24" s="2">
-        <v>15.57776726235636</v>
+        <v>15.39954031768462</v>
       </c>
       <c r="F24" s="2">
-        <v>57.101885935746957</v>
+        <v>5.55911361116502</v>
       </c>
       <c r="G24" s="2">
-        <v>6.0832464225960168</v>
+        <v>5.542084470287534</v>
       </c>
       <c r="H24" s="3">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" s="1">
         <v>46245</v>
       </c>
       <c r="B25" s="2">
-        <v>453.48208309614131</v>
+        <v>420.5265529979246</v>
       </c>
       <c r="C25" s="2">
-        <v>62.207523579361528</v>
+        <v>62.20752357936153</v>
       </c>
       <c r="D25" s="2">
-        <v>331.74854374637749</v>
+        <v>326.5304832160408</v>
       </c>
       <c r="E25" s="2">
-        <v>21.633908637430931</v>
+        <v>21.49635530477597</v>
       </c>
       <c r="F25" s="2">
-        <v>35.147551847183053</v>
+        <v>7.704421999106804</v>
       </c>
       <c r="G25" s="2">
-        <v>2.7445552857882451</v>
+        <v>2.587768898639414</v>
       </c>
       <c r="H25" s="3">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" s="1">
         <v>46246</v>
       </c>
       <c r="B26" s="2">
-        <v>528.2242232040544</v>
+        <v>443.1221675652204</v>
       </c>
       <c r="C26" s="2">
         <v>64.06988657807311</v>
       </c>
       <c r="D26" s="2">
-        <v>341.32002015031247</v>
+        <v>335.2939479168732</v>
       </c>
       <c r="E26" s="2">
-        <v>25.718656604931589</v>
+        <v>25.42092049325092</v>
       </c>
       <c r="F26" s="2">
-        <v>94.796862367482646</v>
+        <v>16.16713979319566</v>
       </c>
       <c r="G26" s="2">
-        <v>2.3187975032544799</v>
+        <v>2.170272783827451</v>
       </c>
       <c r="H26" s="3">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
       <c r="A27" s="1">
         <v>46247</v>
       </c>
       <c r="B27" s="2">
-        <v>430.64362488298627</v>
+        <v>430.6436248829863</v>
       </c>
       <c r="C27" s="2">
-        <v>62.826949618135892</v>
+        <v>62.82694961813589</v>
       </c>
       <c r="D27" s="2">
-        <v>332.11470640858369</v>
+        <v>332.1147064085837</v>
       </c>
       <c r="E27" s="2">
         <v>21.42559106844374</v>
@@ -1150,322 +1109,348 @@
         <v>10.92816330679589</v>
       </c>
       <c r="G27" s="2">
-        <v>3.3482144810269689</v>
+        <v>3.348214481026969</v>
       </c>
       <c r="H27" s="3">
         <v>47</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8">
       <c r="A28" s="1">
         <v>46248</v>
       </c>
       <c r="B28" s="2">
-        <v>493.59212876552277</v>
+        <v>490.517745434921</v>
       </c>
       <c r="C28" s="2">
-        <v>73.370039693084024</v>
+        <v>73.37003969308402</v>
       </c>
       <c r="D28" s="2">
-        <v>390.0046407809499</v>
+        <v>387.088244946605</v>
       </c>
       <c r="E28" s="2">
-        <v>22.335887506807019</v>
+        <v>22.24108584225592</v>
       </c>
       <c r="F28" s="2">
-        <v>4.3534282908174724</v>
+        <v>4.353428290817472</v>
       </c>
       <c r="G28" s="2">
-        <v>3.528132493864331</v>
+        <v>3.464946662158602</v>
       </c>
       <c r="H28" s="3">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
       <c r="A29" s="1">
         <v>46249</v>
       </c>
       <c r="B29" s="2">
-        <v>630.79078541928322</v>
+        <v>499.2150502190239</v>
       </c>
       <c r="C29" s="2">
-        <v>94.197177071087069</v>
+        <v>74.85895852548795</v>
       </c>
       <c r="D29" s="2">
-        <v>391.54341941858161</v>
+        <v>388.1090160822968</v>
       </c>
       <c r="E29" s="2">
-        <v>13.426611959878359</v>
+        <v>13.15567946441679</v>
       </c>
       <c r="F29" s="2">
-        <v>128.33396362321241</v>
+        <v>19.98691280029714</v>
       </c>
       <c r="G29" s="2">
-        <v>3.289613346523709</v>
+        <v>3.104483346525166</v>
       </c>
       <c r="H29" s="3">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
       <c r="A30" s="1">
         <v>46250</v>
       </c>
       <c r="B30" s="2">
-        <v>451.85533122369401</v>
+        <v>332.734012789184</v>
       </c>
       <c r="C30" s="2">
-        <v>67.593469603939184</v>
+        <v>50.02782521181636</v>
       </c>
       <c r="D30" s="2">
-        <v>253.38307744077329</v>
+        <v>253.3830774407733</v>
       </c>
       <c r="E30" s="2">
-        <v>18.29030030822355</v>
+        <v>18.2897728082266</v>
       </c>
       <c r="F30" s="2">
-        <v>110.9350760648648</v>
+        <v>9.448178967568609</v>
       </c>
       <c r="G30" s="2">
-        <v>1.652299750331375</v>
+        <v>1.585158360799154</v>
       </c>
       <c r="H30" s="3">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
       <c r="A31" s="1">
         <v>46251</v>
       </c>
       <c r="B31" s="2">
-        <v>444.19963340397697</v>
+        <v>407.7503264154084</v>
       </c>
       <c r="C31" s="2">
-        <v>69.229384823541878</v>
+        <v>63.50561813300786</v>
       </c>
       <c r="D31" s="2">
-        <v>339.3426651748473</v>
+        <v>313.450419339159</v>
       </c>
       <c r="E31" s="2">
-        <v>28.792287002782491</v>
+        <v>24.67019059661077</v>
       </c>
       <c r="F31" s="2">
-        <v>4.2416080502834594</v>
+        <v>3.739511103116804</v>
       </c>
       <c r="G31" s="2">
-        <v>2.593688352521923</v>
+        <v>2.384587243513928</v>
       </c>
       <c r="H31" s="3">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
       <c r="A32" s="1">
         <v>46252</v>
       </c>
       <c r="B32" s="2">
-        <v>663.99991174402078</v>
+        <v>417.26602835252</v>
       </c>
       <c r="C32" s="2">
-        <v>98.825859045259037</v>
+        <v>65.95898873674891</v>
       </c>
       <c r="D32" s="2">
-        <v>351.61717573950119</v>
+        <v>300.7385854345172</v>
       </c>
       <c r="E32" s="2">
-        <v>47.284813944860879</v>
+        <v>35.25884613889787</v>
       </c>
       <c r="F32" s="2">
-        <v>162.99776188943119</v>
+        <v>12.35078886192706</v>
       </c>
       <c r="G32" s="2">
-        <v>3.274301124968463</v>
+        <v>2.958819180428982</v>
       </c>
       <c r="H32" s="3">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
       <c r="A33" s="1">
         <v>46253</v>
       </c>
       <c r="B33" s="2">
-        <v>694.63439370326262</v>
+        <v>385.8583972031145</v>
       </c>
       <c r="C33" s="2">
-        <v>105.4410611541889</v>
+        <v>61.25962834504634</v>
       </c>
       <c r="D33" s="2">
-        <v>375.30410813305423</v>
+        <v>281.9130619070813</v>
       </c>
       <c r="E33" s="2">
-        <v>51.185770811071983</v>
+        <v>32.04785584772394</v>
       </c>
       <c r="F33" s="2">
-        <v>159.73487969220099</v>
+        <v>8.672184139076206</v>
       </c>
       <c r="G33" s="2">
-        <v>2.9685739127463759</v>
+        <v>1.965666964186563</v>
       </c>
       <c r="H33" s="3">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
       <c r="A34" s="1">
         <v>46254</v>
       </c>
       <c r="B34" s="2">
-        <v>699.10081959158458</v>
+        <v>392.6191602090271</v>
       </c>
       <c r="C34" s="2">
-        <v>104.7918750341363</v>
+        <v>62.98259769282847</v>
       </c>
       <c r="D34" s="2">
-        <v>342.15253555600049</v>
+        <v>269.9536030944208</v>
       </c>
       <c r="E34" s="2">
-        <v>86.095480821252693</v>
+        <v>47.03231324649106</v>
       </c>
       <c r="F34" s="2">
-        <v>162.5039526316296</v>
+        <v>10.25799559920198</v>
       </c>
       <c r="G34" s="2">
-        <v>3.5569755485653878</v>
+        <v>2.392650576084852</v>
       </c>
       <c r="H34" s="3">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
       <c r="A35" s="1">
         <v>46255</v>
       </c>
       <c r="B35" s="2">
-        <v>753.62975155918832</v>
+        <v>437.4563088380887</v>
       </c>
       <c r="C35" s="2">
-        <v>108.19687197884279</v>
+        <v>69.9847307672967</v>
       </c>
       <c r="D35" s="2">
-        <v>357.88138375552472</v>
+        <v>289.7360523767537</v>
       </c>
       <c r="E35" s="2">
-        <v>106.1723560326712</v>
+        <v>62.75813793066889</v>
       </c>
       <c r="F35" s="2">
-        <v>178.1908817241675</v>
+        <v>12.76626775762273</v>
       </c>
       <c r="G35" s="2">
-        <v>3.1882580679820638</v>
+        <v>2.211120005746682</v>
       </c>
       <c r="H35" s="3">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
       <c r="A36" s="1">
         <v>46256</v>
       </c>
       <c r="B36" s="2">
-        <v>806.8052939721432</v>
+        <v>483.2799235725563</v>
       </c>
       <c r="C36" s="2">
-        <v>119.715860667386</v>
+        <v>77.23476513435443</v>
       </c>
       <c r="D36" s="2">
-        <v>354.39638628257927</v>
+        <v>289.2397337409926</v>
       </c>
       <c r="E36" s="2">
-        <v>155.07115230291049</v>
+        <v>92.0354349932385</v>
       </c>
       <c r="F36" s="2">
-        <v>173.78248750738331</v>
+        <v>21.82957415414353</v>
       </c>
       <c r="G36" s="2">
-        <v>3.839407211884132</v>
+        <v>2.940415549827222</v>
       </c>
       <c r="H36" s="3">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
       <c r="A37" s="1">
         <v>46257</v>
       </c>
       <c r="B37" s="2">
-        <v>509.71101574216169</v>
+        <v>393.119182594441</v>
       </c>
       <c r="C37" s="2">
-        <v>80.476073851717842</v>
+        <v>62.58084405240086</v>
       </c>
       <c r="D37" s="2">
-        <v>276.7035884362291</v>
+        <v>226.3322109204285</v>
       </c>
       <c r="E37" s="2">
-        <v>148.7255431878624</v>
+        <v>101.0303626439281</v>
       </c>
       <c r="F37" s="2">
-        <v>1.531809989429183</v>
+        <v>1.470809433609247</v>
       </c>
       <c r="G37" s="2">
-        <v>2.27400027692318</v>
+        <v>1.704955544074376</v>
       </c>
       <c r="H37" s="3">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
       <c r="A38" s="1">
         <v>46258</v>
       </c>
       <c r="B38" s="2">
-        <v>549.37150319815999</v>
+        <v>271.0985417830046</v>
       </c>
       <c r="C38" s="2">
-        <v>88.838087343821925</v>
+        <v>43.1707900578777</v>
       </c>
       <c r="D38" s="2">
-        <v>328.92196055745887</v>
+        <v>173.8350256935282</v>
       </c>
       <c r="E38" s="2">
-        <v>110.2758588733835</v>
+        <v>50.23563352558348</v>
       </c>
       <c r="F38" s="2">
-        <v>17.277070292250979</v>
+        <v>2.570979442248742</v>
       </c>
       <c r="G38" s="2">
-        <v>4.0585261312447898</v>
+        <v>1.286113063766517</v>
       </c>
       <c r="H38" s="3">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
       <c r="A39" s="1">
         <v>46259</v>
       </c>
       <c r="B39" s="2">
-        <v>291.51065943485639</v>
+        <v>330.305268809463</v>
       </c>
       <c r="C39" s="2">
-        <v>45.212950681770842</v>
+        <v>51.07378846882118</v>
       </c>
       <c r="D39" s="2">
-        <v>141.9303877499006</v>
+        <v>167.5843121425939</v>
       </c>
       <c r="E39" s="2">
-        <v>99.898335480472696</v>
+        <v>80.44869748967596</v>
       </c>
       <c r="F39" s="2">
-        <v>3.2041005372173261</v>
+        <v>30.15956793795029</v>
       </c>
       <c r="G39" s="2">
-        <v>1.2648849854949451</v>
+        <v>1.038902770421571</v>
       </c>
       <c r="H39" s="3">
-        <v>34</v>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="1">
+        <v>46260</v>
+      </c>
+      <c r="B40" s="2">
+        <v>205.3681947480313</v>
+      </c>
+      <c r="C40" s="2">
+        <v>31.42087380833924</v>
+      </c>
+      <c r="D40" s="2">
+        <v>101.3812405179694</v>
+      </c>
+      <c r="E40" s="2">
+        <v>67.23086351268822</v>
+      </c>
+      <c r="F40" s="2">
+        <v>4.225343018008603</v>
+      </c>
+      <c r="G40" s="2">
+        <v>1.109873891025782</v>
+      </c>
+      <c r="H40" s="3">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1477,33 +1462,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="98e5d340-1856-43f4-9776-f0c5fe464598">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="0b1f5c80-8d6b-48f0-84f6-ea4845a21fc7" xsi:nil="true"/>
-    <Owner xmlns="98e5d340-1856-43f4-9776-f0c5fe464598">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Owner>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ED34050369F83D419D9CDC413B23CD9E" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="34f0fc59c9e9af6707b4260e15f92132">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="98e5d340-1856-43f4-9776-f0c5fe464598" xmlns:ns3="0b1f5c80-8d6b-48f0-84f6-ea4845a21fc7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="07a1a8fd5e9c2307366362e961f0f77e" ns2:_="" ns3:_="">
     <xsd:import namespace="98e5d340-1856-43f4-9776-f0c5fe464598"/>
@@ -1724,40 +1682,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="98e5d340-1856-43f4-9776-f0c5fe464598">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="0b1f5c80-8d6b-48f0-84f6-ea4845a21fc7" xsi:nil="true"/>
+    <Owner xmlns="98e5d340-1856-43f4-9776-f0c5fe464598">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Owner>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A9C776B-A62A-45AB-BC1C-78ED891AB8D5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="98e5d340-1856-43f4-9776-f0c5fe464598"/>
-    <ds:schemaRef ds:uri="0b1f5c80-8d6b-48f0-84f6-ea4845a21fc7"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36BC45A8-78E4-4D1B-9C0C-3A302260CF94}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF6E3674-AF72-4E1D-8B3E-07BDE01452F1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6379169-C6C9-4BFB-BA83-7A566FD10B93}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B7E3D98-EF0E-434F-A003-6047277231B3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="98e5d340-1856-43f4-9776-f0c5fe464598"/>
-    <ds:schemaRef ds:uri="0b1f5c80-8d6b-48f0-84f6-ea4845a21fc7"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{257D3E6A-C16F-4499-B42A-C3DD1C60179A}"/>
 </file>
--- a/sea_productive.xlsx
+++ b/sea_productive.xlsx
@@ -109,8 +109,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:H40" totalsRowShown="0">
-  <autoFilter ref="A1:H40"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:H43" totalsRowShown="0">
+  <autoFilter ref="A1:H43"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Date_Converted" dataDxfId="0"/>
     <tableColumn id="2" name="Staff Hour (In Hours)" dataDxfId="1"/>
@@ -410,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1406,7 +1406,7 @@
         <v>46259</v>
       </c>
       <c r="B39" s="2">
-        <v>330.305268809463</v>
+        <v>330.3145460313546</v>
       </c>
       <c r="C39" s="2">
         <v>51.07378846882118</v>
@@ -1415,7 +1415,7 @@
         <v>167.5843121425939</v>
       </c>
       <c r="E39" s="2">
-        <v>80.44869748967596</v>
+        <v>80.45797471156757</v>
       </c>
       <c r="F39" s="2">
         <v>30.15956793795029</v>
@@ -1432,25 +1432,103 @@
         <v>46260</v>
       </c>
       <c r="B40" s="2">
-        <v>205.3681947480313</v>
+        <v>308.6420069912855</v>
       </c>
       <c r="C40" s="2">
-        <v>31.42087380833924</v>
+        <v>47.71130578401188</v>
       </c>
       <c r="D40" s="2">
-        <v>101.3812405179694</v>
+        <v>150.9867505273588</v>
       </c>
       <c r="E40" s="2">
-        <v>67.23086351268822</v>
+        <v>77.21690185439256</v>
       </c>
       <c r="F40" s="2">
-        <v>4.225343018008603</v>
+        <v>31.22530160812868</v>
       </c>
       <c r="G40" s="2">
-        <v>1.109873891025782</v>
+        <v>1.501747217393584</v>
       </c>
       <c r="H40" s="3">
-        <v>32</v>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="1">
+        <v>46261</v>
+      </c>
+      <c r="B41" s="2">
+        <v>286.1038685432346</v>
+      </c>
+      <c r="C41" s="2">
+        <v>42.50869315096902</v>
+      </c>
+      <c r="D41" s="2">
+        <v>143.1784045228357</v>
+      </c>
+      <c r="E41" s="2">
+        <v>64.57876411162576</v>
+      </c>
+      <c r="F41" s="2">
+        <v>34.68306953739789</v>
+      </c>
+      <c r="G41" s="2">
+        <v>1.154937220406201</v>
+      </c>
+      <c r="H41" s="3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" s="1">
+        <v>46262</v>
+      </c>
+      <c r="B42" s="2">
+        <v>309.99962861169</v>
+      </c>
+      <c r="C42" s="2">
+        <v>47.7066908056289</v>
+      </c>
+      <c r="D42" s="2">
+        <v>160.115031471247</v>
+      </c>
+      <c r="E42" s="2">
+        <v>63.65117380062739</v>
+      </c>
+      <c r="F42" s="2">
+        <v>36.90015556961298</v>
+      </c>
+      <c r="G42" s="2">
+        <v>1.626576964573728</v>
+      </c>
+      <c r="H42" s="3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" s="1">
+        <v>46263</v>
+      </c>
+      <c r="B43" s="2">
+        <v>220.4689741128905</v>
+      </c>
+      <c r="C43" s="2">
+        <v>31.94074715596934</v>
+      </c>
+      <c r="D43" s="2">
+        <v>128.3376855016267</v>
+      </c>
+      <c r="E43" s="2">
+        <v>51.24936981888695</v>
+      </c>
+      <c r="F43" s="2">
+        <v>7.404625788902243</v>
+      </c>
+      <c r="G43" s="2">
+        <v>1.536545847505331</v>
+      </c>
+      <c r="H43" s="3">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1710,13 +1788,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36BC45A8-78E4-4D1B-9C0C-3A302260CF94}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F0495492-958A-48CC-82B5-D6D4825B010F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6379169-C6C9-4BFB-BA83-7A566FD10B93}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7617699-A2F7-477C-B8FC-726A53DB0B2B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{257D3E6A-C16F-4499-B42A-C3DD1C60179A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73599678-B5B6-4CB1-A4DF-E8197071EED6}"/>
 </file>
--- a/sea_productive.xlsx
+++ b/sea_productive.xlsx
@@ -109,8 +109,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:H43" totalsRowShown="0">
-  <autoFilter ref="A1:H43"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:H48" totalsRowShown="0">
+  <autoFilter ref="A1:H48"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Date_Converted" dataDxfId="0"/>
     <tableColumn id="2" name="Staff Hour (In Hours)" dataDxfId="1"/>
@@ -410,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1016,7 +1016,7 @@
         <v>46244</v>
       </c>
       <c r="B24" s="2">
-        <v>462.4270792535519</v>
+        <v>458.0397142333695</v>
       </c>
       <c r="C24" s="2">
         <v>67.82130650916861</v>
@@ -1028,13 +1028,13 @@
         <v>15.39954031768462</v>
       </c>
       <c r="F24" s="2">
-        <v>5.55911361116502</v>
+        <v>1.199494979166322</v>
       </c>
       <c r="G24" s="2">
-        <v>5.542084470287534</v>
+        <v>5.514338082103834</v>
       </c>
       <c r="H24" s="3">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1042,7 +1042,7 @@
         <v>46245</v>
       </c>
       <c r="B25" s="2">
-        <v>420.5265529979246</v>
+        <v>414.598878777447</v>
       </c>
       <c r="C25" s="2">
         <v>62.20752357936153</v>
@@ -1054,13 +1054,13 @@
         <v>21.49635530477597</v>
       </c>
       <c r="F25" s="2">
-        <v>7.704421999106804</v>
+        <v>1.796588611519999</v>
       </c>
       <c r="G25" s="2">
-        <v>2.587768898639414</v>
+        <v>2.567928065748678</v>
       </c>
       <c r="H25" s="3">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1068,10 +1068,10 @@
         <v>46246</v>
       </c>
       <c r="B26" s="2">
-        <v>443.1221675652204</v>
+        <v>431.2256536189487</v>
       </c>
       <c r="C26" s="2">
-        <v>64.06988657807311</v>
+        <v>64.06943213361834</v>
       </c>
       <c r="D26" s="2">
         <v>335.2939479168732</v>
@@ -1080,13 +1080,13 @@
         <v>25.42092049325092</v>
       </c>
       <c r="F26" s="2">
-        <v>16.16713979319566</v>
+        <v>4.281623346532385</v>
       </c>
       <c r="G26" s="2">
-        <v>2.170272783827451</v>
+        <v>2.159729728673895</v>
       </c>
       <c r="H26" s="3">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1146,10 +1146,10 @@
         <v>46249</v>
       </c>
       <c r="B29" s="2">
-        <v>499.2150502190239</v>
+        <v>484.0771382887244</v>
       </c>
       <c r="C29" s="2">
-        <v>74.85895852548795</v>
+        <v>72.43953412118471</v>
       </c>
       <c r="D29" s="2">
         <v>388.1090160822968</v>
@@ -1158,13 +1158,13 @@
         <v>13.15567946441679</v>
       </c>
       <c r="F29" s="2">
-        <v>19.98691280029714</v>
+        <v>7.273799163144496</v>
       </c>
       <c r="G29" s="2">
-        <v>3.104483346525166</v>
+        <v>3.099109457681577</v>
       </c>
       <c r="H29" s="3">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1172,10 +1172,10 @@
         <v>46250</v>
       </c>
       <c r="B30" s="2">
-        <v>332.734012789184</v>
+        <v>322.2978593918226</v>
       </c>
       <c r="C30" s="2">
-        <v>50.02782521181636</v>
+        <v>49.03985078202354</v>
       </c>
       <c r="D30" s="2">
         <v>253.3830774407733</v>
@@ -1184,13 +1184,13 @@
         <v>18.2897728082266</v>
       </c>
       <c r="F30" s="2">
-        <v>9.448178967568609</v>
+        <v>0</v>
       </c>
       <c r="G30" s="2">
         <v>1.585158360799154</v>
       </c>
       <c r="H30" s="3">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1224,25 +1224,25 @@
         <v>46252</v>
       </c>
       <c r="B32" s="2">
-        <v>417.26602835252</v>
+        <v>399.2559978183333</v>
       </c>
       <c r="C32" s="2">
-        <v>65.95898873674891</v>
+        <v>62.93444349305187</v>
       </c>
       <c r="D32" s="2">
-        <v>300.7385854345172</v>
+        <v>288.4641765298038</v>
       </c>
       <c r="E32" s="2">
-        <v>35.25884613889787</v>
+        <v>33.78893501101269</v>
       </c>
       <c r="F32" s="2">
-        <v>12.35078886192706</v>
+        <v>11.37516360258063</v>
       </c>
       <c r="G32" s="2">
-        <v>2.958819180428982</v>
+        <v>2.693279181884395</v>
       </c>
       <c r="H32" s="3">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1250,25 +1250,25 @@
         <v>46253</v>
       </c>
       <c r="B33" s="2">
-        <v>385.8583972031145</v>
+        <v>368.0096868520228</v>
       </c>
       <c r="C33" s="2">
-        <v>61.25962834504634</v>
+        <v>58.27979694623804</v>
       </c>
       <c r="D33" s="2">
-        <v>281.9130619070813</v>
+        <v>269.3418276750907</v>
       </c>
       <c r="E33" s="2">
-        <v>32.04785584772394</v>
+        <v>30.01644863002597</v>
       </c>
       <c r="F33" s="2">
         <v>8.672184139076206</v>
       </c>
       <c r="G33" s="2">
-        <v>1.965666964186563</v>
+        <v>1.699429461591774</v>
       </c>
       <c r="H33" s="3">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1276,25 +1276,25 @@
         <v>46254</v>
       </c>
       <c r="B34" s="2">
-        <v>392.6191602090271</v>
+        <v>383.6186945644871</v>
       </c>
       <c r="C34" s="2">
-        <v>62.98259769282847</v>
+        <v>61.48986879227502</v>
       </c>
       <c r="D34" s="2">
-        <v>269.9536030944208</v>
+        <v>264.6406183216989</v>
       </c>
       <c r="E34" s="2">
-        <v>47.03231324649106</v>
+        <v>44.86692127498902</v>
       </c>
       <c r="F34" s="2">
         <v>10.25799559920198</v>
       </c>
       <c r="G34" s="2">
-        <v>2.392650576084852</v>
+        <v>2.363290576322211</v>
       </c>
       <c r="H34" s="3">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1302,25 +1302,25 @@
         <v>46255</v>
       </c>
       <c r="B35" s="2">
-        <v>437.4563088380887</v>
+        <v>419.2664725631245</v>
       </c>
       <c r="C35" s="2">
-        <v>69.9847307672967</v>
+        <v>67.01250322972734</v>
       </c>
       <c r="D35" s="2">
-        <v>289.7360523767537</v>
+        <v>281.4347498425984</v>
       </c>
       <c r="E35" s="2">
-        <v>62.75813793066889</v>
+        <v>57.07031952634868</v>
       </c>
       <c r="F35" s="2">
-        <v>12.76626775762273</v>
+        <v>11.77501246385276</v>
       </c>
       <c r="G35" s="2">
-        <v>2.211120005746682</v>
+        <v>1.973887500597371</v>
       </c>
       <c r="H35" s="3">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1328,25 +1328,25 @@
         <v>46256</v>
       </c>
       <c r="B36" s="2">
-        <v>483.2799235725563</v>
+        <v>465.0849793554837</v>
       </c>
       <c r="C36" s="2">
-        <v>77.23476513435443</v>
+        <v>74.26822184206711</v>
       </c>
       <c r="D36" s="2">
-        <v>289.2397337409926</v>
+        <v>280.7708881379902</v>
       </c>
       <c r="E36" s="2">
-        <v>92.0354349932385</v>
+        <v>85.49261995250774</v>
       </c>
       <c r="F36" s="2">
         <v>21.82957415414353</v>
       </c>
       <c r="G36" s="2">
-        <v>2.940415549827222</v>
+        <v>2.723675268775163</v>
       </c>
       <c r="H36" s="3">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1380,25 +1380,25 @@
         <v>46258</v>
       </c>
       <c r="B38" s="2">
-        <v>271.0985417830046</v>
+        <v>235.2853370260336</v>
       </c>
       <c r="C38" s="2">
-        <v>43.1707900578777</v>
+        <v>37.08468008063733</v>
       </c>
       <c r="D38" s="2">
-        <v>173.8350256935282</v>
+        <v>156.8891298472201</v>
       </c>
       <c r="E38" s="2">
-        <v>50.23563352558348</v>
+        <v>38.80698652924763</v>
       </c>
       <c r="F38" s="2">
-        <v>2.570979442248742</v>
+        <v>1.610884726527664</v>
       </c>
       <c r="G38" s="2">
-        <v>1.286113063766517</v>
+        <v>0.8936558424008804</v>
       </c>
       <c r="H38" s="3">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1406,25 +1406,25 @@
         <v>46259</v>
       </c>
       <c r="B39" s="2">
-        <v>330.3145460313546</v>
+        <v>272.5900570905899</v>
       </c>
       <c r="C39" s="2">
-        <v>51.07378846882118</v>
+        <v>42.63818873936931</v>
       </c>
       <c r="D39" s="2">
-        <v>167.5843121425939</v>
+        <v>154.7737228923795</v>
       </c>
       <c r="E39" s="2">
-        <v>80.45797471156757</v>
+        <v>71.46191187466391</v>
       </c>
       <c r="F39" s="2">
-        <v>30.15956793795029</v>
+        <v>2.891773310022222</v>
       </c>
       <c r="G39" s="2">
-        <v>1.038902770421571</v>
+        <v>0.8244602741549413</v>
       </c>
       <c r="H39" s="3">
-        <v>38</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1432,25 +1432,25 @@
         <v>46260</v>
       </c>
       <c r="B40" s="2">
-        <v>308.6420069912855</v>
+        <v>268.0549161466514</v>
       </c>
       <c r="C40" s="2">
-        <v>47.71130578401188</v>
+        <v>42.58442437181042</v>
       </c>
       <c r="D40" s="2">
-        <v>150.9867505273588</v>
+        <v>145.9477679910565</v>
       </c>
       <c r="E40" s="2">
-        <v>77.21690185439256</v>
+        <v>74.98669436097146</v>
       </c>
       <c r="F40" s="2">
-        <v>31.22530160812868</v>
+        <v>3.133208872195747</v>
       </c>
       <c r="G40" s="2">
-        <v>1.501747217393584</v>
+        <v>1.402820550617244</v>
       </c>
       <c r="H40" s="3">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1458,25 +1458,25 @@
         <v>46261</v>
       </c>
       <c r="B41" s="2">
-        <v>286.1038685432346</v>
+        <v>228.0834418903121</v>
       </c>
       <c r="C41" s="2">
-        <v>42.50869315096902</v>
+        <v>35.44571624476877</v>
       </c>
       <c r="D41" s="2">
-        <v>143.1784045228357</v>
+        <v>131.6818270637892</v>
       </c>
       <c r="E41" s="2">
-        <v>64.57876411162576</v>
+        <v>55.65615105956223</v>
       </c>
       <c r="F41" s="2">
-        <v>34.68306953739789</v>
+        <v>4.59136558516158</v>
       </c>
       <c r="G41" s="2">
-        <v>1.154937220406201</v>
+        <v>0.708381937030289</v>
       </c>
       <c r="H41" s="3">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1484,25 +1484,25 @@
         <v>46262</v>
       </c>
       <c r="B42" s="2">
-        <v>309.99962861169</v>
+        <v>242.553671847742</v>
       </c>
       <c r="C42" s="2">
-        <v>47.7066908056289</v>
+        <v>37.49895384332372</v>
       </c>
       <c r="D42" s="2">
-        <v>160.115031471247</v>
+        <v>143.5476370646916</v>
       </c>
       <c r="E42" s="2">
-        <v>63.65117380062739</v>
+        <v>50.03631717801094</v>
       </c>
       <c r="F42" s="2">
-        <v>36.90015556961298</v>
+        <v>10.11687763570083</v>
       </c>
       <c r="G42" s="2">
-        <v>1.626576964573728</v>
+        <v>1.353886126014921</v>
       </c>
       <c r="H42" s="3">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1510,25 +1510,155 @@
         <v>46263</v>
       </c>
       <c r="B43" s="2">
-        <v>220.4689741128905</v>
+        <v>263.7361664312824</v>
       </c>
       <c r="C43" s="2">
-        <v>31.94074715596934</v>
+        <v>38.58693327976598</v>
       </c>
       <c r="D43" s="2">
-        <v>128.3376855016267</v>
+        <v>169.0165806533277</v>
       </c>
       <c r="E43" s="2">
-        <v>51.24936981888695</v>
+        <v>47.32503391609734</v>
       </c>
       <c r="F43" s="2">
-        <v>7.404625788902243</v>
+        <v>6.877144689733783</v>
       </c>
       <c r="G43" s="2">
-        <v>1.536545847505331</v>
+        <v>1.930473892357614</v>
       </c>
       <c r="H43" s="3">
-        <v>27</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="1">
+        <v>46264</v>
+      </c>
+      <c r="B44" s="2">
+        <v>218.7746699998662</v>
+      </c>
+      <c r="C44" s="2">
+        <v>32.33282252651252</v>
+      </c>
+      <c r="D44" s="2">
+        <v>144.5931242529652</v>
+      </c>
+      <c r="E44" s="2">
+        <v>37.66004991756752</v>
+      </c>
+      <c r="F44" s="2">
+        <v>2.307382768011756</v>
+      </c>
+      <c r="G44" s="2">
+        <v>1.881290534809232</v>
+      </c>
+      <c r="H44" s="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" s="1">
+        <v>46265</v>
+      </c>
+      <c r="B45" s="2">
+        <v>108.8138387955531</v>
+      </c>
+      <c r="C45" s="2">
+        <v>18.0344401949313</v>
+      </c>
+      <c r="D45" s="2">
+        <v>85.39879222923813</v>
+      </c>
+      <c r="E45" s="2">
+        <v>4.67153526680751</v>
+      </c>
+      <c r="F45" s="2">
+        <v>0.06592166476779514</v>
+      </c>
+      <c r="G45" s="2">
+        <v>0.6431494398083951</v>
+      </c>
+      <c r="H45" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="1">
+        <v>46266</v>
+      </c>
+      <c r="B46" s="2">
+        <v>126.6281750942086</v>
+      </c>
+      <c r="C46" s="2">
+        <v>20.03433480409284</v>
+      </c>
+      <c r="D46" s="2">
+        <v>74.83791621669118</v>
+      </c>
+      <c r="E46" s="2">
+        <v>31.14009156523479</v>
+      </c>
+      <c r="F46" s="2">
+        <v>0</v>
+      </c>
+      <c r="G46" s="2">
+        <v>0.6158325081898106</v>
+      </c>
+      <c r="H46" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" s="1">
+        <v>46267</v>
+      </c>
+      <c r="B47" s="2">
+        <v>109.5598976120521</v>
+      </c>
+      <c r="C47" s="2">
+        <v>17.49252735397882</v>
+      </c>
+      <c r="D47" s="2">
+        <v>68.17931260380092</v>
+      </c>
+      <c r="E47" s="2">
+        <v>23.31687931662218</v>
+      </c>
+      <c r="F47" s="2">
+        <v>0</v>
+      </c>
+      <c r="G47" s="2">
+        <v>0.5711783376501666</v>
+      </c>
+      <c r="H47" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" s="1">
+        <v>46268</v>
+      </c>
+      <c r="B48" s="2">
+        <v>62.36777227819354</v>
+      </c>
+      <c r="C48" s="2">
+        <v>10.05310173326793</v>
+      </c>
+      <c r="D48" s="2">
+        <v>33.60992530503285</v>
+      </c>
+      <c r="E48" s="2">
+        <v>18.5215457992711</v>
+      </c>
+      <c r="F48" s="2">
+        <v>0</v>
+      </c>
+      <c r="G48" s="2">
+        <v>0.1831994406216674</v>
+      </c>
+      <c r="H48" s="3">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1788,13 +1918,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F0495492-958A-48CC-82B5-D6D4825B010F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ACA1E8F6-C90F-4958-AAA6-9B31F0CBCF9E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7617699-A2F7-477C-B8FC-726A53DB0B2B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB86E38B-36D2-4AA4-876B-8246A038A4F8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73599678-B5B6-4CB1-A4DF-E8197071EED6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F310FD03-ACBA-49A1-A81D-945663D2DDFE}"/>
 </file>
--- a/sea_productive.xlsx
+++ b/sea_productive.xlsx
@@ -109,8 +109,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:H48" totalsRowShown="0">
-  <autoFilter ref="A1:H48"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:H50" totalsRowShown="0">
+  <autoFilter ref="A1:H50"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Date_Converted" dataDxfId="0"/>
     <tableColumn id="2" name="Staff Hour (In Hours)" dataDxfId="1"/>
@@ -410,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1640,25 +1640,77 @@
         <v>46268</v>
       </c>
       <c r="B48" s="2">
-        <v>62.36777227819354</v>
+        <v>146.338607085512</v>
       </c>
       <c r="C48" s="2">
-        <v>10.05310173326793</v>
+        <v>23.75823795022133</v>
       </c>
       <c r="D48" s="2">
-        <v>33.60992530503285</v>
+        <v>96.78985414079727</v>
       </c>
       <c r="E48" s="2">
-        <v>18.5215457992711</v>
+        <v>21.60897969089241</v>
       </c>
       <c r="F48" s="2">
-        <v>0</v>
+        <v>2.893533897507522</v>
       </c>
       <c r="G48" s="2">
-        <v>0.1831994406216674</v>
+        <v>1.288001406093438</v>
       </c>
       <c r="H48" s="3">
-        <v>7</v>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" s="1">
+        <v>46269</v>
+      </c>
+      <c r="B49" s="2">
+        <v>136.3571162579959</v>
+      </c>
+      <c r="C49" s="2">
+        <v>22.71571285638234</v>
+      </c>
+      <c r="D49" s="2">
+        <v>98.40498451118177</v>
+      </c>
+      <c r="E49" s="2">
+        <v>9.447709715557027</v>
+      </c>
+      <c r="F49" s="2">
+        <v>3.583837791648176</v>
+      </c>
+      <c r="G49" s="2">
+        <v>2.20487138322658</v>
+      </c>
+      <c r="H49" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" s="1">
+        <v>46270</v>
+      </c>
+      <c r="B50" s="2">
+        <v>81.5993540147842</v>
+      </c>
+      <c r="C50" s="2">
+        <v>11.91035999440485</v>
+      </c>
+      <c r="D50" s="2">
+        <v>65.48042819205723</v>
+      </c>
+      <c r="E50" s="2">
+        <v>2.349966670905964</v>
+      </c>
+      <c r="F50" s="2">
+        <v>0.5054705414507125</v>
+      </c>
+      <c r="G50" s="2">
+        <v>1.353128615965446</v>
+      </c>
+      <c r="H50" s="3">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1918,13 +1970,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ACA1E8F6-C90F-4958-AAA6-9B31F0CBCF9E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8AC1312-E281-4E6B-852F-53B4F613B30E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB86E38B-36D2-4AA4-876B-8246A038A4F8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5AFEB72F-A47B-49ED-86E2-62FA4FEB8209}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F310FD03-ACBA-49A1-A81D-945663D2DDFE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B22B03BE-3FB4-47BF-822F-4063AE59E6A2}"/>
 </file>
--- a/sea_productive.xlsx
+++ b/sea_productive.xlsx
@@ -109,8 +109,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:H50" totalsRowShown="0">
-  <autoFilter ref="A1:H50"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:H51" totalsRowShown="0">
+  <autoFilter ref="A1:H51"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Date_Converted" dataDxfId="0"/>
     <tableColumn id="2" name="Staff Hour (In Hours)" dataDxfId="1"/>
@@ -410,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1250,7 +1250,7 @@
         <v>46253</v>
       </c>
       <c r="B33" s="2">
-        <v>368.0096868520228</v>
+        <v>368.0096868520227</v>
       </c>
       <c r="C33" s="2">
         <v>58.27979694623804</v>
@@ -1692,25 +1692,51 @@
         <v>46270</v>
       </c>
       <c r="B50" s="2">
-        <v>81.5993540147842</v>
+        <v>155.6289612001281</v>
       </c>
       <c r="C50" s="2">
-        <v>11.91035999440485</v>
+        <v>26.30784478680955</v>
       </c>
       <c r="D50" s="2">
-        <v>65.48042819205723</v>
+        <v>123.2937355797528</v>
       </c>
       <c r="E50" s="2">
-        <v>2.349966670905964</v>
+        <v>2.732204720384131</v>
       </c>
       <c r="F50" s="2">
         <v>0.5054705414507125</v>
       </c>
       <c r="G50" s="2">
-        <v>1.353128615965446</v>
+        <v>2.789705571730932</v>
       </c>
       <c r="H50" s="3">
-        <v>16</v>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="1">
+        <v>46271</v>
+      </c>
+      <c r="B51" s="2">
+        <v>9.015317181447108</v>
+      </c>
+      <c r="C51" s="2">
+        <v>1.424716923551427</v>
+      </c>
+      <c r="D51" s="2">
+        <v>7.581899146627014</v>
+      </c>
+      <c r="E51" s="2">
+        <v>0.00470972225897842</v>
+      </c>
+      <c r="F51" s="2">
+        <v>0</v>
+      </c>
+      <c r="G51" s="2">
+        <v>0.003991389009687636</v>
+      </c>
+      <c r="H51" s="3">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1970,13 +1996,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8AC1312-E281-4E6B-852F-53B4F613B30E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E05534B-BE04-4651-882B-5B367B23E481}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5AFEB72F-A47B-49ED-86E2-62FA4FEB8209}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{21DFD00A-C7C0-497B-8386-B18797DF83CF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B22B03BE-3FB4-47BF-822F-4063AE59E6A2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA14CC21-92FF-4825-A4BC-A1DAA4323D4C}"/>
 </file>